--- a/data/MACSI seminar series.xlsx
+++ b/data/MACSI seminar series.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ulcampus-my.sharepoint.com/personal/david_osullivan_ul_ie/Documents/Academic_work/_Misc/MACSI Seminars/macsi-seminars.github.io/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="330" documentId="13_ncr:1_{12BE53B5-C8C7-44FE-8280-19C653D9122E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{630C7241-9336-4D66-B399-5744B6D942CA}"/>
+  <xr:revisionPtr revIDLastSave="337" documentId="13_ncr:1_{12BE53B5-C8C7-44FE-8280-19C653D9122E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF5AA23A-AA63-F64E-AC91-E809D4E886F6}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="416">
   <si>
     <t>Fill in as much of the green boxes as possible. Ideally, this would be before you have finished your visitors travel dates (just to avoid double booking).</t>
   </si>
@@ -1141,208 +1141,220 @@
     <t>Catherine Higgins</t>
   </si>
   <si>
+    <t>https://scholar.google.com/citations?user=ikeLYIMAAAAJ&amp;hl=en</t>
+  </si>
+  <si>
+    <t>https://link.springer.com/article/10.1007/s11634-024-00611-8 ; https://onlinelibrary.wiley.com/doi/10.1002/qub2.70011</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/catherine-higgins-4b5hg/</t>
+  </si>
+  <si>
+    <t>Stuart Thomson</t>
+  </si>
+  <si>
+    <t>Cornelius Fritz</t>
+  </si>
+  <si>
+    <t>Trinity college Dublin</t>
+  </si>
+  <si>
+    <t>Scalable Durational Event Models: Application to Physical and Digital Interactions</t>
+  </si>
+  <si>
+    <t>Durable interactions are ubiquitous in social network analysis and are increasingly observed with precise time stamps. Phone and video calls, for example, are events to which a specific duration can be assigned. We term data encoding interactions with the start and end times “durational event data”. Recent advances in data collection have enabled the observation of such data over extended periods of time and between large populations of actors. Methodologically, we propose the Durational Event Model, an extension of Relational Event Models that decouples the modeling of event incidence from event duration. Computationally, we derive a fast, memory-efficient, and exact block-coordinate ascent algorithm to facilitate large-scale inference. Theoretical complexity analysis and numerical simulations demonstrate computational superiority of this approach over state-of-the-art methods. We apply the model to physical and digital interactions among college students in Copenhagen.  Our empirical findings reveal that past interactions drive physical interactions, whereas digital interactions are influenced predominantly by friendship ties and prior dyadic contact. </t>
+  </si>
+  <si>
+    <t>https://scholar.google.de/citations?user=0X7D4mwAAAAJ&amp;hl=en</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://arxiv.org/abs/2504.00049 </t>
+  </si>
+  <si>
+    <t>https://www.tcd.ie/scss/people/academic-staff/fritzc/ ; https://www.corneliusfritz.com/about/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chris Howland </t>
+  </si>
+  <si>
+    <t>Carl Scarrott</t>
+  </si>
+  <si>
+    <t>https://scholar.google.com/citations?user=kRgtZZcAAAAJ&amp;hl=en</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://research.universityofgalway.ie/en/persons/carl-scarrott/ </t>
+  </si>
+  <si>
+    <t>Andrew Keane</t>
+  </si>
+  <si>
+    <t>Open</t>
+  </si>
+  <si>
+    <t>May</t>
+  </si>
+  <si>
+    <t>This is a just a place for those who are interested but that dont have a specific date in mind. (Ideally, a couple of these are people that we could invite with relatively short notice to fill missing slots.)</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Where are they from?</t>
+  </si>
+  <si>
+    <t>Adacemic Host</t>
+  </si>
+  <si>
+    <t>Colm</t>
+  </si>
+  <si>
+    <t>Niamh Cahill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Niall Madden </t>
+  </si>
+  <si>
+    <t>Mehakpreet</t>
+  </si>
+  <si>
+    <t>Paul Weaver (invitation sent)</t>
+  </si>
+  <si>
+    <t>UL (Bernal)</t>
+  </si>
+  <si>
+    <t>Eleanor Doman</t>
+  </si>
+  <si>
+    <t>Manchester</t>
+  </si>
+  <si>
+    <t>Connor Hacket</t>
+  </si>
+  <si>
+    <t>MU</t>
+  </si>
+  <si>
+    <t>David Henry (?)</t>
+  </si>
+  <si>
+    <t>Jess Enright</t>
+  </si>
+  <si>
+    <t>Glasgow</t>
+  </si>
+  <si>
+    <t>JS/Networks</t>
+  </si>
+  <si>
+    <t>Ben Swallows</t>
+  </si>
+  <si>
+    <t>St Andrews</t>
+  </si>
+  <si>
+    <t>JS</t>
+  </si>
+  <si>
+    <t>Andrew Finlay</t>
+  </si>
+  <si>
+    <t>Uni Michigan</t>
+  </si>
+  <si>
+    <t>Denis Allard</t>
+  </si>
+  <si>
+    <t>INRAE</t>
+  </si>
+  <si>
+    <t>Nicholas J Clark</t>
+  </si>
+  <si>
+    <t>University of Queensland</t>
+  </si>
+  <si>
+    <t>Andrew Zammit Mangion</t>
+  </si>
+  <si>
+    <t>University of Wollongong</t>
+  </si>
+  <si>
+    <t>Trinity</t>
+  </si>
+  <si>
+    <t>DOS</t>
+  </si>
+  <si>
+    <t>UCD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paul Weaver </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suzanne Fielding </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doireann O'Kiely and Anthony </t>
+  </si>
+  <si>
+    <t>Week</t>
+  </si>
+  <si>
+    <t>Speaker</t>
+  </si>
+  <si>
+    <t>Taken</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taken </t>
+  </si>
+  <si>
+    <t>Seminar Series AY2024-25 Sem 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contact david.osullivan@ul.ie &amp; mehakpreet.singh@ul.ie to book a speaker in. </t>
+  </si>
+  <si>
+    <t>Deptartmental contact</t>
+  </si>
+  <si>
+    <t>Wednesday</t>
+  </si>
+  <si>
+    <t>Robery Garvey</t>
+  </si>
+  <si>
+    <t>Tentative speaker</t>
+  </si>
+  <si>
+    <t>Leornard Henckel</t>
+  </si>
+  <si>
     <t>Novel approaches for clustering gene expression profiles in temporal and spatial transcriptomics</t>
   </si>
   <si>
     <t>Functional clustering methods group curves without prior knowledge of the underlying clustering structure. A key challenge is class imbalance,where some clusters are significantly larger than others. This leads to smaller clusters being misclassified into larger clusters, resulting in a poor clustering accuracy. While class imbalance is well-studied in supervised classification, it has received limited attention in unsupervised settings.  To address this, we introduce functional iterative hierarchical clustering (funIHC), a novel method for clustering imbalanced one-dimensional functional data.  We demonstrate the effectiveness of funIHC against sixteen leading alternatives.  We extend this methodology to two-dimensional functional data with spatial transcriptomics IHC (stIHC), focusing on clustering spatially variable genes into modules that reflect shared spatial expression patterns. We demonstrate that stIHC outperforms existing clustering methods in spatial transcriptomics. Gene ontology enrichment analysis confirms that both funIHC and stIHC identify biologically coherent and distinct clusters, demonstrating their utility for meaningful clustering in both time and space.</t>
   </si>
   <si>
-    <t>https://scholar.google.com/citations?user=ikeLYIMAAAAJ&amp;hl=en</t>
-  </si>
-  <si>
-    <t>https://link.springer.com/article/10.1007/s11634-024-00611-8 ; https://onlinelibrary.wiley.com/doi/10.1002/qub2.70011</t>
-  </si>
-  <si>
-    <t>https://www.linkedin.com/in/catherine-higgins-4b5hg/</t>
-  </si>
-  <si>
-    <t>Stuart Thomson</t>
-  </si>
-  <si>
     <t>Driven interfacial hydrodynamics, and some physics-informed machine learning</t>
   </si>
   <si>
     <t>In this talk I will present a few topics of recent interest that centre around the theme of “driven interfacial hydrodynamics”: fluid mechanical systems in which droplets and particles are self-propelled through interaction with the environment. I will also present some very recent work on using differentiable physics (a branch of physics-informed machine learning) to determine constitutive relations for highly plasticised metals.</t>
   </si>
   <si>
-    <t>Cornelius Fritz</t>
-  </si>
-  <si>
-    <t>Trinity college Dublin</t>
-  </si>
-  <si>
-    <t>Scalable Durational Event Models: Application to Physical and Digital Interactions</t>
-  </si>
-  <si>
-    <t>Durable interactions are ubiquitous in social network analysis and are increasingly observed with precise time stamps. Phone and video calls, for example, are events to which a specific duration can be assigned. We term data encoding interactions with the start and end times “durational event data”. Recent advances in data collection have enabled the observation of such data over extended periods of time and between large populations of actors. Methodologically, we propose the Durational Event Model, an extension of Relational Event Models that decouples the modeling of event incidence from event duration. Computationally, we derive a fast, memory-efficient, and exact block-coordinate ascent algorithm to facilitate large-scale inference. Theoretical complexity analysis and numerical simulations demonstrate computational superiority of this approach over state-of-the-art methods. We apply the model to physical and digital interactions among college students in Copenhagen.  Our empirical findings reveal that past interactions drive physical interactions, whereas digital interactions are influenced predominantly by friendship ties and prior dyadic contact. </t>
-  </si>
-  <si>
-    <t>https://scholar.google.de/citations?user=0X7D4mwAAAAJ&amp;hl=en</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://arxiv.org/abs/2504.00049 </t>
-  </si>
-  <si>
-    <t>https://www.tcd.ie/scss/people/academic-staff/fritzc/ ; https://www.corneliusfritz.com/about/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chris Howland </t>
-  </si>
-  <si>
-    <t>Carl Scarrott</t>
-  </si>
-  <si>
-    <t>https://scholar.google.com/citations?user=kRgtZZcAAAAJ&amp;hl=en</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://research.universityofgalway.ie/en/persons/carl-scarrott/ </t>
-  </si>
-  <si>
-    <t>Andrew Keane</t>
-  </si>
-  <si>
-    <t>Open</t>
-  </si>
-  <si>
-    <t>May</t>
-  </si>
-  <si>
-    <t>This is a just a place for those who are interested but that dont have a specific date in mind. (Ideally, a couple of these are people that we could invite with relatively short notice to fill missing slots.)</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Where are they from?</t>
-  </si>
-  <si>
-    <t>Adacemic Host</t>
-  </si>
-  <si>
-    <t>Colm</t>
-  </si>
-  <si>
-    <t>Niamh Cahill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Niall Madden </t>
-  </si>
-  <si>
-    <t>Mehakpreet</t>
-  </si>
-  <si>
-    <t>Paul Weaver (invitation sent)</t>
-  </si>
-  <si>
-    <t>UL (Bernal)</t>
-  </si>
-  <si>
-    <t>Eleanor Doman</t>
-  </si>
-  <si>
-    <t>Manchester</t>
-  </si>
-  <si>
-    <t>Connor Hacket</t>
-  </si>
-  <si>
-    <t>MU</t>
-  </si>
-  <si>
-    <t>David Henry (?)</t>
-  </si>
-  <si>
-    <t>Jess Enright</t>
-  </si>
-  <si>
-    <t>Glasgow</t>
-  </si>
-  <si>
-    <t>JS/Networks</t>
-  </si>
-  <si>
-    <t>Ben Swallows</t>
-  </si>
-  <si>
-    <t>St Andrews</t>
-  </si>
-  <si>
-    <t>JS</t>
-  </si>
-  <si>
-    <t>Andrew Finlay</t>
-  </si>
-  <si>
-    <t>Uni Michigan</t>
-  </si>
-  <si>
-    <t>Denis Allard</t>
-  </si>
-  <si>
-    <t>INRAE</t>
-  </si>
-  <si>
-    <t>Nicholas J Clark</t>
-  </si>
-  <si>
-    <t>University of Queensland</t>
-  </si>
-  <si>
-    <t>Andrew Zammit Mangion</t>
-  </si>
-  <si>
-    <t>University of Wollongong</t>
-  </si>
-  <si>
-    <t>Trinity</t>
-  </si>
-  <si>
-    <t>DOS</t>
-  </si>
-  <si>
-    <t>UCD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paul Weaver </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suzanne Fielding </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Doireann O'Kiely and Anthony </t>
-  </si>
-  <si>
-    <t>Week</t>
-  </si>
-  <si>
-    <t>Speaker</t>
-  </si>
-  <si>
-    <t>Taken</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taken </t>
-  </si>
-  <si>
-    <t>Seminar Series AY2024-25 Sem 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contact david.osullivan@ul.ie &amp; mehakpreet.singh@ul.ie to book a speaker in. </t>
-  </si>
-  <si>
-    <t>Deptartmental contact</t>
-  </si>
-  <si>
-    <t>Wednesday</t>
-  </si>
-  <si>
-    <t>Robery Garvey</t>
-  </si>
-  <si>
-    <t>Tentative speaker</t>
-  </si>
-  <si>
-    <t>Leornard Henckel</t>
+    <t>Loops, not groups: Long cycles are responsible for discontinuous phase transitions in higher-order contagions</t>
+  </si>
+  <si>
+    <t>Discontinuous phase transitions are often observed in the outbreak sizes when we have dynamics on higher-order networks. Here, we consider higher-order networks to be networks with groups. In this talk, we consider complex-contagion dynamics on a network with groups of size two and three. We show that just having groups is insufficient to observe a discontinuous phase transition in the outbreak size, and that longer cycles are required to produce this behaviour. This brings us closer to fully understanding why we sometimes see discontinuous phase transitions in dynamics on higher-order networks where we do not in the dyadic versions of the models.</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2511.15688</t>
+  </si>
+  <si>
+    <t>https://www.leahkeating.ie/</t>
   </si>
 </sst>
 </file>
@@ -2507,32 +2519,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7958562-D4BB-4776-9668-682A6F2E2AD0}">
   <dimension ref="A1:Y20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="11.140625" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="24.140625" customWidth="1"/>
-    <col min="8" max="8" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="52.85546875" customWidth="1"/>
-    <col min="10" max="10" width="61" customWidth="1"/>
-    <col min="11" max="11" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="12.5703125" customWidth="1"/>
-    <col min="14" max="14" width="41" customWidth="1"/>
-    <col min="15" max="15" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="36.5703125" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="39" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="28.42578125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="37.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="11.1640625" customWidth="1"/>
+    <col min="5" max="5" width="13.31640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="24.078125" customWidth="1"/>
+    <col min="8" max="8" width="21.1171875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="52.8671875" customWidth="1"/>
+    <col min="10" max="10" width="60.9375" customWidth="1"/>
+    <col min="11" max="11" width="20.58203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="12.5078125" customWidth="1"/>
+    <col min="14" max="14" width="41.02734375" customWidth="1"/>
+    <col min="15" max="15" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="36.58984375" customWidth="1"/>
+    <col min="17" max="17" width="9.68359375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.97265625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.68359375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="18.6953125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="39.01171875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="28.3828125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="26.6328125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="37.80078125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2543,7 +2555,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -2620,7 +2632,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>45317</v>
       </c>
@@ -2687,7 +2699,7 @@
       <c r="X3" s="13"/>
       <c r="Y3" s="13"/>
     </row>
-    <row r="4" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>45323</v>
       </c>
@@ -2750,7 +2762,7 @@
       <c r="X4" s="13"/>
       <c r="Y4" s="13"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>45324</v>
       </c>
@@ -2811,7 +2823,7 @@
       <c r="X5" s="13"/>
       <c r="Y5" s="13"/>
     </row>
-    <row r="6" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>45331</v>
       </c>
@@ -2878,7 +2890,7 @@
       <c r="X6" s="13"/>
       <c r="Y6" s="13"/>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>45338</v>
       </c>
@@ -2947,7 +2959,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>45345</v>
       </c>
@@ -3014,7 +3026,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>45359</v>
       </c>
@@ -3067,7 +3079,7 @@
       <c r="X9" s="13"/>
       <c r="Y9" s="13"/>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>45366</v>
       </c>
@@ -3136,7 +3148,7 @@
       <c r="X10" s="13"/>
       <c r="Y10" s="13"/>
     </row>
-    <row r="11" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>45379</v>
       </c>
@@ -3197,7 +3209,7 @@
       <c r="X11" s="13"/>
       <c r="Y11" s="13"/>
     </row>
-    <row r="12" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>45386</v>
       </c>
@@ -3260,7 +3272,7 @@
       <c r="X12" s="13"/>
       <c r="Y12" s="13"/>
     </row>
-    <row r="13" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>45387</v>
       </c>
@@ -3329,7 +3341,7 @@
       <c r="X13" s="13"/>
       <c r="Y13" s="13"/>
     </row>
-    <row r="14" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>45394</v>
       </c>
@@ -3390,7 +3402,7 @@
       <c r="X14" s="13"/>
       <c r="Y14" s="13"/>
     </row>
-    <row r="15" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>45398</v>
       </c>
@@ -3459,7 +3471,7 @@
       <c r="X15" s="13"/>
       <c r="Y15" s="13"/>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>45401</v>
       </c>
@@ -3522,7 +3534,7 @@
       <c r="X16" s="18"/>
       <c r="Y16" s="18"/>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>45421</v>
       </c>
@@ -3593,7 +3605,7 @@
       <c r="X17" s="18"/>
       <c r="Y17" s="18"/>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A18" s="26">
         <v>45474</v>
       </c>
@@ -3644,7 +3656,7 @@
       <c r="X18" s="18"/>
       <c r="Y18" s="18"/>
     </row>
-    <row r="19" spans="1:25" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:25" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="26">
         <v>45505</v>
       </c>
@@ -3695,7 +3707,7 @@
       <c r="X19" s="18"/>
       <c r="Y19" s="18"/>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A20" s="26"/>
       <c r="B20" s="26"/>
       <c r="C20" s="26"/>
@@ -3737,32 +3749,32 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y44"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="11.140625" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="24.140625" customWidth="1"/>
-    <col min="8" max="8" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="52.85546875" customWidth="1"/>
-    <col min="10" max="10" width="61" customWidth="1"/>
-    <col min="11" max="11" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="12.5703125" customWidth="1"/>
-    <col min="14" max="14" width="41" customWidth="1"/>
-    <col min="15" max="15" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="36.5703125" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="39" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="28.42578125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="37.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="11.1640625" customWidth="1"/>
+    <col min="5" max="5" width="13.31640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="24.078125" customWidth="1"/>
+    <col min="8" max="8" width="21.1171875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="52.8671875" customWidth="1"/>
+    <col min="10" max="10" width="60.9375" customWidth="1"/>
+    <col min="11" max="11" width="20.58203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="12.5078125" customWidth="1"/>
+    <col min="14" max="14" width="41.02734375" customWidth="1"/>
+    <col min="15" max="15" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="36.58984375" customWidth="1"/>
+    <col min="17" max="17" width="9.68359375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.97265625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.68359375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="18.6953125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="39.01171875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="28.3828125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="26.6328125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="37.80078125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3773,7 +3785,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" ht="28.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="145" t="s">
         <v>3</v>
       </c>
@@ -3850,7 +3862,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>45548</v>
       </c>
@@ -3915,7 +3927,7 @@
       <c r="X3" s="46"/>
       <c r="Y3" s="44"/>
     </row>
-    <row r="4" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>45555</v>
       </c>
@@ -3964,7 +3976,7 @@
       <c r="X4" s="15"/>
       <c r="Y4" s="13"/>
     </row>
-    <row r="5" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>45562</v>
       </c>
@@ -4013,7 +4025,7 @@
       <c r="X5" s="15"/>
       <c r="Y5" s="13"/>
     </row>
-    <row r="6" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>45576</v>
       </c>
@@ -4062,7 +4074,7 @@
       <c r="X6" s="15"/>
       <c r="Y6" s="13"/>
     </row>
-    <row r="7" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>45583</v>
       </c>
@@ -4111,7 +4123,7 @@
       <c r="X7" s="15"/>
       <c r="Y7" s="13"/>
     </row>
-    <row r="8" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>45596</v>
       </c>
@@ -4160,7 +4172,7 @@
       <c r="X8" s="15"/>
       <c r="Y8" s="13"/>
     </row>
-    <row r="9" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>45604</v>
       </c>
@@ -4209,7 +4221,7 @@
       <c r="X9" s="15"/>
       <c r="Y9" s="13"/>
     </row>
-    <row r="10" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>45611</v>
       </c>
@@ -4258,7 +4270,7 @@
       <c r="X10" s="15"/>
       <c r="Y10" s="13"/>
     </row>
-    <row r="11" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>45625</v>
       </c>
@@ -4307,7 +4319,7 @@
       <c r="X11" s="15"/>
       <c r="Y11" s="13"/>
     </row>
-    <row r="12" spans="1:25" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>45632</v>
       </c>
@@ -4364,20 +4376,20 @@
       <c r="X12" s="20"/>
       <c r="Y12" s="18"/>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" s="26"/>
       <c r="B13" s="26"/>
       <c r="C13" s="26"/>
       <c r="D13" s="26"/>
       <c r="I13" s="3"/>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A14" s="26"/>
       <c r="B14" s="26"/>
       <c r="C14" s="26"/>
       <c r="D14" s="26"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="61"/>
       <c r="B29" s="61"/>
       <c r="C29" s="61"/>
@@ -4389,59 +4401,59 @@
       <c r="I29" s="61"/>
       <c r="J29" s="61"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" s="60"/>
       <c r="B31" s="60"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" s="60"/>
       <c r="B32" s="60"/>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="60"/>
       <c r="B33" s="60"/>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="60"/>
       <c r="B34" s="60"/>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="60"/>
       <c r="B35" s="60"/>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="60"/>
       <c r="B36" s="60"/>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" s="60"/>
       <c r="B37" s="60"/>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="60"/>
       <c r="B38" s="60"/>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" s="60"/>
       <c r="B39" s="60"/>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="60"/>
       <c r="B40" s="60"/>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" s="60"/>
       <c r="B41" s="60"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" s="60"/>
       <c r="B42" s="60"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" s="60"/>
       <c r="B43" s="60"/>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" s="60"/>
       <c r="B44" s="60"/>
     </row>
@@ -4470,35 +4482,35 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12299A9A-6C0C-4F92-957E-FBFCB6211744}">
   <dimension ref="A1:Y45"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.140625" customWidth="1"/>
-    <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.5703125" customWidth="1"/>
-    <col min="7" max="7" width="30.85546875" customWidth="1"/>
-    <col min="8" max="8" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="31.85546875" customWidth="1"/>
-    <col min="11" max="11" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="12.5703125" customWidth="1"/>
-    <col min="14" max="14" width="43.140625" customWidth="1"/>
-    <col min="15" max="15" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="36.5703125" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="39" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="28.42578125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="37.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5078125" customWidth="1"/>
+    <col min="2" max="2" width="5.91796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.1640625" customWidth="1"/>
+    <col min="4" max="4" width="11.02734375" customWidth="1"/>
+    <col min="5" max="5" width="9.14453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.6171875" customWidth="1"/>
+    <col min="7" max="7" width="30.8046875" customWidth="1"/>
+    <col min="8" max="8" width="21.25390625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="36.58984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="31.87890625" customWidth="1"/>
+    <col min="11" max="11" width="20.58203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="12.5078125" customWidth="1"/>
+    <col min="14" max="14" width="43.1796875" customWidth="1"/>
+    <col min="15" max="15" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="36.58984375" customWidth="1"/>
+    <col min="17" max="17" width="9.68359375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.97265625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="18.6953125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="39.01171875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="28.3828125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="26.6328125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="37.80078125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4509,7 +4521,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="64" t="s">
         <v>3</v>
       </c>
@@ -4586,7 +4598,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>45694</v>
       </c>
@@ -4638,7 +4650,7 @@
       <c r="X3" s="46"/>
       <c r="Y3" s="44"/>
     </row>
-    <row r="4" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>45708</v>
       </c>
@@ -4696,7 +4708,7 @@
       <c r="X4" s="15"/>
       <c r="Y4" s="13"/>
     </row>
-    <row r="5" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>45722</v>
       </c>
@@ -4752,7 +4764,7 @@
       <c r="X5" s="15"/>
       <c r="Y5" s="13"/>
     </row>
-    <row r="6" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>45735</v>
       </c>
@@ -4808,7 +4820,7 @@
       <c r="X6" s="15"/>
       <c r="Y6" s="13"/>
     </row>
-    <row r="7" spans="1:25" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>45750</v>
       </c>
@@ -4862,7 +4874,7 @@
       <c r="X7" s="15"/>
       <c r="Y7" s="13"/>
     </row>
-    <row r="8" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>45751</v>
       </c>
@@ -4921,7 +4933,7 @@
       <c r="X8" s="15"/>
       <c r="Y8" s="13"/>
     </row>
-    <row r="9" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>45757</v>
       </c>
@@ -4983,7 +4995,7 @@
       <c r="X9" s="15"/>
       <c r="Y9" s="13"/>
     </row>
-    <row r="10" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>45758</v>
       </c>
@@ -5037,7 +5049,7 @@
       <c r="X10" s="20"/>
       <c r="Y10" s="18"/>
     </row>
-    <row r="11" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>45764</v>
       </c>
@@ -5097,7 +5109,7 @@
       <c r="X11" s="35"/>
       <c r="Y11" s="35"/>
     </row>
-    <row r="12" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>45771</v>
       </c>
@@ -5158,7 +5170,7 @@
       <c r="X12" s="35"/>
       <c r="Y12" s="35"/>
     </row>
-    <row r="13" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>45785</v>
       </c>
@@ -5211,7 +5223,7 @@
       <c r="X13" s="35"/>
       <c r="Y13" s="35"/>
     </row>
-    <row r="14" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>45799</v>
       </c>
@@ -5257,7 +5269,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>45805</v>
       </c>
@@ -5291,101 +5303,101 @@
         <v>250</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="75"/>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="26"/>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="26"/>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="26"/>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="75"/>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="26"/>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="75"/>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="26"/>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="26"/>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="26"/>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="26"/>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="26"/>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="26"/>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B31" s="60"/>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" s="60"/>
       <c r="B32" s="60"/>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="60"/>
       <c r="B33" s="60"/>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="60"/>
       <c r="B34" s="60"/>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="60"/>
       <c r="B35" s="60"/>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="60"/>
       <c r="B36" s="60"/>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" s="60"/>
       <c r="B37" s="60"/>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="60"/>
       <c r="B38" s="60"/>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" s="60"/>
       <c r="B39" s="60"/>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="60"/>
       <c r="B40" s="60"/>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" s="60"/>
       <c r="B41" s="60"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" s="60"/>
       <c r="B42" s="60"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" s="60"/>
       <c r="B43" s="60"/>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" s="60"/>
       <c r="B44" s="60"/>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" s="60"/>
     </row>
   </sheetData>
@@ -5410,34 +5422,34 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{243C2AD8-98F5-4435-96A3-1C2CAB922825}">
   <dimension ref="A1:Y26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="14.5703125" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="6" max="6" width="33.42578125" customWidth="1"/>
-    <col min="7" max="7" width="30.85546875" customWidth="1"/>
-    <col min="8" max="8" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="31.85546875" customWidth="1"/>
-    <col min="11" max="11" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="12.5703125" customWidth="1"/>
-    <col min="14" max="14" width="43.140625" customWidth="1"/>
-    <col min="15" max="15" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="36.5703125" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="39" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="28.42578125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="37.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.64453125" customWidth="1"/>
+    <col min="2" max="2" width="14.52734375" customWidth="1"/>
+    <col min="3" max="3" width="20.04296875" customWidth="1"/>
+    <col min="4" max="4" width="11.02734375" customWidth="1"/>
+    <col min="6" max="6" width="33.359375" customWidth="1"/>
+    <col min="7" max="7" width="30.8046875" customWidth="1"/>
+    <col min="8" max="8" width="21.25390625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="36.58984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="31.87890625" customWidth="1"/>
+    <col min="11" max="11" width="20.58203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="12.5078125" customWidth="1"/>
+    <col min="14" max="14" width="43.1796875" customWidth="1"/>
+    <col min="15" max="15" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="36.58984375" customWidth="1"/>
+    <col min="17" max="17" width="9.68359375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.97265625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="18.6953125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="39.01171875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="28.3828125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="26.6328125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="37.80078125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5448,7 +5460,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A2" s="78" t="s">
         <v>3</v>
       </c>
@@ -5525,7 +5537,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="159">
         <v>45911</v>
       </c>
@@ -5588,7 +5600,7 @@
       <c r="X3" s="46"/>
       <c r="Y3" s="44"/>
     </row>
-    <row r="4" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="160">
         <v>45917</v>
       </c>
@@ -5657,7 +5669,7 @@
       <c r="X4" s="15"/>
       <c r="Y4" s="13"/>
     </row>
-    <row r="5" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="160">
         <v>45926</v>
       </c>
@@ -5715,7 +5727,7 @@
       <c r="X5" s="15"/>
       <c r="Y5" s="13"/>
     </row>
-    <row r="6" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="160">
         <v>45939</v>
       </c>
@@ -5779,7 +5791,7 @@
       <c r="X6" s="15"/>
       <c r="Y6" s="13"/>
     </row>
-    <row r="7" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="160">
         <v>45946</v>
       </c>
@@ -5836,7 +5848,7 @@
       <c r="X7" s="15"/>
       <c r="Y7" s="13"/>
     </row>
-    <row r="8" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="160">
         <v>45953</v>
       </c>
@@ -5894,7 +5906,7 @@
       <c r="X8" s="15"/>
       <c r="Y8" s="13"/>
     </row>
-    <row r="9" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="160">
         <v>45967</v>
       </c>
@@ -5956,7 +5968,7 @@
       <c r="X9" s="15"/>
       <c r="Y9" s="13"/>
     </row>
-    <row r="10" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="160">
         <v>45974</v>
       </c>
@@ -6019,7 +6031,7 @@
       <c r="X10" s="15"/>
       <c r="Y10" s="13"/>
     </row>
-    <row r="11" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="160">
         <v>45980</v>
       </c>
@@ -6070,7 +6082,7 @@
       <c r="X11" s="35"/>
       <c r="Y11" s="35"/>
     </row>
-    <row r="12" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="160">
         <f>A10+7</f>
         <v>45981</v>
@@ -6123,7 +6135,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" s="160">
         <v>45986</v>
       </c>
@@ -6159,7 +6171,7 @@
       <c r="M13" s="158"/>
       <c r="N13" s="158"/>
     </row>
-    <row r="14" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="160">
         <v>45988</v>
       </c>
@@ -6214,7 +6226,7 @@
       <c r="X14" s="15"/>
       <c r="Y14" s="13"/>
     </row>
-    <row r="15" spans="1:25" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="161">
         <v>45995</v>
       </c>
@@ -6277,35 +6289,35 @@
       <c r="X15" s="15"/>
       <c r="Y15" s="13"/>
     </row>
-    <row r="16" spans="1:25" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:25" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="26"/>
       <c r="B16" s="26"/>
       <c r="C16" s="26"/>
       <c r="X16" s="20"/>
       <c r="Y16" s="18"/>
     </row>
-    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="26"/>
       <c r="B17" s="26"/>
       <c r="C17" s="26"/>
     </row>
-    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="26"/>
       <c r="B18" s="26"/>
       <c r="C18" s="26"/>
     </row>
-    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="26"/>
       <c r="B19" s="26"/>
       <c r="C19" s="26"/>
     </row>
-    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <protectedRanges>
     <protectedRange algorithmName="SHA-512" hashValue="pQyTzP/d7t5ThMimBt5mu8gGozgAm1OwF6BMILsn5/kmtZ5mZf81NMi09wwU8mvtItxf0EVNWa6V4MCa0DKeSQ==" saltValue="NzZBiAQ1yFjat+SeIqh2Uw==" spinCount="100000" sqref="A3:E19" name="Range3_1"/>
@@ -6339,34 +6351,34 @@
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="A1:Y16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" customWidth="1"/>
-    <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" customWidth="1"/>
-    <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="6" max="6" width="33.42578125" customWidth="1"/>
-    <col min="7" max="7" width="30.85546875" customWidth="1"/>
-    <col min="8" max="8" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="31.85546875" customWidth="1"/>
-    <col min="11" max="11" width="20.42578125" customWidth="1"/>
-    <col min="12" max="13" width="12.5703125" customWidth="1"/>
-    <col min="14" max="14" width="43.140625" customWidth="1"/>
-    <col min="15" max="15" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="36.5703125" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="39" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="28.42578125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="37.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5078125" customWidth="1"/>
+    <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.08203125" customWidth="1"/>
+    <col min="4" max="4" width="11.02734375" customWidth="1"/>
+    <col min="6" max="6" width="33.359375" customWidth="1"/>
+    <col min="7" max="7" width="30.8046875" customWidth="1"/>
+    <col min="8" max="8" width="21.25390625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="36.58984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="31.87890625" customWidth="1"/>
+    <col min="11" max="11" width="20.4453125" customWidth="1"/>
+    <col min="12" max="13" width="12.5078125" customWidth="1"/>
+    <col min="14" max="14" width="43.1796875" customWidth="1"/>
+    <col min="15" max="15" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="36.58984375" customWidth="1"/>
+    <col min="17" max="17" width="9.68359375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.97265625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="18.6953125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="39.01171875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="28.3828125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="26.6328125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="37.80078125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6377,7 +6389,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A2" s="64" t="s">
         <v>3</v>
       </c>
@@ -6454,7 +6466,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="75">
         <v>46051</v>
       </c>
@@ -6503,7 +6515,7 @@
       <c r="X3" s="46"/>
       <c r="Y3" s="44"/>
     </row>
-    <row r="4" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="75">
         <f>A3+12</f>
         <v>46063</v>
@@ -6554,7 +6566,7 @@
       <c r="X4" s="15"/>
       <c r="Y4" s="13"/>
     </row>
-    <row r="5" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="75">
         <f>A4+16</f>
         <v>46079</v>
@@ -6609,7 +6621,7 @@
       <c r="X5" s="15"/>
       <c r="Y5" s="13"/>
     </row>
-    <row r="6" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="75">
         <f>A5+14</f>
         <v>46093</v>
@@ -6639,14 +6651,18 @@
         <v>95</v>
       </c>
       <c r="I6" s="98" t="s">
-        <v>342</v>
+        <v>412</v>
       </c>
       <c r="J6" s="98" t="s">
-        <v>342</v>
+        <v>413</v>
       </c>
       <c r="K6" s="102"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
+      <c r="L6" s="24" t="s">
+        <v>414</v>
+      </c>
+      <c r="M6" s="24" t="s">
+        <v>415</v>
+      </c>
       <c r="N6" s="16"/>
       <c r="O6" s="35"/>
       <c r="P6" s="5"/>
@@ -6660,7 +6676,7 @@
       <c r="X6" s="15"/>
       <c r="Y6" s="13"/>
     </row>
-    <row r="7" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="75">
         <f>A6+7</f>
         <v>46100</v>
@@ -6687,19 +6703,19 @@
         <v>101</v>
       </c>
       <c r="I7" s="98" t="s">
+        <v>408</v>
+      </c>
+      <c r="J7" s="98" t="s">
+        <v>409</v>
+      </c>
+      <c r="K7" s="102" t="s">
         <v>344</v>
       </c>
-      <c r="J7" s="98" t="s">
+      <c r="L7" s="24" t="s">
         <v>345</v>
       </c>
-      <c r="K7" s="102" t="s">
+      <c r="M7" s="24" t="s">
         <v>346</v>
-      </c>
-      <c r="L7" s="24" t="s">
-        <v>347</v>
-      </c>
-      <c r="M7" s="24" t="s">
-        <v>348</v>
       </c>
       <c r="N7" s="16"/>
       <c r="O7" s="35"/>
@@ -6714,7 +6730,7 @@
       <c r="X7" s="15"/>
       <c r="Y7" s="13"/>
     </row>
-    <row r="8" spans="1:25" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="75">
         <f>A6+14</f>
         <v>46107</v>
@@ -6735,7 +6751,7 @@
         <v>9</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="G8" s="14" t="s">
         <v>52</v>
@@ -6744,10 +6760,10 @@
         <v>87</v>
       </c>
       <c r="I8" s="98" t="s">
-        <v>350</v>
+        <v>410</v>
       </c>
       <c r="J8" s="98" t="s">
-        <v>351</v>
+        <v>411</v>
       </c>
       <c r="K8" s="102"/>
       <c r="L8" s="5"/>
@@ -6765,7 +6781,7 @@
       <c r="X8" s="15"/>
       <c r="Y8" s="13"/>
     </row>
-    <row r="9" spans="1:25" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="75">
         <f>A8+7</f>
         <v>46114</v>
@@ -6783,28 +6799,28 @@
         <v>10</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>101</v>
       </c>
       <c r="I9" s="98" t="s">
+        <v>350</v>
+      </c>
+      <c r="J9" s="98" t="s">
+        <v>351</v>
+      </c>
+      <c r="K9" s="102" t="s">
+        <v>352</v>
+      </c>
+      <c r="L9" s="24" t="s">
+        <v>353</v>
+      </c>
+      <c r="M9" s="24" t="s">
         <v>354</v>
-      </c>
-      <c r="J9" s="98" t="s">
-        <v>355</v>
-      </c>
-      <c r="K9" s="102" t="s">
-        <v>356</v>
-      </c>
-      <c r="L9" s="24" t="s">
-        <v>357</v>
-      </c>
-      <c r="M9" s="24" t="s">
-        <v>358</v>
       </c>
       <c r="N9" s="16"/>
       <c r="O9" s="35"/>
@@ -6819,7 +6835,7 @@
       <c r="X9" s="15"/>
       <c r="Y9" s="13"/>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="75">
         <v>46120</v>
       </c>
@@ -6838,7 +6854,7 @@
         <v>11</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="G10" s="14" t="s">
         <v>77</v>
@@ -6868,7 +6884,7 @@
       <c r="X10" s="15"/>
       <c r="Y10" s="13"/>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="75">
         <f>A10+7</f>
         <v>46127</v>
@@ -6888,7 +6904,7 @@
         <v>12</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="G11" s="14" t="s">
         <v>195</v>
@@ -6903,11 +6919,11 @@
         <v>342</v>
       </c>
       <c r="K11" s="102" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="L11" s="5"/>
       <c r="M11" s="24" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="N11" s="16"/>
       <c r="O11" s="35"/>
@@ -6922,7 +6938,7 @@
       <c r="X11" s="15"/>
       <c r="Y11" s="13"/>
     </row>
-    <row r="12" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="75">
         <v>46135</v>
       </c>
@@ -6939,7 +6955,7 @@
         <v>13</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="G12" s="14" t="s">
         <v>73</v>
@@ -6969,24 +6985,24 @@
       <c r="X12" s="15"/>
       <c r="Y12" s="13"/>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" s="26"/>
       <c r="B13" s="26"/>
       <c r="C13" s="26"/>
       <c r="X13" s="20"/>
       <c r="Y13" s="18"/>
     </row>
-    <row r="14" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="26"/>
       <c r="B14" s="26"/>
       <c r="C14" s="26"/>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A15" s="26"/>
       <c r="B15" s="26"/>
       <c r="C15" s="26"/>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A16" s="26"/>
       <c r="B16" s="26"/>
       <c r="C16" s="26"/>
@@ -7009,6 +7025,8 @@
     <hyperlink ref="K7" r:id="rId6" xr:uid="{EEDAB9A6-23C2-44A6-AE32-27763DA4A1D2}"/>
     <hyperlink ref="M7" r:id="rId7" xr:uid="{60F7675F-B0A2-4588-8DBC-226BD313FA08}"/>
     <hyperlink ref="L7" r:id="rId8" xr:uid="{B5519C91-F3AF-4FFA-92F0-015F0993FEC9}"/>
+    <hyperlink ref="L6" r:id="rId9" xr:uid="{E20CE4D9-AFC3-FE4E-8238-9CE8FB74EA4B}"/>
+    <hyperlink ref="M6" r:id="rId10" xr:uid="{6053315A-23DA-DA4E-9447-0140277816C3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7017,34 +7035,34 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A33E49C-EC2E-42B7-80E4-DD607C0B7A89}">
   <dimension ref="A1:Y13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" customWidth="1"/>
-    <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" customWidth="1"/>
-    <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="6" max="6" width="33.42578125" customWidth="1"/>
-    <col min="7" max="7" width="30.85546875" customWidth="1"/>
-    <col min="8" max="8" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="31.85546875" customWidth="1"/>
-    <col min="11" max="11" width="20.42578125" customWidth="1"/>
-    <col min="12" max="13" width="12.5703125" customWidth="1"/>
-    <col min="14" max="14" width="43.140625" customWidth="1"/>
-    <col min="15" max="15" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="36.5703125" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="39" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="28.42578125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="37.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5078125" customWidth="1"/>
+    <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.08203125" customWidth="1"/>
+    <col min="4" max="4" width="11.02734375" customWidth="1"/>
+    <col min="6" max="6" width="33.359375" customWidth="1"/>
+    <col min="7" max="7" width="30.8046875" customWidth="1"/>
+    <col min="8" max="8" width="21.25390625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="36.58984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="31.87890625" customWidth="1"/>
+    <col min="11" max="11" width="20.4453125" customWidth="1"/>
+    <col min="12" max="13" width="12.5078125" customWidth="1"/>
+    <col min="14" max="14" width="43.1796875" customWidth="1"/>
+    <col min="15" max="15" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="36.58984375" customWidth="1"/>
+    <col min="17" max="17" width="9.68359375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.97265625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="18.6953125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="39.01171875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="28.3828125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="26.6328125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="37.80078125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7055,7 +7073,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" ht="28.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="64" t="s">
         <v>3</v>
       </c>
@@ -7132,7 +7150,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="75">
         <v>46275</v>
       </c>
@@ -7151,7 +7169,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="G3" s="14" t="s">
         <v>342</v>
@@ -7181,7 +7199,7 @@
       <c r="X3" s="46"/>
       <c r="Y3" s="44"/>
     </row>
-    <row r="4" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="75">
         <f>A3+14</f>
         <v>46289</v>
@@ -7202,7 +7220,7 @@
         <v>3</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="G4" s="14" t="s">
         <v>342</v>
@@ -7232,7 +7250,7 @@
       <c r="X4" s="15"/>
       <c r="Y4" s="13"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="75">
         <f t="shared" ref="A5" si="2">A4+14</f>
         <v>46303</v>
@@ -7253,7 +7271,7 @@
         <v>5</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="G5" s="14" t="s">
         <v>342</v>
@@ -7287,7 +7305,7 @@
       <c r="X5" s="15"/>
       <c r="Y5" s="13"/>
     </row>
-    <row r="6" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="75">
         <f>A5+14</f>
         <v>46317</v>
@@ -7308,7 +7326,7 @@
         <v>7</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="G6" s="14" t="s">
         <v>342</v>
@@ -7338,7 +7356,7 @@
       <c r="X6" s="15"/>
       <c r="Y6" s="13"/>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="75">
         <f>A6+14</f>
         <v>46331</v>
@@ -7359,7 +7377,7 @@
         <v>9</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="G7" s="14" t="s">
         <v>342</v>
@@ -7389,7 +7407,7 @@
       <c r="X7" s="15"/>
       <c r="Y7" s="13"/>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="75">
         <f>A7+14</f>
         <v>46345</v>
@@ -7408,7 +7426,7 @@
         <v>11</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="G8" s="14" t="s">
         <v>342</v>
@@ -7438,7 +7456,7 @@
       <c r="X8" s="15"/>
       <c r="Y8" s="13"/>
     </row>
-    <row r="9" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="75">
         <v>46121</v>
       </c>
@@ -7446,7 +7464,7 @@
         <v>190</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="D9" s="27" t="s">
         <v>278</v>
@@ -7455,7 +7473,7 @@
         <v>13</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="G9" s="14" t="s">
         <v>342</v>
@@ -7485,24 +7503,24 @@
       <c r="X9" s="15"/>
       <c r="Y9" s="13"/>
     </row>
-    <row r="10" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="26"/>
       <c r="B10" s="26"/>
       <c r="C10" s="26"/>
       <c r="X10" s="20"/>
       <c r="Y10" s="18"/>
     </row>
-    <row r="11" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="26"/>
       <c r="B11" s="26"/>
       <c r="C11" s="26"/>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" s="26"/>
       <c r="B12" s="26"/>
       <c r="C12" s="26"/>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" s="26"/>
       <c r="B13" s="26"/>
       <c r="C13" s="26"/>
@@ -7524,204 +7542,204 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AEC079F-155A-491D-9189-1418FC903287}">
   <dimension ref="A1:C19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="31.28515625" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="20.140625" customWidth="1"/>
+    <col min="1" max="1" width="31.34375" customWidth="1"/>
+    <col min="2" max="2" width="25.9609375" customWidth="1"/>
+    <col min="3" max="3" width="20.17578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="55" t="s">
+        <v>363</v>
+      </c>
+      <c r="B2" s="54" t="s">
+        <v>364</v>
+      </c>
+      <c r="C2" s="54" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="136" t="s">
         <v>366</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="55" t="s">
-        <v>367</v>
-      </c>
-      <c r="B2" s="54" t="s">
-        <v>368</v>
-      </c>
-      <c r="C2" s="54" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="136" t="s">
-        <v>370</v>
       </c>
       <c r="B3" s="137"/>
       <c r="C3" s="138" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="B4" s="52"/>
       <c r="C4" s="50" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="52" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="B5" s="52"/>
       <c r="C5" s="50" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="52" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="B6" s="52" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C6" s="50" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="52" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="B7" s="52" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="C7" s="50" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="52" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="B8" s="52" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C8" s="50" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="52" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="B9" s="52"/>
       <c r="C9" s="50"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="52" t="s">
+        <v>377</v>
+      </c>
+      <c r="B10" s="52" t="s">
+        <v>378</v>
+      </c>
+      <c r="C10" s="50" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="52" t="s">
+        <v>380</v>
+      </c>
+      <c r="B11" s="52" t="s">
         <v>381</v>
       </c>
-      <c r="B10" s="52" t="s">
+      <c r="C11" s="50" t="s">
         <v>382</v>
       </c>
-      <c r="C10" s="50" t="s">
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="52" t="s">
         <v>383</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="52" t="s">
+      <c r="B12" s="52" t="s">
         <v>384</v>
       </c>
-      <c r="B11" s="52" t="s">
+      <c r="C12" s="50" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="52" t="s">
         <v>385</v>
       </c>
-      <c r="C11" s="50" t="s">
+      <c r="B13" s="52" t="s">
         <v>386</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="52" t="s">
+      <c r="C13" s="50" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="52" t="s">
         <v>387</v>
       </c>
-      <c r="B12" s="52" t="s">
+      <c r="B14" s="52" t="s">
         <v>388</v>
       </c>
-      <c r="C12" s="50" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="52" t="s">
+      <c r="C14" s="50" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="52" t="s">
         <v>389</v>
       </c>
-      <c r="B13" s="52" t="s">
+      <c r="B15" s="52" t="s">
         <v>390</v>
       </c>
-      <c r="C13" s="50" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="52" t="s">
-        <v>391</v>
-      </c>
-      <c r="B14" s="52" t="s">
-        <v>392</v>
-      </c>
-      <c r="C14" s="50" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="52" t="s">
-        <v>393</v>
-      </c>
-      <c r="B15" s="52" t="s">
-        <v>394</v>
-      </c>
       <c r="C15" s="50" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="137" t="s">
         <v>321</v>
       </c>
       <c r="B16" s="137" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="C16" s="139" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="137" t="s">
         <v>343</v>
       </c>
       <c r="B17" s="137" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="C17" s="139" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="52" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B18" s="52" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C18" s="50" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="53" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="B19" s="53" t="s">
         <v>230</v>
       </c>
       <c r="C19" s="51" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
     </row>
   </sheetData>
@@ -7737,24 +7755,24 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AD19DE5-C22F-4D41-B540-76D70438E18B}">
   <dimension ref="A1:I16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.85546875" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" customWidth="1"/>
+    <col min="1" max="1" width="17.890625" customWidth="1"/>
+    <col min="6" max="6" width="14.52734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="135" t="s">
         <v>3</v>
       </c>
       <c r="B1" s="131" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C1" s="130" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="169">
         <v>46051</v>
       </c>
@@ -7762,14 +7780,14 @@
         <v>1</v>
       </c>
       <c r="C2" s="170" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="F2" s="75"/>
       <c r="G2" s="77"/>
       <c r="H2" s="29"/>
       <c r="I2" s="55"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="171">
         <f>A2+7</f>
         <v>46058</v>
@@ -7779,14 +7797,14 @@
         <v>2</v>
       </c>
       <c r="C3" s="170" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="F3" s="75"/>
       <c r="G3" s="2"/>
       <c r="H3" s="26"/>
       <c r="I3" s="27"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="171">
         <f t="shared" ref="A4:A12" si="0">A3+7</f>
         <v>46065</v>
@@ -7796,14 +7814,14 @@
         <v>3</v>
       </c>
       <c r="C4" s="170" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="F4" s="75"/>
       <c r="G4" s="2"/>
       <c r="H4" s="26"/>
       <c r="I4" s="27"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="171">
         <f t="shared" si="0"/>
         <v>46072</v>
@@ -7813,14 +7831,14 @@
         <v>4</v>
       </c>
       <c r="C5" s="170" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="F5" s="75"/>
       <c r="G5" s="2"/>
       <c r="H5" s="26"/>
       <c r="I5" s="27"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="133">
         <f t="shared" si="0"/>
         <v>46079</v>
@@ -7830,14 +7848,14 @@
         <v>5</v>
       </c>
       <c r="C6" s="134" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="F6" s="75"/>
       <c r="G6" s="2"/>
       <c r="H6" s="26"/>
       <c r="I6" s="27"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="133">
         <f t="shared" si="0"/>
         <v>46086</v>
@@ -7847,14 +7865,14 @@
         <v>6</v>
       </c>
       <c r="C7" s="134" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="F7" s="75"/>
       <c r="G7" s="2"/>
       <c r="H7" s="26"/>
       <c r="I7" s="27"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="133">
         <f t="shared" si="0"/>
         <v>46093</v>
@@ -7864,14 +7882,14 @@
         <v>7</v>
       </c>
       <c r="C8" s="134" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="F8" s="75"/>
       <c r="G8" s="2"/>
       <c r="H8" s="26"/>
       <c r="I8" s="27"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="133">
         <f t="shared" si="0"/>
         <v>46100</v>
@@ -7881,14 +7899,14 @@
         <v>8</v>
       </c>
       <c r="C9" s="134" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="F9" s="75"/>
       <c r="G9" s="2"/>
       <c r="H9" s="26"/>
       <c r="I9" s="27"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="133">
         <f t="shared" si="0"/>
         <v>46107</v>
@@ -7898,14 +7916,14 @@
         <v>9</v>
       </c>
       <c r="C10" s="134" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="F10" s="75"/>
       <c r="G10" s="2"/>
       <c r="H10" s="26"/>
       <c r="I10" s="27"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="133">
         <f t="shared" si="0"/>
         <v>46114</v>
@@ -7915,10 +7933,10 @@
         <v>10</v>
       </c>
       <c r="C11" s="134" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="133">
         <f t="shared" si="0"/>
         <v>46121</v>
@@ -7928,10 +7946,10 @@
         <v>11</v>
       </c>
       <c r="C12" s="134" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="133">
         <f t="shared" ref="A13:A14" si="3">A12+7</f>
         <v>46128</v>
@@ -7941,10 +7959,10 @@
         <v>12</v>
       </c>
       <c r="C13" s="134" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="133">
         <f t="shared" si="3"/>
         <v>46135</v>
@@ -7954,15 +7972,15 @@
         <v>13</v>
       </c>
       <c r="C14" s="134" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="133"/>
       <c r="B15" s="134"/>
       <c r="C15" s="134"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G16" s="26"/>
     </row>
   </sheetData>
@@ -7989,29 +8007,29 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2BB5C5F-5790-4A91-A6E8-8841719DA1FC}">
   <dimension ref="A2:I20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" customWidth="1"/>
-    <col min="4" max="4" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.7109375" customWidth="1"/>
-    <col min="7" max="7" width="38.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.42578125" customWidth="1"/>
-    <col min="9" max="9" width="64.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.41015625" customWidth="1"/>
+    <col min="2" max="2" width="9.14453125" customWidth="1"/>
+    <col min="3" max="3" width="14.66015625" customWidth="1"/>
+    <col min="4" max="4" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.75" customWidth="1"/>
+    <col min="7" max="7" width="38.203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.46484375" customWidth="1"/>
+    <col min="9" max="9" width="64.703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A2" s="91" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A3" s="79" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="37.5" x14ac:dyDescent="0.25">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="35.25" x14ac:dyDescent="0.25">
       <c r="A5" s="80" t="s">
         <v>3</v>
       </c>
@@ -8034,13 +8052,13 @@
         <v>9</v>
       </c>
       <c r="H5" s="82" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="I5" s="81" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A6" s="92">
         <v>45694</v>
       </c>
@@ -8067,7 +8085,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A7" s="83">
         <v>45708</v>
       </c>
@@ -8096,7 +8114,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A8" s="83">
         <v>45722</v>
       </c>
@@ -8123,7 +8141,7 @@
       </c>
       <c r="I8" s="86"/>
     </row>
-    <row r="9" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A9" s="83">
         <v>45735</v>
       </c>
@@ -8134,7 +8152,7 @@
         <v>198</v>
       </c>
       <c r="D9" s="94" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="E9" s="94">
         <v>8</v>
@@ -8152,7 +8170,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A10" s="83">
         <v>45744</v>
       </c>
@@ -8179,7 +8197,7 @@
       </c>
       <c r="I10" s="86"/>
     </row>
-    <row r="11" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A11" s="83">
         <v>45750</v>
       </c>
@@ -8196,7 +8214,7 @@
         <v>10</v>
       </c>
       <c r="F11" s="87" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="G11" s="87" t="s">
         <v>68</v>
@@ -8206,7 +8224,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A12" s="83">
         <v>45758</v>
       </c>
@@ -8235,7 +8253,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A13" s="83">
         <v>45764</v>
       </c>
@@ -8252,13 +8270,13 @@
         <v>12</v>
       </c>
       <c r="F13" s="87" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G13" s="87"/>
       <c r="H13" s="87"/>
       <c r="I13" s="86"/>
     </row>
-    <row r="14" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A14" s="88">
         <v>45771</v>
       </c>
@@ -8275,7 +8293,7 @@
         <v>13</v>
       </c>
       <c r="F14" s="90" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="G14" s="90" t="s">
         <v>77</v>
@@ -8287,7 +8305,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="20" spans="8:8" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="20" spans="8:8" ht="18.75" x14ac:dyDescent="0.25">
       <c r="H20" s="79"/>
     </row>
   </sheetData>

--- a/data/MACSI seminar series.xlsx
+++ b/data/MACSI seminar series.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29912"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ulcampus-my.sharepoint.com/personal/david_osullivan_ul_ie/Documents/Academic_work/_Misc/MACSI Seminars/macsi-seminars.github.io/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="337" documentId="13_ncr:1_{12BE53B5-C8C7-44FE-8280-19C653D9122E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF5AA23A-AA63-F64E-AC91-E809D4E886F6}"/>
+  <xr:revisionPtr revIDLastSave="356" documentId="13_ncr:1_{12BE53B5-C8C7-44FE-8280-19C653D9122E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1BFF16E0-978C-40A1-BCB6-463F79566EF9}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1019" uniqueCount="420">
   <si>
     <t>Fill in as much of the green boxes as possible. Ideally, this would be before you have finished your visitors travel dates (just to avoid double booking).</t>
   </si>
@@ -1135,46 +1135,76 @@
     <t>Leah Keating</t>
   </si>
   <si>
+    <t>Loops, not groups: Long cycles are responsible for discontinuous phase transitions in higher-order contagions</t>
+  </si>
+  <si>
+    <t>Discontinuous phase transitions are often observed in the outbreak sizes when we have dynamics on higher-order networks. Here, we consider higher-order networks to be networks with groups. In this talk, we consider complex-contagion dynamics on a network with groups of size two and three. We show that just having groups is insufficient to observe a discontinuous phase transition in the outbreak size, and that longer cycles are required to produce this behaviour. This brings us closer to fully understanding why we sometimes see discontinuous phase transitions in dynamics on higher-order networks where we do not in the dyadic versions of the models.</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2511.15688</t>
+  </si>
+  <si>
+    <t>https://www.leahkeating.ie/</t>
+  </si>
+  <si>
+    <t>Catherine Higgins</t>
+  </si>
+  <si>
+    <t>Novel approaches for clustering gene expression profiles in temporal and spatial transcriptomics</t>
+  </si>
+  <si>
+    <t>Functional clustering methods group curves without prior knowledge of the underlying clustering structure. A key challenge is class imbalance,where some clusters are significantly larger than others. This leads to smaller clusters being misclassified into larger clusters, resulting in a poor clustering accuracy. While class imbalance is well-studied in supervised classification, it has received limited attention in unsupervised settings.  To address this, we introduce functional iterative hierarchical clustering (funIHC), a novel method for clustering imbalanced one-dimensional functional data.  We demonstrate the effectiveness of funIHC against sixteen leading alternatives.  We extend this methodology to two-dimensional functional data with spatial transcriptomics IHC (stIHC), focusing on clustering spatially variable genes into modules that reflect shared spatial expression patterns. We demonstrate that stIHC outperforms existing clustering methods in spatial transcriptomics. Gene ontology enrichment analysis confirms that both funIHC and stIHC identify biologically coherent and distinct clusters, demonstrating their utility for meaningful clustering in both time and space.</t>
+  </si>
+  <si>
+    <t>https://scholar.google.com/citations?user=ikeLYIMAAAAJ&amp;hl=en</t>
+  </si>
+  <si>
+    <t>https://link.springer.com/article/10.1007/s11634-024-00611-8 ; https://onlinelibrary.wiley.com/doi/10.1002/qub2.70011</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/catherine-higgins-4b5hg/</t>
+  </si>
+  <si>
+    <t>Stuart Thomson</t>
+  </si>
+  <si>
+    <t>Driven interfacial hydrodynamics, and some physics-informed machine learning</t>
+  </si>
+  <si>
+    <t>In this talk I will present a few topics of recent interest that centre around the theme of “driven interfacial hydrodynamics”: fluid mechanical systems in which droplets and particles are self-propelled through interaction with the environment. I will also present some very recent work on using differentiable physics (a branch of physics-informed machine learning) to determine constitutive relations for highly plasticised metals.</t>
+  </si>
+  <si>
+    <t>Yes already booked</t>
+  </si>
+  <si>
+    <t>Cornelius Fritz</t>
+  </si>
+  <si>
+    <t>Trinity college Dublin</t>
+  </si>
+  <si>
+    <t>Scalable Durational Event Models: Application to Physical and Digital Interactions</t>
+  </si>
+  <si>
+    <t>Durable interactions are ubiquitous in social network analysis and are increasingly observed with precise time stamps. Phone and video calls, for example, are events to which a specific duration can be assigned. We term data encoding interactions with the start and end times “durational event data”. Recent advances in data collection have enabled the observation of such data over extended periods of time and between large populations of actors. Methodologically, we propose the Durational Event Model, an extension of Relational Event Models that decouples the modeling of event incidence from event duration. Computationally, we derive a fast, memory-efficient, and exact block-coordinate ascent algorithm to facilitate large-scale inference. Theoretical complexity analysis and numerical simulations demonstrate computational superiority of this approach over state-of-the-art methods. We apply the model to physical and digital interactions among college students in Copenhagen.  Our empirical findings reveal that past interactions drive physical interactions, whereas digital interactions are influenced predominantly by friendship ties and prior dyadic contact. </t>
+  </si>
+  <si>
+    <t>https://scholar.google.de/citations?user=0X7D4mwAAAAJ&amp;hl=en</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://arxiv.org/abs/2504.00049 </t>
+  </si>
+  <si>
+    <t>https://www.tcd.ie/scss/people/academic-staff/fritzc/ ; https://www.corneliusfritz.com/about/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chris Howland </t>
+  </si>
+  <si>
     <t>TBC</t>
   </si>
   <si>
-    <t>Catherine Higgins</t>
-  </si>
-  <si>
-    <t>https://scholar.google.com/citations?user=ikeLYIMAAAAJ&amp;hl=en</t>
-  </si>
-  <si>
-    <t>https://link.springer.com/article/10.1007/s11634-024-00611-8 ; https://onlinelibrary.wiley.com/doi/10.1002/qub2.70011</t>
-  </si>
-  <si>
-    <t>https://www.linkedin.com/in/catherine-higgins-4b5hg/</t>
-  </si>
-  <si>
-    <t>Stuart Thomson</t>
-  </si>
-  <si>
-    <t>Cornelius Fritz</t>
-  </si>
-  <si>
-    <t>Trinity college Dublin</t>
-  </si>
-  <si>
-    <t>Scalable Durational Event Models: Application to Physical and Digital Interactions</t>
-  </si>
-  <si>
-    <t>Durable interactions are ubiquitous in social network analysis and are increasingly observed with precise time stamps. Phone and video calls, for example, are events to which a specific duration can be assigned. We term data encoding interactions with the start and end times “durational event data”. Recent advances in data collection have enabled the observation of such data over extended periods of time and between large populations of actors. Methodologically, we propose the Durational Event Model, an extension of Relational Event Models that decouples the modeling of event incidence from event duration. Computationally, we derive a fast, memory-efficient, and exact block-coordinate ascent algorithm to facilitate large-scale inference. Theoretical complexity analysis and numerical simulations demonstrate computational superiority of this approach over state-of-the-art methods. We apply the model to physical and digital interactions among college students in Copenhagen.  Our empirical findings reveal that past interactions drive physical interactions, whereas digital interactions are influenced predominantly by friendship ties and prior dyadic contact. </t>
-  </si>
-  <si>
-    <t>https://scholar.google.de/citations?user=0X7D4mwAAAAJ&amp;hl=en</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://arxiv.org/abs/2504.00049 </t>
-  </si>
-  <si>
-    <t>https://www.tcd.ie/scss/people/academic-staff/fritzc/ ; https://www.corneliusfritz.com/about/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chris Howland </t>
+    <t>Michel Destrade</t>
   </si>
   <si>
     <t>Carl Scarrott</t>
@@ -1300,6 +1330,12 @@
     <t xml:space="preserve">Doireann O'Kiely and Anthony </t>
   </si>
   <si>
+    <t>Hassan Alkhayuon</t>
+  </si>
+  <si>
+    <t>UCC</t>
+  </si>
+  <si>
     <t>Week</t>
   </si>
   <si>
@@ -1331,30 +1367,6 @@
   </si>
   <si>
     <t>Leornard Henckel</t>
-  </si>
-  <si>
-    <t>Novel approaches for clustering gene expression profiles in temporal and spatial transcriptomics</t>
-  </si>
-  <si>
-    <t>Functional clustering methods group curves without prior knowledge of the underlying clustering structure. A key challenge is class imbalance,where some clusters are significantly larger than others. This leads to smaller clusters being misclassified into larger clusters, resulting in a poor clustering accuracy. While class imbalance is well-studied in supervised classification, it has received limited attention in unsupervised settings.  To address this, we introduce functional iterative hierarchical clustering (funIHC), a novel method for clustering imbalanced one-dimensional functional data.  We demonstrate the effectiveness of funIHC against sixteen leading alternatives.  We extend this methodology to two-dimensional functional data with spatial transcriptomics IHC (stIHC), focusing on clustering spatially variable genes into modules that reflect shared spatial expression patterns. We demonstrate that stIHC outperforms existing clustering methods in spatial transcriptomics. Gene ontology enrichment analysis confirms that both funIHC and stIHC identify biologically coherent and distinct clusters, demonstrating their utility for meaningful clustering in both time and space.</t>
-  </si>
-  <si>
-    <t>Driven interfacial hydrodynamics, and some physics-informed machine learning</t>
-  </si>
-  <si>
-    <t>In this talk I will present a few topics of recent interest that centre around the theme of “driven interfacial hydrodynamics”: fluid mechanical systems in which droplets and particles are self-propelled through interaction with the environment. I will also present some very recent work on using differentiable physics (a branch of physics-informed machine learning) to determine constitutive relations for highly plasticised metals.</t>
-  </si>
-  <si>
-    <t>Loops, not groups: Long cycles are responsible for discontinuous phase transitions in higher-order contagions</t>
-  </si>
-  <si>
-    <t>Discontinuous phase transitions are often observed in the outbreak sizes when we have dynamics on higher-order networks. Here, we consider higher-order networks to be networks with groups. In this talk, we consider complex-contagion dynamics on a network with groups of size two and three. We show that just having groups is insufficient to observe a discontinuous phase transition in the outbreak size, and that longer cycles are required to produce this behaviour. This brings us closer to fully understanding why we sometimes see discontinuous phase transitions in dynamics on higher-order networks where we do not in the dyadic versions of the models.</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/abs/2511.15688</t>
-  </si>
-  <si>
-    <t>https://www.leahkeating.ie/</t>
   </si>
 </sst>
 </file>
@@ -1364,7 +1376,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2222,9 +2234,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2262,7 +2274,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2368,7 +2380,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2510,7 +2522,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2519,32 +2531,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7958562-D4BB-4776-9668-682A6F2E2AD0}">
   <dimension ref="A1:Y20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="11.1640625" customWidth="1"/>
-    <col min="5" max="5" width="13.31640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="24.078125" customWidth="1"/>
-    <col min="8" max="8" width="21.1171875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="52.8671875" customWidth="1"/>
-    <col min="10" max="10" width="60.9375" customWidth="1"/>
-    <col min="11" max="11" width="20.58203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="12.5078125" customWidth="1"/>
-    <col min="14" max="14" width="41.02734375" customWidth="1"/>
-    <col min="15" max="15" width="19.7734375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="36.58984375" customWidth="1"/>
-    <col min="17" max="17" width="9.68359375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.97265625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.68359375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="18.6953125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="39.01171875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="28.3828125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="26.6328125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="37.80078125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="11.140625" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="24.140625" customWidth="1"/>
+    <col min="8" max="8" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="52.85546875" customWidth="1"/>
+    <col min="10" max="10" width="61" customWidth="1"/>
+    <col min="11" max="11" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="12.5703125" customWidth="1"/>
+    <col min="14" max="14" width="41" customWidth="1"/>
+    <col min="15" max="15" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="36.5703125" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="39" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="37.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2555,7 +2567,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25" ht="27.75">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -2632,7 +2644,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25" ht="13.5" customHeight="1">
       <c r="A3" s="2">
         <v>45317</v>
       </c>
@@ -2699,7 +2711,7 @@
       <c r="X3" s="13"/>
       <c r="Y3" s="13"/>
     </row>
-    <row r="4" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25" ht="13.5" customHeight="1">
       <c r="A4" s="2">
         <v>45323</v>
       </c>
@@ -2762,7 +2774,7 @@
       <c r="X4" s="13"/>
       <c r="Y4" s="13"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="2">
         <v>45324</v>
       </c>
@@ -2823,7 +2835,7 @@
       <c r="X5" s="13"/>
       <c r="Y5" s="13"/>
     </row>
-    <row r="6" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" ht="12.75" customHeight="1">
       <c r="A6" s="2">
         <v>45331</v>
       </c>
@@ -2890,7 +2902,7 @@
       <c r="X6" s="13"/>
       <c r="Y6" s="13"/>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="2">
         <v>45338</v>
       </c>
@@ -2959,7 +2971,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" ht="15" customHeight="1">
       <c r="A8" s="2">
         <v>45345</v>
       </c>
@@ -3026,7 +3038,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" ht="16.5" customHeight="1">
       <c r="A9" s="2">
         <v>45359</v>
       </c>
@@ -3079,7 +3091,7 @@
       <c r="X9" s="13"/>
       <c r="Y9" s="13"/>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25">
       <c r="A10" s="2">
         <v>45366</v>
       </c>
@@ -3148,7 +3160,7 @@
       <c r="X10" s="13"/>
       <c r="Y10" s="13"/>
     </row>
-    <row r="11" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" ht="15" customHeight="1">
       <c r="A11" s="2">
         <v>45379</v>
       </c>
@@ -3209,7 +3221,7 @@
       <c r="X11" s="13"/>
       <c r="Y11" s="13"/>
     </row>
-    <row r="12" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25" ht="13.5" customHeight="1">
       <c r="A12" s="2">
         <v>45386</v>
       </c>
@@ -3272,7 +3284,7 @@
       <c r="X12" s="13"/>
       <c r="Y12" s="13"/>
     </row>
-    <row r="13" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25" ht="16.5" customHeight="1">
       <c r="A13" s="2">
         <v>45387</v>
       </c>
@@ -3341,7 +3353,7 @@
       <c r="X13" s="13"/>
       <c r="Y13" s="13"/>
     </row>
-    <row r="14" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25" ht="15.75" customHeight="1">
       <c r="A14" s="2">
         <v>45394</v>
       </c>
@@ -3402,7 +3414,7 @@
       <c r="X14" s="13"/>
       <c r="Y14" s="13"/>
     </row>
-    <row r="15" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25" ht="17.25" customHeight="1">
       <c r="A15" s="2">
         <v>45398</v>
       </c>
@@ -3471,7 +3483,7 @@
       <c r="X15" s="13"/>
       <c r="Y15" s="13"/>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25">
       <c r="A16" s="2">
         <v>45401</v>
       </c>
@@ -3534,7 +3546,7 @@
       <c r="X16" s="18"/>
       <c r="Y16" s="18"/>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:25">
       <c r="A17" s="4">
         <v>45421</v>
       </c>
@@ -3605,7 +3617,7 @@
       <c r="X17" s="18"/>
       <c r="Y17" s="18"/>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:25">
       <c r="A18" s="26">
         <v>45474</v>
       </c>
@@ -3656,7 +3668,7 @@
       <c r="X18" s="18"/>
       <c r="Y18" s="18"/>
     </row>
-    <row r="19" spans="1:25" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" ht="17.25" customHeight="1" thickBot="1">
       <c r="A19" s="26">
         <v>45505</v>
       </c>
@@ -3707,7 +3719,7 @@
       <c r="X19" s="18"/>
       <c r="Y19" s="18"/>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:25">
       <c r="A20" s="26"/>
       <c r="B20" s="26"/>
       <c r="C20" s="26"/>
@@ -3749,32 +3761,32 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y44"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="11.1640625" customWidth="1"/>
-    <col min="5" max="5" width="13.31640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="24.078125" customWidth="1"/>
-    <col min="8" max="8" width="21.1171875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="52.8671875" customWidth="1"/>
-    <col min="10" max="10" width="60.9375" customWidth="1"/>
-    <col min="11" max="11" width="20.58203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="12.5078125" customWidth="1"/>
-    <col min="14" max="14" width="41.02734375" customWidth="1"/>
-    <col min="15" max="15" width="19.7734375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="36.58984375" customWidth="1"/>
-    <col min="17" max="17" width="9.68359375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.97265625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.68359375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="18.6953125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="39.01171875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="28.3828125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="26.6328125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="37.80078125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="11.140625" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="24.140625" customWidth="1"/>
+    <col min="8" max="8" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="52.85546875" customWidth="1"/>
+    <col min="10" max="10" width="61" customWidth="1"/>
+    <col min="11" max="11" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="12.5703125" customWidth="1"/>
+    <col min="14" max="14" width="41" customWidth="1"/>
+    <col min="15" max="15" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="36.5703125" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="39" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="37.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3785,7 +3797,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="28.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" ht="28.5" thickBot="1">
       <c r="A2" s="145" t="s">
         <v>3</v>
       </c>
@@ -3862,7 +3874,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25" ht="15" customHeight="1">
       <c r="A3" s="2">
         <v>45548</v>
       </c>
@@ -3927,7 +3939,7 @@
       <c r="X3" s="46"/>
       <c r="Y3" s="44"/>
     </row>
-    <row r="4" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25" ht="15" customHeight="1">
       <c r="A4" s="2">
         <v>45555</v>
       </c>
@@ -3976,7 +3988,7 @@
       <c r="X4" s="15"/>
       <c r="Y4" s="13"/>
     </row>
-    <row r="5" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" ht="15" customHeight="1">
       <c r="A5" s="2">
         <v>45562</v>
       </c>
@@ -4025,7 +4037,7 @@
       <c r="X5" s="15"/>
       <c r="Y5" s="13"/>
     </row>
-    <row r="6" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" ht="15" customHeight="1">
       <c r="A6" s="2">
         <v>45576</v>
       </c>
@@ -4074,7 +4086,7 @@
       <c r="X6" s="15"/>
       <c r="Y6" s="13"/>
     </row>
-    <row r="7" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" ht="15" customHeight="1">
       <c r="A7" s="2">
         <v>45583</v>
       </c>
@@ -4123,7 +4135,7 @@
       <c r="X7" s="15"/>
       <c r="Y7" s="13"/>
     </row>
-    <row r="8" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" ht="15" customHeight="1">
       <c r="A8" s="2">
         <v>45596</v>
       </c>
@@ -4172,7 +4184,7 @@
       <c r="X8" s="15"/>
       <c r="Y8" s="13"/>
     </row>
-    <row r="9" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" ht="15" customHeight="1">
       <c r="A9" s="2">
         <v>45604</v>
       </c>
@@ -4221,7 +4233,7 @@
       <c r="X9" s="15"/>
       <c r="Y9" s="13"/>
     </row>
-    <row r="10" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" ht="15" customHeight="1">
       <c r="A10" s="2">
         <v>45611</v>
       </c>
@@ -4270,7 +4282,7 @@
       <c r="X10" s="15"/>
       <c r="Y10" s="13"/>
     </row>
-    <row r="11" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" ht="15" customHeight="1">
       <c r="A11" s="2">
         <v>45625</v>
       </c>
@@ -4319,7 +4331,7 @@
       <c r="X11" s="15"/>
       <c r="Y11" s="13"/>
     </row>
-    <row r="12" spans="1:25" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" ht="15" customHeight="1" thickBot="1">
       <c r="A12" s="4">
         <v>45632</v>
       </c>
@@ -4376,20 +4388,20 @@
       <c r="X12" s="20"/>
       <c r="Y12" s="18"/>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25">
       <c r="A13" s="26"/>
       <c r="B13" s="26"/>
       <c r="C13" s="26"/>
       <c r="D13" s="26"/>
       <c r="I13" s="3"/>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25">
       <c r="A14" s="26"/>
       <c r="B14" s="26"/>
       <c r="C14" s="26"/>
       <c r="D14" s="26"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10">
       <c r="A29" s="61"/>
       <c r="B29" s="61"/>
       <c r="C29" s="61"/>
@@ -4401,59 +4413,59 @@
       <c r="I29" s="61"/>
       <c r="J29" s="61"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10">
       <c r="A31" s="60"/>
       <c r="B31" s="60"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10">
       <c r="A32" s="60"/>
       <c r="B32" s="60"/>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2">
       <c r="A33" s="60"/>
       <c r="B33" s="60"/>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2">
       <c r="A34" s="60"/>
       <c r="B34" s="60"/>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2">
       <c r="A35" s="60"/>
       <c r="B35" s="60"/>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2">
       <c r="A36" s="60"/>
       <c r="B36" s="60"/>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2">
       <c r="A37" s="60"/>
       <c r="B37" s="60"/>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2">
       <c r="A38" s="60"/>
       <c r="B38" s="60"/>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2">
       <c r="A39" s="60"/>
       <c r="B39" s="60"/>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2">
       <c r="A40" s="60"/>
       <c r="B40" s="60"/>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2">
       <c r="A41" s="60"/>
       <c r="B41" s="60"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2">
       <c r="A42" s="60"/>
       <c r="B42" s="60"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2">
       <c r="A43" s="60"/>
       <c r="B43" s="60"/>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:2">
       <c r="A44" s="60"/>
       <c r="B44" s="60"/>
     </row>
@@ -4482,35 +4494,35 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12299A9A-6C0C-4F92-957E-FBFCB6211744}">
   <dimension ref="A1:Y45"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.5078125" customWidth="1"/>
-    <col min="2" max="2" width="5.91796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.1640625" customWidth="1"/>
-    <col min="4" max="4" width="11.02734375" customWidth="1"/>
-    <col min="5" max="5" width="9.14453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.6171875" customWidth="1"/>
-    <col min="7" max="7" width="30.8046875" customWidth="1"/>
-    <col min="8" max="8" width="21.25390625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="36.58984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="31.87890625" customWidth="1"/>
-    <col min="11" max="11" width="20.58203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="12.5078125" customWidth="1"/>
-    <col min="14" max="14" width="43.1796875" customWidth="1"/>
-    <col min="15" max="15" width="19.7734375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="36.58984375" customWidth="1"/>
-    <col min="17" max="17" width="9.68359375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.97265625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.703125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="18.6953125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="39.01171875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="28.3828125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="26.6328125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="37.80078125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.5703125" customWidth="1"/>
+    <col min="7" max="7" width="30.85546875" customWidth="1"/>
+    <col min="8" max="8" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="31.85546875" customWidth="1"/>
+    <col min="11" max="11" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="12.5703125" customWidth="1"/>
+    <col min="14" max="14" width="43.140625" customWidth="1"/>
+    <col min="15" max="15" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="36.5703125" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="39" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="37.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4521,7 +4533,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" ht="27.75" customHeight="1" thickBot="1">
       <c r="A2" s="64" t="s">
         <v>3</v>
       </c>
@@ -4598,7 +4610,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25" ht="15" customHeight="1">
       <c r="A3" s="2">
         <v>45694</v>
       </c>
@@ -4650,7 +4662,7 @@
       <c r="X3" s="46"/>
       <c r="Y3" s="44"/>
     </row>
-    <row r="4" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25" ht="14.25" customHeight="1">
       <c r="A4" s="2">
         <v>45708</v>
       </c>
@@ -4708,7 +4720,7 @@
       <c r="X4" s="15"/>
       <c r="Y4" s="13"/>
     </row>
-    <row r="5" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" ht="14.25" customHeight="1">
       <c r="A5" s="2">
         <v>45722</v>
       </c>
@@ -4764,7 +4776,7 @@
       <c r="X5" s="15"/>
       <c r="Y5" s="13"/>
     </row>
-    <row r="6" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" ht="16.5" customHeight="1">
       <c r="A6" s="2">
         <v>45735</v>
       </c>
@@ -4820,7 +4832,7 @@
       <c r="X6" s="15"/>
       <c r="Y6" s="13"/>
     </row>
-    <row r="7" spans="1:25" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" ht="18" customHeight="1">
       <c r="A7" s="2">
         <v>45750</v>
       </c>
@@ -4874,7 +4886,7 @@
       <c r="X7" s="15"/>
       <c r="Y7" s="13"/>
     </row>
-    <row r="8" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" ht="16.5" customHeight="1">
       <c r="A8" s="2">
         <v>45751</v>
       </c>
@@ -4933,7 +4945,7 @@
       <c r="X8" s="15"/>
       <c r="Y8" s="13"/>
     </row>
-    <row r="9" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" ht="15.75" customHeight="1">
       <c r="A9" s="2">
         <v>45757</v>
       </c>
@@ -4995,7 +5007,7 @@
       <c r="X9" s="15"/>
       <c r="Y9" s="13"/>
     </row>
-    <row r="10" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" ht="15.75" customHeight="1">
       <c r="A10" s="2">
         <v>45758</v>
       </c>
@@ -5049,7 +5061,7 @@
       <c r="X10" s="20"/>
       <c r="Y10" s="18"/>
     </row>
-    <row r="11" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" ht="15.75" customHeight="1">
       <c r="A11" s="4">
         <v>45764</v>
       </c>
@@ -5109,7 +5121,7 @@
       <c r="X11" s="35"/>
       <c r="Y11" s="35"/>
     </row>
-    <row r="12" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25" ht="15.75" customHeight="1">
       <c r="A12" s="4">
         <v>45771</v>
       </c>
@@ -5170,7 +5182,7 @@
       <c r="X12" s="35"/>
       <c r="Y12" s="35"/>
     </row>
-    <row r="13" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25" ht="15.75" customHeight="1">
       <c r="A13" s="2">
         <v>45785</v>
       </c>
@@ -5223,7 +5235,7 @@
       <c r="X13" s="35"/>
       <c r="Y13" s="35"/>
     </row>
-    <row r="14" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25" ht="15.75" customHeight="1">
       <c r="A14" s="4">
         <v>45799</v>
       </c>
@@ -5269,7 +5281,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25" ht="15.75" customHeight="1">
       <c r="A15" s="4">
         <v>45805</v>
       </c>
@@ -5303,101 +5315,101 @@
         <v>250</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25" ht="15.75" customHeight="1">
       <c r="A16" s="75"/>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2">
       <c r="A17" s="26"/>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2">
       <c r="A18" s="26"/>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2">
       <c r="A19" s="26"/>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2">
       <c r="A20" s="75"/>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2">
       <c r="A21" s="26"/>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2">
       <c r="A22" s="75"/>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2">
       <c r="A23" s="26"/>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2">
       <c r="A24" s="26"/>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2">
       <c r="A25" s="26"/>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2">
       <c r="A26" s="26"/>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2">
       <c r="A27" s="26"/>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2">
       <c r="A28" s="26"/>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:2">
       <c r="B31" s="60"/>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2">
       <c r="A32" s="60"/>
       <c r="B32" s="60"/>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2">
       <c r="A33" s="60"/>
       <c r="B33" s="60"/>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2">
       <c r="A34" s="60"/>
       <c r="B34" s="60"/>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2">
       <c r="A35" s="60"/>
       <c r="B35" s="60"/>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2">
       <c r="A36" s="60"/>
       <c r="B36" s="60"/>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2">
       <c r="A37" s="60"/>
       <c r="B37" s="60"/>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2">
       <c r="A38" s="60"/>
       <c r="B38" s="60"/>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2">
       <c r="A39" s="60"/>
       <c r="B39" s="60"/>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2">
       <c r="A40" s="60"/>
       <c r="B40" s="60"/>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2">
       <c r="A41" s="60"/>
       <c r="B41" s="60"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2">
       <c r="A42" s="60"/>
       <c r="B42" s="60"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2">
       <c r="A43" s="60"/>
       <c r="B43" s="60"/>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:2">
       <c r="A44" s="60"/>
       <c r="B44" s="60"/>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2">
       <c r="A45" s="60"/>
     </row>
   </sheetData>
@@ -5422,34 +5434,34 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{243C2AD8-98F5-4435-96A3-1C2CAB922825}">
   <dimension ref="A1:Y26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.64453125" customWidth="1"/>
-    <col min="2" max="2" width="14.52734375" customWidth="1"/>
-    <col min="3" max="3" width="20.04296875" customWidth="1"/>
-    <col min="4" max="4" width="11.02734375" customWidth="1"/>
-    <col min="6" max="6" width="33.359375" customWidth="1"/>
-    <col min="7" max="7" width="30.8046875" customWidth="1"/>
-    <col min="8" max="8" width="21.25390625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="36.58984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="31.87890625" customWidth="1"/>
-    <col min="11" max="11" width="20.58203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="12.5078125" customWidth="1"/>
-    <col min="14" max="14" width="43.1796875" customWidth="1"/>
-    <col min="15" max="15" width="19.7734375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="36.58984375" customWidth="1"/>
-    <col min="17" max="17" width="9.68359375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.97265625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.703125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="18.6953125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="39.01171875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="28.3828125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="26.6328125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="37.80078125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="6" max="6" width="33.42578125" customWidth="1"/>
+    <col min="7" max="7" width="30.85546875" customWidth="1"/>
+    <col min="8" max="8" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="31.85546875" customWidth="1"/>
+    <col min="11" max="11" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="12.5703125" customWidth="1"/>
+    <col min="14" max="14" width="43.140625" customWidth="1"/>
+    <col min="15" max="15" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="36.5703125" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="39" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="37.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5460,7 +5472,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25" ht="27.75">
       <c r="A2" s="78" t="s">
         <v>3</v>
       </c>
@@ -5537,7 +5549,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" ht="15" customHeight="1" thickBot="1">
       <c r="A3" s="159">
         <v>45911</v>
       </c>
@@ -5600,7 +5612,7 @@
       <c r="X3" s="46"/>
       <c r="Y3" s="44"/>
     </row>
-    <row r="4" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25" ht="15" customHeight="1">
       <c r="A4" s="160">
         <v>45917</v>
       </c>
@@ -5669,7 +5681,7 @@
       <c r="X4" s="15"/>
       <c r="Y4" s="13"/>
     </row>
-    <row r="5" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" ht="15" customHeight="1">
       <c r="A5" s="160">
         <v>45926</v>
       </c>
@@ -5727,7 +5739,7 @@
       <c r="X5" s="15"/>
       <c r="Y5" s="13"/>
     </row>
-    <row r="6" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" ht="15" customHeight="1">
       <c r="A6" s="160">
         <v>45939</v>
       </c>
@@ -5791,7 +5803,7 @@
       <c r="X6" s="15"/>
       <c r="Y6" s="13"/>
     </row>
-    <row r="7" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" ht="15" customHeight="1">
       <c r="A7" s="160">
         <v>45946</v>
       </c>
@@ -5848,7 +5860,7 @@
       <c r="X7" s="15"/>
       <c r="Y7" s="13"/>
     </row>
-    <row r="8" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" ht="15" customHeight="1">
       <c r="A8" s="160">
         <v>45953</v>
       </c>
@@ -5906,7 +5918,7 @@
       <c r="X8" s="15"/>
       <c r="Y8" s="13"/>
     </row>
-    <row r="9" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" ht="15" customHeight="1">
       <c r="A9" s="160">
         <v>45967</v>
       </c>
@@ -5968,7 +5980,7 @@
       <c r="X9" s="15"/>
       <c r="Y9" s="13"/>
     </row>
-    <row r="10" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" ht="15" customHeight="1">
       <c r="A10" s="160">
         <v>45974</v>
       </c>
@@ -6031,7 +6043,7 @@
       <c r="X10" s="15"/>
       <c r="Y10" s="13"/>
     </row>
-    <row r="11" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" ht="15" customHeight="1">
       <c r="A11" s="160">
         <v>45980</v>
       </c>
@@ -6082,7 +6094,7 @@
       <c r="X11" s="35"/>
       <c r="Y11" s="35"/>
     </row>
-    <row r="12" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25" ht="16.5" customHeight="1">
       <c r="A12" s="160">
         <f>A10+7</f>
         <v>45981</v>
@@ -6135,7 +6147,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25">
       <c r="A13" s="160">
         <v>45986</v>
       </c>
@@ -6171,7 +6183,7 @@
       <c r="M13" s="158"/>
       <c r="N13" s="158"/>
     </row>
-    <row r="14" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25" ht="15" customHeight="1">
       <c r="A14" s="160">
         <v>45988</v>
       </c>
@@ -6226,7 +6238,7 @@
       <c r="X14" s="15"/>
       <c r="Y14" s="13"/>
     </row>
-    <row r="15" spans="1:25" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" ht="15" customHeight="1" thickBot="1">
       <c r="A15" s="161">
         <v>45995</v>
       </c>
@@ -6289,35 +6301,35 @@
       <c r="X15" s="15"/>
       <c r="Y15" s="13"/>
     </row>
-    <row r="16" spans="1:25" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" ht="15" customHeight="1" thickBot="1">
       <c r="A16" s="26"/>
       <c r="B16" s="26"/>
       <c r="C16" s="26"/>
       <c r="X16" s="20"/>
       <c r="Y16" s="18"/>
     </row>
-    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" ht="15" customHeight="1">
       <c r="A17" s="26"/>
       <c r="B17" s="26"/>
       <c r="C17" s="26"/>
     </row>
-    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" ht="15" customHeight="1">
       <c r="A18" s="26"/>
       <c r="B18" s="26"/>
       <c r="C18" s="26"/>
     </row>
-    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" ht="15" customHeight="1">
       <c r="A19" s="26"/>
       <c r="B19" s="26"/>
       <c r="C19" s="26"/>
     </row>
-    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="20" spans="1:3" ht="15" customHeight="1"/>
+    <row r="21" spans="1:3" ht="15" customHeight="1"/>
+    <row r="22" spans="1:3" ht="15" customHeight="1"/>
+    <row r="23" spans="1:3" ht="15" customHeight="1"/>
+    <row r="24" spans="1:3" ht="15" customHeight="1"/>
+    <row r="25" spans="1:3" ht="15" customHeight="1"/>
+    <row r="26" spans="1:3" ht="15" customHeight="1"/>
   </sheetData>
   <protectedRanges>
     <protectedRange algorithmName="SHA-512" hashValue="pQyTzP/d7t5ThMimBt5mu8gGozgAm1OwF6BMILsn5/kmtZ5mZf81NMi09wwU8mvtItxf0EVNWa6V4MCa0DKeSQ==" saltValue="NzZBiAQ1yFjat+SeIqh2Uw==" spinCount="100000" sqref="A3:E19" name="Range3_1"/>
@@ -6350,35 +6362,35 @@
   <sheetPr>
     <tabColor theme="9"/>
   </sheetPr>
-  <dimension ref="A1:Y16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:Y17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.5078125" customWidth="1"/>
-    <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.08203125" customWidth="1"/>
-    <col min="4" max="4" width="11.02734375" customWidth="1"/>
-    <col min="6" max="6" width="33.359375" customWidth="1"/>
-    <col min="7" max="7" width="30.8046875" customWidth="1"/>
-    <col min="8" max="8" width="21.25390625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="36.58984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="31.87890625" customWidth="1"/>
-    <col min="11" max="11" width="20.4453125" customWidth="1"/>
-    <col min="12" max="13" width="12.5078125" customWidth="1"/>
-    <col min="14" max="14" width="43.1796875" customWidth="1"/>
-    <col min="15" max="15" width="19.7734375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="36.58984375" customWidth="1"/>
-    <col min="17" max="17" width="9.68359375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.97265625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.703125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="18.6953125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="39.01171875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="28.3828125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="26.6328125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="37.80078125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.140625" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" customWidth="1"/>
+    <col min="6" max="6" width="33.42578125" customWidth="1"/>
+    <col min="7" max="7" width="30.85546875" customWidth="1"/>
+    <col min="8" max="8" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="31.85546875" customWidth="1"/>
+    <col min="11" max="11" width="20.42578125" customWidth="1"/>
+    <col min="12" max="13" width="12.5703125" customWidth="1"/>
+    <col min="14" max="14" width="43.140625" customWidth="1"/>
+    <col min="15" max="15" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="36.5703125" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="39" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="37.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6389,7 +6401,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25" ht="27.75">
       <c r="A2" s="64" t="s">
         <v>3</v>
       </c>
@@ -6466,7 +6478,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25" ht="15" customHeight="1">
       <c r="A3" s="75">
         <v>46051</v>
       </c>
@@ -6515,7 +6527,7 @@
       <c r="X3" s="46"/>
       <c r="Y3" s="44"/>
     </row>
-    <row r="4" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25" ht="15.75" customHeight="1">
       <c r="A4" s="75">
         <f>A3+12</f>
         <v>46063</v>
@@ -6566,7 +6578,7 @@
       <c r="X4" s="15"/>
       <c r="Y4" s="13"/>
     </row>
-    <row r="5" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" ht="18.75" customHeight="1">
       <c r="A5" s="75">
         <f>A4+16</f>
         <v>46079</v>
@@ -6621,7 +6633,7 @@
       <c r="X5" s="15"/>
       <c r="Y5" s="13"/>
     </row>
-    <row r="6" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" ht="15.75" customHeight="1">
       <c r="A6" s="75">
         <f>A5+14</f>
         <v>46093</v>
@@ -6651,17 +6663,17 @@
         <v>95</v>
       </c>
       <c r="I6" s="98" t="s">
-        <v>412</v>
+        <v>342</v>
       </c>
       <c r="J6" s="98" t="s">
-        <v>413</v>
+        <v>343</v>
       </c>
       <c r="K6" s="102"/>
       <c r="L6" s="24" t="s">
-        <v>414</v>
+        <v>344</v>
       </c>
       <c r="M6" s="24" t="s">
-        <v>415</v>
+        <v>345</v>
       </c>
       <c r="N6" s="16"/>
       <c r="O6" s="35"/>
@@ -6676,7 +6688,7 @@
       <c r="X6" s="15"/>
       <c r="Y6" s="13"/>
     </row>
-    <row r="7" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" ht="15.75" customHeight="1">
       <c r="A7" s="75">
         <f>A6+7</f>
         <v>46100</v>
@@ -6694,7 +6706,7 @@
         <v>8</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G7" s="14" t="s">
         <v>77</v>
@@ -6703,19 +6715,19 @@
         <v>101</v>
       </c>
       <c r="I7" s="98" t="s">
-        <v>408</v>
+        <v>347</v>
       </c>
       <c r="J7" s="98" t="s">
-        <v>409</v>
+        <v>348</v>
       </c>
       <c r="K7" s="102" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="L7" s="24" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="M7" s="24" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="N7" s="16"/>
       <c r="O7" s="35"/>
@@ -6730,7 +6742,7 @@
       <c r="X7" s="15"/>
       <c r="Y7" s="13"/>
     </row>
-    <row r="8" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" ht="17.25" customHeight="1">
       <c r="A8" s="75">
         <f>A6+14</f>
         <v>46107</v>
@@ -6751,7 +6763,7 @@
         <v>9</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="G8" s="14" t="s">
         <v>52</v>
@@ -6760,10 +6772,733 @@
         <v>87</v>
       </c>
       <c r="I8" s="98" t="s">
-        <v>410</v>
+        <v>353</v>
       </c>
       <c r="J8" s="98" t="s">
-        <v>411</v>
+        <v>354</v>
+      </c>
+      <c r="K8" s="102"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="16"/>
+      <c r="O8" s="35"/>
+      <c r="P8" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q8" s="5"/>
+      <c r="R8" s="5"/>
+      <c r="S8" s="16"/>
+      <c r="T8" s="35"/>
+      <c r="U8" s="5"/>
+      <c r="V8" s="5"/>
+      <c r="W8" s="5"/>
+      <c r="X8" s="15"/>
+      <c r="Y8" s="13"/>
+    </row>
+    <row r="9" spans="1:25" ht="18" customHeight="1">
+      <c r="A9" s="75">
+        <f>A8+7</f>
+        <v>46114</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>209</v>
+      </c>
+      <c r="D9" s="27" t="s">
+        <v>278</v>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>357</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="I9" s="98" t="s">
+        <v>358</v>
+      </c>
+      <c r="J9" s="98" t="s">
+        <v>359</v>
+      </c>
+      <c r="K9" s="102" t="s">
+        <v>360</v>
+      </c>
+      <c r="L9" s="24" t="s">
+        <v>361</v>
+      </c>
+      <c r="M9" s="24" t="s">
+        <v>362</v>
+      </c>
+      <c r="N9" s="16"/>
+      <c r="O9" s="35"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="5"/>
+      <c r="R9" s="5"/>
+      <c r="S9" s="16"/>
+      <c r="T9" s="35"/>
+      <c r="U9" s="5"/>
+      <c r="V9" s="5"/>
+      <c r="W9" s="5"/>
+      <c r="X9" s="15"/>
+      <c r="Y9" s="13"/>
+    </row>
+    <row r="10" spans="1:25">
+      <c r="A10" s="75">
+        <v>46120</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C10" s="26" t="str">
+        <f t="shared" si="0"/>
+        <v>Apr</v>
+      </c>
+      <c r="D10" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="E10">
+        <v>11</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>363</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="I10" s="98" t="s">
+        <v>364</v>
+      </c>
+      <c r="J10" s="98" t="s">
+        <v>364</v>
+      </c>
+      <c r="K10" s="102"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="16"/>
+      <c r="O10" s="35"/>
+      <c r="P10" s="5"/>
+      <c r="Q10" s="5"/>
+      <c r="R10" s="5"/>
+      <c r="S10" s="16"/>
+      <c r="T10" s="35"/>
+      <c r="U10" s="5"/>
+      <c r="V10" s="5"/>
+      <c r="W10" s="5"/>
+      <c r="X10" s="15"/>
+      <c r="Y10" s="13"/>
+    </row>
+    <row r="11" spans="1:25">
+      <c r="A11" s="75">
+        <v>46121</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C11" s="26" t="s">
+        <v>209</v>
+      </c>
+      <c r="D11" s="27" t="s">
+        <v>278</v>
+      </c>
+      <c r="E11">
+        <v>11</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>365</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="I11" s="98" t="s">
+        <v>364</v>
+      </c>
+      <c r="J11" s="98" t="s">
+        <v>364</v>
+      </c>
+      <c r="K11" s="102"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="16"/>
+      <c r="O11" s="35"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="5"/>
+      <c r="R11" s="5"/>
+      <c r="S11" s="16"/>
+      <c r="T11" s="35"/>
+      <c r="U11" s="5"/>
+      <c r="V11" s="5"/>
+      <c r="W11" s="5"/>
+      <c r="X11" s="15"/>
+      <c r="Y11" s="13"/>
+    </row>
+    <row r="12" spans="1:25">
+      <c r="A12" s="75">
+        <v>46128</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C12" s="26" t="str">
+        <f t="shared" ref="C12" si="3">TEXT(A12, "mmm")</f>
+        <v>Apr</v>
+      </c>
+      <c r="D12" s="27" t="str">
+        <f t="shared" ref="D12" si="4">TEXT(A12, "dddd")</f>
+        <v>Thursday</v>
+      </c>
+      <c r="E12">
+        <v>12</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>366</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="I12" s="98" t="s">
+        <v>364</v>
+      </c>
+      <c r="J12" s="98" t="s">
+        <v>364</v>
+      </c>
+      <c r="K12" s="102" t="s">
+        <v>367</v>
+      </c>
+      <c r="L12" s="5"/>
+      <c r="M12" s="24" t="s">
+        <v>368</v>
+      </c>
+      <c r="N12" s="16"/>
+      <c r="O12" s="35"/>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="5"/>
+      <c r="R12" s="5"/>
+      <c r="S12" s="16"/>
+      <c r="T12" s="35"/>
+      <c r="U12" s="5"/>
+      <c r="V12" s="5"/>
+      <c r="W12" s="5"/>
+      <c r="X12" s="15"/>
+      <c r="Y12" s="13"/>
+    </row>
+    <row r="13" spans="1:25" ht="18.75" customHeight="1">
+      <c r="A13" s="75">
+        <v>46135</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C13" s="26" t="s">
+        <v>209</v>
+      </c>
+      <c r="D13" s="27" t="s">
+        <v>278</v>
+      </c>
+      <c r="E13">
+        <v>13</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>369</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="I13" s="98" t="s">
+        <v>364</v>
+      </c>
+      <c r="J13" s="98" t="s">
+        <v>364</v>
+      </c>
+      <c r="K13" s="102"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="16"/>
+      <c r="O13" s="35"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="5"/>
+      <c r="R13" s="5"/>
+      <c r="S13" s="16"/>
+      <c r="T13" s="35"/>
+      <c r="U13" s="5"/>
+      <c r="V13" s="5"/>
+      <c r="W13" s="5"/>
+      <c r="X13" s="15"/>
+      <c r="Y13" s="13"/>
+    </row>
+    <row r="14" spans="1:25">
+      <c r="A14" s="26"/>
+      <c r="B14" s="26"/>
+      <c r="C14" s="26"/>
+      <c r="X14" s="20"/>
+      <c r="Y14" s="18"/>
+    </row>
+    <row r="15" spans="1:25" ht="12.75" customHeight="1">
+      <c r="A15" s="26"/>
+      <c r="B15" s="26"/>
+      <c r="C15" s="26"/>
+    </row>
+    <row r="16" spans="1:25">
+      <c r="A16" s="26"/>
+      <c r="B16" s="26"/>
+      <c r="C16" s="26"/>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="26"/>
+      <c r="B17" s="26"/>
+      <c r="C17" s="26"/>
+    </row>
+  </sheetData>
+  <protectedRanges>
+    <protectedRange algorithmName="SHA-512" hashValue="pQyTzP/d7t5ThMimBt5mu8gGozgAm1OwF6BMILsn5/kmtZ5mZf81NMi09wwU8mvtItxf0EVNWa6V4MCa0DKeSQ==" saltValue="NzZBiAQ1yFjat+SeIqh2Uw==" spinCount="100000" sqref="A3:E17" name="Range3_1"/>
+    <protectedRange algorithmName="SHA-512" hashValue="JNB4nrqrfZD45ijUCOmyuk44ibTGOz2xPKKqUb8Fu6IzynfOW0Plt2J4MjvTXFpCm0cEkYqWWfoKwgUFnGztPw==" saltValue="gktf/myRKhBCN9s2pCislA==" spinCount="100000" sqref="A2:L2 N2:Y2" name="Range4_1"/>
+    <protectedRange algorithmName="SHA-512" hashValue="B/N8xqtMc7pXr3rfrr4k91A6IFAPX6lxEHUr9qsJ3yHA+MBnFuw+x27DjsTYKp86iL5C7QQh1TPFTQHueWpZbw==" saltValue="c0IR/echnZmip5yS1t29Rw==" spinCount="100000" sqref="T3:T13" name="Range6_1"/>
+    <protectedRange algorithmName="SHA-512" hashValue="BKDH3ki5lE3XQdc5qZnIH6o8wW8E0PkHgMZFCkv/XYDEa+b/qenui0oReDIqPDXHceUVJ+rEgU3I9CDBHraDYg==" saltValue="ruXqG4NOhhm7cSLor8wHfw==" spinCount="100000" sqref="O2:O13" name="Range7_1"/>
+    <protectedRange sqref="X14:Y14 F3:Y13" name="Range8_1"/>
+    <protectedRange algorithmName="SHA-512" hashValue="JNB4nrqrfZD45ijUCOmyuk44ibTGOz2xPKKqUb8Fu6IzynfOW0Plt2J4MjvTXFpCm0cEkYqWWfoKwgUFnGztPw==" saltValue="gktf/myRKhBCN9s2pCislA==" spinCount="100000" sqref="M2" name="Range4_1_1"/>
+  </protectedRanges>
+  <hyperlinks>
+    <hyperlink ref="L9" r:id="rId1" xr:uid="{A4F5128F-E5C7-4066-B2E0-72C9A9E730AF}"/>
+    <hyperlink ref="M9" r:id="rId2" xr:uid="{58E46CD9-E829-4A89-8A0F-2BA3FCB0FBEC}"/>
+    <hyperlink ref="K9" r:id="rId3" xr:uid="{F42BC370-1CFD-46B8-99BD-1F21405A14EB}"/>
+    <hyperlink ref="M12" r:id="rId4" xr:uid="{CA8FFAFE-0C05-4395-B597-29714402C65D}"/>
+    <hyperlink ref="K12" r:id="rId5" xr:uid="{F2415116-3F84-4CE2-BC5E-AB58A12B487F}"/>
+    <hyperlink ref="K7" r:id="rId6" xr:uid="{EEDAB9A6-23C2-44A6-AE32-27763DA4A1D2}"/>
+    <hyperlink ref="M7" r:id="rId7" xr:uid="{60F7675F-B0A2-4588-8DBC-226BD313FA08}"/>
+    <hyperlink ref="L7" r:id="rId8" xr:uid="{B5519C91-F3AF-4FFA-92F0-015F0993FEC9}"/>
+    <hyperlink ref="L6" r:id="rId9" xr:uid="{E20CE4D9-AFC3-FE4E-8238-9CE8FB74EA4B}"/>
+    <hyperlink ref="M6" r:id="rId10" xr:uid="{6053315A-23DA-DA4E-9447-0140277816C3}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A33E49C-EC2E-42B7-80E4-DD607C0B7A89}">
+  <dimension ref="A1:Y13"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.5703125" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.140625" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="6" max="6" width="33.42578125" customWidth="1"/>
+    <col min="7" max="7" width="30.85546875" customWidth="1"/>
+    <col min="8" max="8" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="31.85546875" customWidth="1"/>
+    <col min="11" max="11" width="20.42578125" customWidth="1"/>
+    <col min="12" max="13" width="12.5703125" customWidth="1"/>
+    <col min="14" max="14" width="43.140625" customWidth="1"/>
+    <col min="15" max="15" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="36.5703125" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="39" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="37.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:25" ht="15.75" thickBot="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" ht="28.5" thickBot="1">
+      <c r="A2" s="64" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="63" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="78" t="s">
+        <v>137</v>
+      </c>
+      <c r="E2" s="64" t="s">
+        <v>189</v>
+      </c>
+      <c r="F2" s="140" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="141" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="142" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="143" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" s="144" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2" s="66" t="s">
+        <v>14</v>
+      </c>
+      <c r="M2" s="66" t="s">
+        <v>15</v>
+      </c>
+      <c r="N2" s="67" t="s">
+        <v>16</v>
+      </c>
+      <c r="O2" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="P2" s="66" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q2" s="65" t="s">
+        <v>19</v>
+      </c>
+      <c r="R2" s="66" t="s">
+        <v>20</v>
+      </c>
+      <c r="S2" s="67" t="s">
+        <v>21</v>
+      </c>
+      <c r="T2" s="69" t="s">
+        <v>22</v>
+      </c>
+      <c r="U2" s="67" t="s">
+        <v>23</v>
+      </c>
+      <c r="V2" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="W2" s="66" t="s">
+        <v>138</v>
+      </c>
+      <c r="X2" s="70" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y2" s="70" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" ht="15" customHeight="1">
+      <c r="A3" s="75">
+        <v>46275</v>
+      </c>
+      <c r="B3" s="77" t="s">
+        <v>190</v>
+      </c>
+      <c r="C3" s="29" t="str">
+        <f>TEXT(A3, "mmm")</f>
+        <v>Sep</v>
+      </c>
+      <c r="D3" s="55" t="str">
+        <f>TEXT(A3, "dddd")</f>
+        <v>Thursday</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>370</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>364</v>
+      </c>
+      <c r="H3" s="14" t="s">
+        <v>364</v>
+      </c>
+      <c r="I3" s="98" t="s">
+        <v>364</v>
+      </c>
+      <c r="J3" s="98" t="s">
+        <v>364</v>
+      </c>
+      <c r="K3" s="73"/>
+      <c r="L3" s="40"/>
+      <c r="M3" s="40"/>
+      <c r="N3" s="38"/>
+      <c r="O3" s="35"/>
+      <c r="P3" s="40"/>
+      <c r="Q3" s="40"/>
+      <c r="R3" s="40"/>
+      <c r="S3" s="38"/>
+      <c r="T3" s="35"/>
+      <c r="U3" s="40"/>
+      <c r="V3" s="40"/>
+      <c r="W3" s="40"/>
+      <c r="X3" s="46"/>
+      <c r="Y3" s="44"/>
+    </row>
+    <row r="4" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A4" s="75">
+        <f>A3+14</f>
+        <v>46289</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C4" s="26" t="str">
+        <f t="shared" ref="C4:C7" si="0">TEXT(A4, "mmm")</f>
+        <v>Sep</v>
+      </c>
+      <c r="D4" s="27" t="str">
+        <f t="shared" ref="D4:D8" si="1">TEXT(A4, "dddd")</f>
+        <v>Thursday</v>
+      </c>
+      <c r="E4">
+        <f>E3+2</f>
+        <v>3</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>370</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>364</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="I4" s="98" t="s">
+        <v>364</v>
+      </c>
+      <c r="J4" s="98" t="s">
+        <v>364</v>
+      </c>
+      <c r="K4" s="102"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="16"/>
+      <c r="O4" s="35"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="5"/>
+      <c r="S4" s="16"/>
+      <c r="T4" s="35"/>
+      <c r="U4" s="5"/>
+      <c r="V4" s="5"/>
+      <c r="W4" s="5"/>
+      <c r="X4" s="15"/>
+      <c r="Y4" s="13"/>
+    </row>
+    <row r="5" spans="1:25">
+      <c r="A5" s="75">
+        <f t="shared" ref="A5" si="2">A4+14</f>
+        <v>46303</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C5" s="26" t="str">
+        <f t="shared" si="0"/>
+        <v>Oct</v>
+      </c>
+      <c r="D5" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v>Thursday</v>
+      </c>
+      <c r="E5">
+        <f t="shared" ref="E5:E6" si="3">E4+2</f>
+        <v>5</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>370</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>364</v>
+      </c>
+      <c r="H5" s="14" t="s">
+        <v>364</v>
+      </c>
+      <c r="I5" s="98" t="s">
+        <v>364</v>
+      </c>
+      <c r="J5" s="98" t="s">
+        <v>364</v>
+      </c>
+      <c r="K5" s="102"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="16"/>
+      <c r="O5" s="35" t="s">
+        <v>339</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="Q5" s="5"/>
+      <c r="R5" s="5"/>
+      <c r="S5" s="16"/>
+      <c r="T5" s="35"/>
+      <c r="U5" s="5"/>
+      <c r="V5" s="5"/>
+      <c r="W5" s="5"/>
+      <c r="X5" s="15"/>
+      <c r="Y5" s="13"/>
+    </row>
+    <row r="6" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A6" s="75">
+        <f>A5+14</f>
+        <v>46317</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C6" s="26" t="str">
+        <f t="shared" si="0"/>
+        <v>Oct</v>
+      </c>
+      <c r="D6" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v>Thursday</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>370</v>
+      </c>
+      <c r="G6" s="14" t="s">
+        <v>364</v>
+      </c>
+      <c r="H6" s="14" t="s">
+        <v>364</v>
+      </c>
+      <c r="I6" s="98" t="s">
+        <v>364</v>
+      </c>
+      <c r="J6" s="98" t="s">
+        <v>364</v>
+      </c>
+      <c r="K6" s="102"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="16"/>
+      <c r="O6" s="35"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="5"/>
+      <c r="R6" s="5"/>
+      <c r="S6" s="16"/>
+      <c r="T6" s="35"/>
+      <c r="U6" s="5"/>
+      <c r="V6" s="5"/>
+      <c r="W6" s="5"/>
+      <c r="X6" s="15"/>
+      <c r="Y6" s="13"/>
+    </row>
+    <row r="7" spans="1:25">
+      <c r="A7" s="75">
+        <f>A6+14</f>
+        <v>46331</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C7" s="26" t="str">
+        <f t="shared" si="0"/>
+        <v>Nov</v>
+      </c>
+      <c r="D7" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v>Thursday</v>
+      </c>
+      <c r="E7">
+        <f>E6+2</f>
+        <v>9</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>370</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>364</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>364</v>
+      </c>
+      <c r="I7" s="98" t="s">
+        <v>364</v>
+      </c>
+      <c r="J7" s="98" t="s">
+        <v>364</v>
+      </c>
+      <c r="K7" s="102"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="16"/>
+      <c r="O7" s="35"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="5"/>
+      <c r="R7" s="5"/>
+      <c r="S7" s="16"/>
+      <c r="T7" s="35"/>
+      <c r="U7" s="5"/>
+      <c r="V7" s="5"/>
+      <c r="W7" s="5"/>
+      <c r="X7" s="15"/>
+      <c r="Y7" s="13"/>
+    </row>
+    <row r="8" spans="1:25">
+      <c r="A8" s="75">
+        <f>A7+14</f>
+        <v>46345</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>209</v>
+      </c>
+      <c r="D8" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v>Thursday</v>
+      </c>
+      <c r="E8">
+        <v>11</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>370</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>364</v>
+      </c>
+      <c r="H8" s="14" t="s">
+        <v>364</v>
+      </c>
+      <c r="I8" s="98" t="s">
+        <v>364</v>
+      </c>
+      <c r="J8" s="98" t="s">
+        <v>364</v>
       </c>
       <c r="K8" s="102"/>
       <c r="L8" s="5"/>
@@ -6781,711 +7516,36 @@
       <c r="X8" s="15"/>
       <c r="Y8" s="13"/>
     </row>
-    <row r="9" spans="1:25" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" ht="18.75" customHeight="1">
       <c r="A9" s="75">
-        <f>A8+7</f>
-        <v>46114</v>
+        <v>46121</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>190</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>209</v>
+        <v>371</v>
       </c>
       <c r="D9" s="27" t="s">
         <v>278</v>
       </c>
       <c r="E9">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>348</v>
+        <v>370</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>349</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>101</v>
+        <v>364</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>364</v>
       </c>
       <c r="I9" s="98" t="s">
-        <v>350</v>
+        <v>364</v>
       </c>
       <c r="J9" s="98" t="s">
-        <v>351</v>
-      </c>
-      <c r="K9" s="102" t="s">
-        <v>352</v>
-      </c>
-      <c r="L9" s="24" t="s">
-        <v>353</v>
-      </c>
-      <c r="M9" s="24" t="s">
-        <v>354</v>
-      </c>
-      <c r="N9" s="16"/>
-      <c r="O9" s="35"/>
-      <c r="P9" s="5"/>
-      <c r="Q9" s="5"/>
-      <c r="R9" s="5"/>
-      <c r="S9" s="16"/>
-      <c r="T9" s="35"/>
-      <c r="U9" s="5"/>
-      <c r="V9" s="5"/>
-      <c r="W9" s="5"/>
-      <c r="X9" s="15"/>
-      <c r="Y9" s="13"/>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A10" s="75">
-        <v>46120</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C10" s="26" t="str">
-        <f t="shared" si="0"/>
-        <v>Apr</v>
-      </c>
-      <c r="D10" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v>Wednesday</v>
-      </c>
-      <c r="E10">
-        <v>11</v>
-      </c>
-      <c r="F10" s="16" t="s">
-        <v>355</v>
-      </c>
-      <c r="G10" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="I10" s="98" t="s">
-        <v>342</v>
-      </c>
-      <c r="J10" s="98" t="s">
-        <v>342</v>
-      </c>
-      <c r="K10" s="102"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="16"/>
-      <c r="O10" s="35"/>
-      <c r="P10" s="5"/>
-      <c r="Q10" s="5"/>
-      <c r="R10" s="5"/>
-      <c r="S10" s="16"/>
-      <c r="T10" s="35"/>
-      <c r="U10" s="5"/>
-      <c r="V10" s="5"/>
-      <c r="W10" s="5"/>
-      <c r="X10" s="15"/>
-      <c r="Y10" s="13"/>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A11" s="75">
-        <f>A10+7</f>
-        <v>46127</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C11" s="26" t="str">
-        <f t="shared" ref="C11" si="3">TEXT(A11, "mmm")</f>
-        <v>Apr</v>
-      </c>
-      <c r="D11" s="27" t="str">
-        <f t="shared" ref="D11" si="4">TEXT(A11, "dddd")</f>
-        <v>Wednesday</v>
-      </c>
-      <c r="E11">
-        <v>12</v>
-      </c>
-      <c r="F11" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="G11" s="14" t="s">
-        <v>195</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="I11" s="98" t="s">
-        <v>342</v>
-      </c>
-      <c r="J11" s="98" t="s">
-        <v>342</v>
-      </c>
-      <c r="K11" s="102" t="s">
-        <v>357</v>
-      </c>
-      <c r="L11" s="5"/>
-      <c r="M11" s="24" t="s">
-        <v>358</v>
-      </c>
-      <c r="N11" s="16"/>
-      <c r="O11" s="35"/>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="5"/>
-      <c r="R11" s="5"/>
-      <c r="S11" s="16"/>
-      <c r="T11" s="35"/>
-      <c r="U11" s="5"/>
-      <c r="V11" s="5"/>
-      <c r="W11" s="5"/>
-      <c r="X11" s="15"/>
-      <c r="Y11" s="13"/>
-    </row>
-    <row r="12" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="75">
-        <v>46135</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C12" s="26" t="s">
-        <v>209</v>
-      </c>
-      <c r="D12" s="27" t="s">
-        <v>278</v>
-      </c>
-      <c r="E12">
-        <v>13</v>
-      </c>
-      <c r="F12" s="16" t="s">
-        <v>359</v>
-      </c>
-      <c r="G12" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="I12" s="98" t="s">
-        <v>342</v>
-      </c>
-      <c r="J12" s="98" t="s">
-        <v>342</v>
-      </c>
-      <c r="K12" s="102"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="5"/>
-      <c r="N12" s="16"/>
-      <c r="O12" s="35"/>
-      <c r="P12" s="5"/>
-      <c r="Q12" s="5"/>
-      <c r="R12" s="5"/>
-      <c r="S12" s="16"/>
-      <c r="T12" s="35"/>
-      <c r="U12" s="5"/>
-      <c r="V12" s="5"/>
-      <c r="W12" s="5"/>
-      <c r="X12" s="15"/>
-      <c r="Y12" s="13"/>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A13" s="26"/>
-      <c r="B13" s="26"/>
-      <c r="C13" s="26"/>
-      <c r="X13" s="20"/>
-      <c r="Y13" s="18"/>
-    </row>
-    <row r="14" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="26"/>
-      <c r="B14" s="26"/>
-      <c r="C14" s="26"/>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A15" s="26"/>
-      <c r="B15" s="26"/>
-      <c r="C15" s="26"/>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A16" s="26"/>
-      <c r="B16" s="26"/>
-      <c r="C16" s="26"/>
-    </row>
-  </sheetData>
-  <protectedRanges>
-    <protectedRange algorithmName="SHA-512" hashValue="pQyTzP/d7t5ThMimBt5mu8gGozgAm1OwF6BMILsn5/kmtZ5mZf81NMi09wwU8mvtItxf0EVNWa6V4MCa0DKeSQ==" saltValue="NzZBiAQ1yFjat+SeIqh2Uw==" spinCount="100000" sqref="A3:E16" name="Range3_1"/>
-    <protectedRange algorithmName="SHA-512" hashValue="JNB4nrqrfZD45ijUCOmyuk44ibTGOz2xPKKqUb8Fu6IzynfOW0Plt2J4MjvTXFpCm0cEkYqWWfoKwgUFnGztPw==" saltValue="gktf/myRKhBCN9s2pCislA==" spinCount="100000" sqref="A2:L2 N2:Y2" name="Range4_1"/>
-    <protectedRange algorithmName="SHA-512" hashValue="B/N8xqtMc7pXr3rfrr4k91A6IFAPX6lxEHUr9qsJ3yHA+MBnFuw+x27DjsTYKp86iL5C7QQh1TPFTQHueWpZbw==" saltValue="c0IR/echnZmip5yS1t29Rw==" spinCount="100000" sqref="T3:T12" name="Range6_1"/>
-    <protectedRange algorithmName="SHA-512" hashValue="BKDH3ki5lE3XQdc5qZnIH6o8wW8E0PkHgMZFCkv/XYDEa+b/qenui0oReDIqPDXHceUVJ+rEgU3I9CDBHraDYg==" saltValue="ruXqG4NOhhm7cSLor8wHfw==" spinCount="100000" sqref="O2:O12" name="Range7_1"/>
-    <protectedRange sqref="X13:Y13 F3:Y12" name="Range8_1"/>
-    <protectedRange algorithmName="SHA-512" hashValue="JNB4nrqrfZD45ijUCOmyuk44ibTGOz2xPKKqUb8Fu6IzynfOW0Plt2J4MjvTXFpCm0cEkYqWWfoKwgUFnGztPw==" saltValue="gktf/myRKhBCN9s2pCislA==" spinCount="100000" sqref="M2" name="Range4_1_1"/>
-  </protectedRanges>
-  <hyperlinks>
-    <hyperlink ref="L9" r:id="rId1" xr:uid="{A4F5128F-E5C7-4066-B2E0-72C9A9E730AF}"/>
-    <hyperlink ref="M9" r:id="rId2" xr:uid="{58E46CD9-E829-4A89-8A0F-2BA3FCB0FBEC}"/>
-    <hyperlink ref="K9" r:id="rId3" xr:uid="{F42BC370-1CFD-46B8-99BD-1F21405A14EB}"/>
-    <hyperlink ref="M11" r:id="rId4" xr:uid="{CA8FFAFE-0C05-4395-B597-29714402C65D}"/>
-    <hyperlink ref="K11" r:id="rId5" xr:uid="{F2415116-3F84-4CE2-BC5E-AB58A12B487F}"/>
-    <hyperlink ref="K7" r:id="rId6" xr:uid="{EEDAB9A6-23C2-44A6-AE32-27763DA4A1D2}"/>
-    <hyperlink ref="M7" r:id="rId7" xr:uid="{60F7675F-B0A2-4588-8DBC-226BD313FA08}"/>
-    <hyperlink ref="L7" r:id="rId8" xr:uid="{B5519C91-F3AF-4FFA-92F0-015F0993FEC9}"/>
-    <hyperlink ref="L6" r:id="rId9" xr:uid="{E20CE4D9-AFC3-FE4E-8238-9CE8FB74EA4B}"/>
-    <hyperlink ref="M6" r:id="rId10" xr:uid="{6053315A-23DA-DA4E-9447-0140277816C3}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A33E49C-EC2E-42B7-80E4-DD607C0B7A89}">
-  <dimension ref="A1:Y13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="12.5078125" customWidth="1"/>
-    <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.08203125" customWidth="1"/>
-    <col min="4" max="4" width="11.02734375" customWidth="1"/>
-    <col min="6" max="6" width="33.359375" customWidth="1"/>
-    <col min="7" max="7" width="30.8046875" customWidth="1"/>
-    <col min="8" max="8" width="21.25390625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="36.58984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="31.87890625" customWidth="1"/>
-    <col min="11" max="11" width="20.4453125" customWidth="1"/>
-    <col min="12" max="13" width="12.5078125" customWidth="1"/>
-    <col min="14" max="14" width="43.1796875" customWidth="1"/>
-    <col min="15" max="15" width="19.7734375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="36.58984375" customWidth="1"/>
-    <col min="17" max="17" width="9.68359375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.97265625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.703125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="18.6953125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="39.01171875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="28.3828125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="26.6328125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="37.80078125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="P1" t="s">
-        <v>1</v>
-      </c>
-      <c r="U1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:25" ht="28.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="64" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="76" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="63" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="78" t="s">
-        <v>137</v>
-      </c>
-      <c r="E2" s="64" t="s">
-        <v>189</v>
-      </c>
-      <c r="F2" s="140" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="141" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="142" t="s">
-        <v>10</v>
-      </c>
-      <c r="I2" s="143" t="s">
-        <v>11</v>
-      </c>
-      <c r="J2" s="140" t="s">
-        <v>12</v>
-      </c>
-      <c r="K2" s="144" t="s">
-        <v>13</v>
-      </c>
-      <c r="L2" s="66" t="s">
-        <v>14</v>
-      </c>
-      <c r="M2" s="66" t="s">
-        <v>15</v>
-      </c>
-      <c r="N2" s="67" t="s">
-        <v>16</v>
-      </c>
-      <c r="O2" s="68" t="s">
-        <v>17</v>
-      </c>
-      <c r="P2" s="66" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q2" s="65" t="s">
-        <v>19</v>
-      </c>
-      <c r="R2" s="66" t="s">
-        <v>20</v>
-      </c>
-      <c r="S2" s="67" t="s">
-        <v>21</v>
-      </c>
-      <c r="T2" s="69" t="s">
-        <v>22</v>
-      </c>
-      <c r="U2" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="V2" s="65" t="s">
-        <v>24</v>
-      </c>
-      <c r="W2" s="66" t="s">
-        <v>138</v>
-      </c>
-      <c r="X2" s="70" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y2" s="70" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="75">
-        <v>46275</v>
-      </c>
-      <c r="B3" s="77" t="s">
-        <v>190</v>
-      </c>
-      <c r="C3" s="29" t="str">
-        <f>TEXT(A3, "mmm")</f>
-        <v>Sep</v>
-      </c>
-      <c r="D3" s="55" t="str">
-        <f>TEXT(A3, "dddd")</f>
-        <v>Thursday</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>360</v>
-      </c>
-      <c r="G3" s="14" t="s">
-        <v>342</v>
-      </c>
-      <c r="H3" s="14" t="s">
-        <v>342</v>
-      </c>
-      <c r="I3" s="98" t="s">
-        <v>342</v>
-      </c>
-      <c r="J3" s="98" t="s">
-        <v>342</v>
-      </c>
-      <c r="K3" s="73"/>
-      <c r="L3" s="40"/>
-      <c r="M3" s="40"/>
-      <c r="N3" s="38"/>
-      <c r="O3" s="35"/>
-      <c r="P3" s="40"/>
-      <c r="Q3" s="40"/>
-      <c r="R3" s="40"/>
-      <c r="S3" s="38"/>
-      <c r="T3" s="35"/>
-      <c r="U3" s="40"/>
-      <c r="V3" s="40"/>
-      <c r="W3" s="40"/>
-      <c r="X3" s="46"/>
-      <c r="Y3" s="44"/>
-    </row>
-    <row r="4" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="75">
-        <f>A3+14</f>
-        <v>46289</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C4" s="26" t="str">
-        <f t="shared" ref="C4:C7" si="0">TEXT(A4, "mmm")</f>
-        <v>Sep</v>
-      </c>
-      <c r="D4" s="27" t="str">
-        <f t="shared" ref="D4:D8" si="1">TEXT(A4, "dddd")</f>
-        <v>Thursday</v>
-      </c>
-      <c r="E4">
-        <f>E3+2</f>
-        <v>3</v>
-      </c>
-      <c r="F4" s="16" t="s">
-        <v>360</v>
-      </c>
-      <c r="G4" s="14" t="s">
-        <v>342</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>342</v>
-      </c>
-      <c r="I4" s="98" t="s">
-        <v>342</v>
-      </c>
-      <c r="J4" s="98" t="s">
-        <v>342</v>
-      </c>
-      <c r="K4" s="102"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="16"/>
-      <c r="O4" s="35"/>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="5"/>
-      <c r="R4" s="5"/>
-      <c r="S4" s="16"/>
-      <c r="T4" s="35"/>
-      <c r="U4" s="5"/>
-      <c r="V4" s="5"/>
-      <c r="W4" s="5"/>
-      <c r="X4" s="15"/>
-      <c r="Y4" s="13"/>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A5" s="75">
-        <f t="shared" ref="A5" si="2">A4+14</f>
-        <v>46303</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C5" s="26" t="str">
-        <f t="shared" si="0"/>
-        <v>Oct</v>
-      </c>
-      <c r="D5" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v>Thursday</v>
-      </c>
-      <c r="E5">
-        <f t="shared" ref="E5:E6" si="3">E4+2</f>
-        <v>5</v>
-      </c>
-      <c r="F5" s="16" t="s">
-        <v>360</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>342</v>
-      </c>
-      <c r="H5" s="14" t="s">
-        <v>342</v>
-      </c>
-      <c r="I5" s="98" t="s">
-        <v>342</v>
-      </c>
-      <c r="J5" s="98" t="s">
-        <v>342</v>
-      </c>
-      <c r="K5" s="102"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="16"/>
-      <c r="O5" s="35" t="s">
-        <v>339</v>
-      </c>
-      <c r="P5" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="Q5" s="5"/>
-      <c r="R5" s="5"/>
-      <c r="S5" s="16"/>
-      <c r="T5" s="35"/>
-      <c r="U5" s="5"/>
-      <c r="V5" s="5"/>
-      <c r="W5" s="5"/>
-      <c r="X5" s="15"/>
-      <c r="Y5" s="13"/>
-    </row>
-    <row r="6" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="75">
-        <f>A5+14</f>
-        <v>46317</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C6" s="26" t="str">
-        <f t="shared" si="0"/>
-        <v>Oct</v>
-      </c>
-      <c r="D6" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v>Thursday</v>
-      </c>
-      <c r="E6">
-        <f t="shared" si="3"/>
-        <v>7</v>
-      </c>
-      <c r="F6" s="16" t="s">
-        <v>360</v>
-      </c>
-      <c r="G6" s="14" t="s">
-        <v>342</v>
-      </c>
-      <c r="H6" s="14" t="s">
-        <v>342</v>
-      </c>
-      <c r="I6" s="98" t="s">
-        <v>342</v>
-      </c>
-      <c r="J6" s="98" t="s">
-        <v>342</v>
-      </c>
-      <c r="K6" s="102"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="16"/>
-      <c r="O6" s="35"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="5"/>
-      <c r="R6" s="5"/>
-      <c r="S6" s="16"/>
-      <c r="T6" s="35"/>
-      <c r="U6" s="5"/>
-      <c r="V6" s="5"/>
-      <c r="W6" s="5"/>
-      <c r="X6" s="15"/>
-      <c r="Y6" s="13"/>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A7" s="75">
-        <f>A6+14</f>
-        <v>46331</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C7" s="26" t="str">
-        <f t="shared" si="0"/>
-        <v>Nov</v>
-      </c>
-      <c r="D7" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v>Thursday</v>
-      </c>
-      <c r="E7">
-        <f>E6+2</f>
-        <v>9</v>
-      </c>
-      <c r="F7" s="16" t="s">
-        <v>360</v>
-      </c>
-      <c r="G7" s="14" t="s">
-        <v>342</v>
-      </c>
-      <c r="H7" s="14" t="s">
-        <v>342</v>
-      </c>
-      <c r="I7" s="98" t="s">
-        <v>342</v>
-      </c>
-      <c r="J7" s="98" t="s">
-        <v>342</v>
-      </c>
-      <c r="K7" s="102"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="16"/>
-      <c r="O7" s="35"/>
-      <c r="P7" s="5"/>
-      <c r="Q7" s="5"/>
-      <c r="R7" s="5"/>
-      <c r="S7" s="16"/>
-      <c r="T7" s="35"/>
-      <c r="U7" s="5"/>
-      <c r="V7" s="5"/>
-      <c r="W7" s="5"/>
-      <c r="X7" s="15"/>
-      <c r="Y7" s="13"/>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A8" s="75">
-        <f>A7+14</f>
-        <v>46345</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C8" s="26" t="s">
-        <v>209</v>
-      </c>
-      <c r="D8" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v>Thursday</v>
-      </c>
-      <c r="E8">
-        <v>11</v>
-      </c>
-      <c r="F8" s="16" t="s">
-        <v>360</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>342</v>
-      </c>
-      <c r="H8" s="14" t="s">
-        <v>342</v>
-      </c>
-      <c r="I8" s="98" t="s">
-        <v>342</v>
-      </c>
-      <c r="J8" s="98" t="s">
-        <v>342</v>
-      </c>
-      <c r="K8" s="102"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="16"/>
-      <c r="O8" s="35"/>
-      <c r="P8" s="5"/>
-      <c r="Q8" s="5"/>
-      <c r="R8" s="5"/>
-      <c r="S8" s="16"/>
-      <c r="T8" s="35"/>
-      <c r="U8" s="5"/>
-      <c r="V8" s="5"/>
-      <c r="W8" s="5"/>
-      <c r="X8" s="15"/>
-      <c r="Y8" s="13"/>
-    </row>
-    <row r="9" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="75">
-        <v>46121</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C9" s="26" t="s">
-        <v>361</v>
-      </c>
-      <c r="D9" s="27" t="s">
-        <v>278</v>
-      </c>
-      <c r="E9">
-        <v>13</v>
-      </c>
-      <c r="F9" s="16" t="s">
-        <v>360</v>
-      </c>
-      <c r="G9" s="14" t="s">
-        <v>342</v>
-      </c>
-      <c r="H9" s="14" t="s">
-        <v>342</v>
-      </c>
-      <c r="I9" s="98" t="s">
-        <v>342</v>
-      </c>
-      <c r="J9" s="98" t="s">
-        <v>342</v>
+        <v>364</v>
       </c>
       <c r="K9" s="102"/>
       <c r="L9" s="5"/>
@@ -7503,24 +7563,24 @@
       <c r="X9" s="15"/>
       <c r="Y9" s="13"/>
     </row>
-    <row r="10" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" ht="15.75" thickBot="1">
       <c r="A10" s="26"/>
       <c r="B10" s="26"/>
       <c r="C10" s="26"/>
       <c r="X10" s="20"/>
       <c r="Y10" s="18"/>
     </row>
-    <row r="11" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" ht="12.75" customHeight="1">
       <c r="A11" s="26"/>
       <c r="B11" s="26"/>
       <c r="C11" s="26"/>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25">
       <c r="A12" s="26"/>
       <c r="B12" s="26"/>
       <c r="C12" s="26"/>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25">
       <c r="A13" s="26"/>
       <c r="B13" s="26"/>
       <c r="C13" s="26"/>
@@ -7541,205 +7601,213 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AEC079F-155A-491D-9189-1418FC903287}">
-  <dimension ref="A1:C19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:C20"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="31.34375" customWidth="1"/>
-    <col min="2" max="2" width="25.9609375" customWidth="1"/>
-    <col min="3" max="3" width="20.17578125" customWidth="1"/>
+    <col min="1" max="1" width="31.28515625" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" s="55" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="B2" s="54" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="C2" s="54" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" s="136" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="B3" s="137"/>
       <c r="C3" s="138" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3">
       <c r="A4" s="5" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="B4" s="52"/>
       <c r="C4" s="50" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3">
       <c r="A5" s="52" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="B5" s="52"/>
       <c r="C5" s="50" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" s="52" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="B6" s="52" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="C6" s="50" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3">
       <c r="A7" s="52" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="B7" s="52" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="C7" s="50" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3">
       <c r="A8" s="52" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="B8" s="52" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="C8" s="50" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3">
       <c r="A9" s="52" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="B9" s="52"/>
       <c r="C9" s="50"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3">
       <c r="A10" s="52" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="B10" s="52" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="C10" s="50" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
       <c r="A11" s="52" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="B11" s="52" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="C11" s="50" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
       <c r="A12" s="52" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="B12" s="52" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="C12" s="50" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
       <c r="A13" s="52" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="B13" s="52" t="s">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="C13" s="50" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
       <c r="A14" s="52" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="B14" s="52" t="s">
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="C14" s="50" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
       <c r="A15" s="52" t="s">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="B15" s="52" t="s">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="C15" s="50" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
       <c r="A16" s="137" t="s">
         <v>321</v>
       </c>
       <c r="B16" s="137" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="C16" s="139" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17" s="137" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B17" s="137" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="C17" s="139" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18" s="52" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="B18" s="52" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="C18" s="50" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3">
       <c r="A19" s="53" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="B19" s="53" t="s">
         <v>230</v>
       </c>
       <c r="C19" s="51" t="s">
-        <v>396</v>
+        <v>406</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>407</v>
+      </c>
+      <c r="B20" t="s">
+        <v>408</v>
       </c>
     </row>
   </sheetData>
@@ -7755,24 +7823,24 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AD19DE5-C22F-4D41-B540-76D70438E18B}">
   <dimension ref="A1:I16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17.890625" customWidth="1"/>
-    <col min="6" max="6" width="14.52734375" customWidth="1"/>
+    <col min="1" max="1" width="17.85546875" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="15.75" thickBot="1">
       <c r="A1" s="135" t="s">
         <v>3</v>
       </c>
       <c r="B1" s="131" t="s">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="C1" s="130" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="169">
         <v>46051</v>
       </c>
@@ -7780,14 +7848,14 @@
         <v>1</v>
       </c>
       <c r="C2" s="170" t="s">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="F2" s="75"/>
       <c r="G2" s="77"/>
       <c r="H2" s="29"/>
       <c r="I2" s="55"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9">
       <c r="A3" s="171">
         <f>A2+7</f>
         <v>46058</v>
@@ -7797,14 +7865,14 @@
         <v>2</v>
       </c>
       <c r="C3" s="170" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="F3" s="75"/>
       <c r="G3" s="2"/>
       <c r="H3" s="26"/>
       <c r="I3" s="27"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9">
       <c r="A4" s="171">
         <f t="shared" ref="A4:A12" si="0">A3+7</f>
         <v>46065</v>
@@ -7814,14 +7882,14 @@
         <v>3</v>
       </c>
       <c r="C4" s="170" t="s">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="F4" s="75"/>
       <c r="G4" s="2"/>
       <c r="H4" s="26"/>
       <c r="I4" s="27"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9">
       <c r="A5" s="171">
         <f t="shared" si="0"/>
         <v>46072</v>
@@ -7831,14 +7899,14 @@
         <v>4</v>
       </c>
       <c r="C5" s="170" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="F5" s="75"/>
       <c r="G5" s="2"/>
       <c r="H5" s="26"/>
       <c r="I5" s="27"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9">
       <c r="A6" s="133">
         <f t="shared" si="0"/>
         <v>46079</v>
@@ -7848,14 +7916,14 @@
         <v>5</v>
       </c>
       <c r="C6" s="134" t="s">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="F6" s="75"/>
       <c r="G6" s="2"/>
       <c r="H6" s="26"/>
       <c r="I6" s="27"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9">
       <c r="A7" s="133">
         <f t="shared" si="0"/>
         <v>46086</v>
@@ -7865,14 +7933,14 @@
         <v>6</v>
       </c>
       <c r="C7" s="134" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="F7" s="75"/>
       <c r="G7" s="2"/>
       <c r="H7" s="26"/>
       <c r="I7" s="27"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9">
       <c r="A8" s="133">
         <f t="shared" si="0"/>
         <v>46093</v>
@@ -7882,14 +7950,14 @@
         <v>7</v>
       </c>
       <c r="C8" s="134" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="F8" s="75"/>
       <c r="G8" s="2"/>
       <c r="H8" s="26"/>
       <c r="I8" s="27"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9">
       <c r="A9" s="133">
         <f t="shared" si="0"/>
         <v>46100</v>
@@ -7899,14 +7967,14 @@
         <v>8</v>
       </c>
       <c r="C9" s="134" t="s">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="F9" s="75"/>
       <c r="G9" s="2"/>
       <c r="H9" s="26"/>
       <c r="I9" s="27"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9">
       <c r="A10" s="133">
         <f t="shared" si="0"/>
         <v>46107</v>
@@ -7916,14 +7984,14 @@
         <v>9</v>
       </c>
       <c r="C10" s="134" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="F10" s="75"/>
       <c r="G10" s="2"/>
       <c r="H10" s="26"/>
       <c r="I10" s="27"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9">
       <c r="A11" s="133">
         <f t="shared" si="0"/>
         <v>46114</v>
@@ -7933,10 +8001,10 @@
         <v>10</v>
       </c>
       <c r="C11" s="134" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="133">
         <f t="shared" si="0"/>
         <v>46121</v>
@@ -7946,10 +8014,10 @@
         <v>11</v>
       </c>
       <c r="C12" s="134" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="133">
         <f t="shared" ref="A13:A14" si="3">A12+7</f>
         <v>46128</v>
@@ -7959,10 +8027,10 @@
         <v>12</v>
       </c>
       <c r="C13" s="134" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="133">
         <f t="shared" si="3"/>
         <v>46135</v>
@@ -7972,15 +8040,15 @@
         <v>13</v>
       </c>
       <c r="C14" s="134" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="133"/>
       <c r="B15" s="134"/>
       <c r="C15" s="134"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9">
       <c r="G16" s="26"/>
     </row>
   </sheetData>
@@ -8007,29 +8075,29 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2BB5C5F-5790-4A91-A6E8-8841719DA1FC}">
   <dimension ref="A2:I20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.41015625" customWidth="1"/>
-    <col min="2" max="2" width="9.14453125" customWidth="1"/>
-    <col min="3" max="3" width="14.66015625" customWidth="1"/>
-    <col min="4" max="4" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.75" customWidth="1"/>
-    <col min="7" max="7" width="38.203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.46484375" customWidth="1"/>
-    <col min="9" max="9" width="64.703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" customWidth="1"/>
+    <col min="4" max="4" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.7109375" customWidth="1"/>
+    <col min="7" max="7" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.42578125" customWidth="1"/>
+    <col min="9" max="9" width="64.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" ht="23.25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="23.25">
       <c r="A2" s="91" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="18.75">
       <c r="A3" s="79" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="35.25" x14ac:dyDescent="0.25">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="35.25">
       <c r="A5" s="80" t="s">
         <v>3</v>
       </c>
@@ -8052,13 +8120,13 @@
         <v>9</v>
       </c>
       <c r="H5" s="82" t="s">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="I5" s="81" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="18.75">
       <c r="A6" s="92">
         <v>45694</v>
       </c>
@@ -8082,10 +8150,10 @@
       </c>
       <c r="H6" s="85"/>
       <c r="I6" s="84" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="18.75">
       <c r="A7" s="83">
         <v>45708</v>
       </c>
@@ -8114,7 +8182,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="18.75">
       <c r="A8" s="83">
         <v>45722</v>
       </c>
@@ -8141,7 +8209,7 @@
       </c>
       <c r="I8" s="86"/>
     </row>
-    <row r="9" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="18.75">
       <c r="A9" s="83">
         <v>45735</v>
       </c>
@@ -8152,7 +8220,7 @@
         <v>198</v>
       </c>
       <c r="D9" s="94" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="E9" s="94">
         <v>8</v>
@@ -8167,10 +8235,10 @@
         <v>206</v>
       </c>
       <c r="I9" s="86" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="18.75">
       <c r="A10" s="83">
         <v>45744</v>
       </c>
@@ -8197,7 +8265,7 @@
       </c>
       <c r="I10" s="86"/>
     </row>
-    <row r="11" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="18.75">
       <c r="A11" s="83">
         <v>45750</v>
       </c>
@@ -8214,17 +8282,17 @@
         <v>10</v>
       </c>
       <c r="F11" s="87" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="G11" s="87" t="s">
         <v>68</v>
       </c>
       <c r="H11" s="87"/>
       <c r="I11" s="86" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="18.75">
       <c r="A12" s="83">
         <v>45758</v>
       </c>
@@ -8250,10 +8318,10 @@
         <v>31</v>
       </c>
       <c r="I12" s="86" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="18.75">
       <c r="A13" s="83">
         <v>45764</v>
       </c>
@@ -8270,13 +8338,13 @@
         <v>12</v>
       </c>
       <c r="F13" s="87" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="G13" s="87"/>
       <c r="H13" s="87"/>
       <c r="I13" s="86"/>
     </row>
-    <row r="14" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="18.75">
       <c r="A14" s="88">
         <v>45771</v>
       </c>
@@ -8293,7 +8361,7 @@
         <v>13</v>
       </c>
       <c r="F14" s="90" t="s">
-        <v>407</v>
+        <v>419</v>
       </c>
       <c r="G14" s="90" t="s">
         <v>77</v>
@@ -8305,7 +8373,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="20" spans="8:8" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="8:8" ht="18.75">
       <c r="H20" s="79"/>
     </row>
   </sheetData>

--- a/data/MACSI seminar series.xlsx
+++ b/data/MACSI seminar series.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ulcampus-my.sharepoint.com/personal/david_osullivan_ul_ie/Documents/Academic_work/_Misc/MACSI Seminars/macsi-seminars.github.io/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="356" documentId="13_ncr:1_{12BE53B5-C8C7-44FE-8280-19C653D9122E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1BFF16E0-978C-40A1-BCB6-463F79566EF9}"/>
+  <xr:revisionPtr revIDLastSave="362" documentId="13_ncr:1_{12BE53B5-C8C7-44FE-8280-19C653D9122E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C389BF6-7B71-4379-89DC-61D8349F7487}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1019" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1021" uniqueCount="423">
   <si>
     <t>Fill in as much of the green boxes as possible. Ideally, this would be before you have finished your visitors travel dates (just to avoid double booking).</t>
   </si>
@@ -1180,9 +1180,6 @@
     <t>Cornelius Fritz</t>
   </si>
   <si>
-    <t>Trinity college Dublin</t>
-  </si>
-  <si>
     <t>Scalable Durational Event Models: Application to Physical and Digital Interactions</t>
   </si>
   <si>
@@ -1205,6 +1202,18 @@
   </si>
   <si>
     <t>Michel Destrade</t>
+  </si>
+  <si>
+    <t>An introduction to the European Research Council grants</t>
+  </si>
+  <si>
+    <t>This talk provides an insider’s overview of the European Research Council and its funding schemes, informed by a 12-month secondment at the ERC Executive Agency in Brussels in 2024-25. It explains how ERC proposals are evaluated in practice, with emphasis on what panels look for when assessing excellence, ambition, and feasibility. The presentation covers the different ERC grant types, the structure of proposals, the two-step evaluation process, common misconceptions, and recurring reasons why strong applications might fail. It also discusses how to frame a compelling frontier-research narrative and how to position oneself strategically for the ERC grants.</t>
+  </si>
+  <si>
+    <t>https://scholar.google.com/citations?user=EQAvBLgAAAAJ&amp;hl=en</t>
+  </si>
+  <si>
+    <t>https://maths.universityofgalway.ie/~destrade/</t>
   </si>
   <si>
     <t>Carl Scarrott</t>
@@ -6816,25 +6825,25 @@
         <v>356</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>357</v>
+        <v>322</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>101</v>
       </c>
       <c r="I9" s="98" t="s">
+        <v>357</v>
+      </c>
+      <c r="J9" s="98" t="s">
         <v>358</v>
       </c>
-      <c r="J9" s="98" t="s">
+      <c r="K9" s="102" t="s">
         <v>359</v>
       </c>
-      <c r="K9" s="102" t="s">
+      <c r="L9" s="24" t="s">
         <v>360</v>
       </c>
-      <c r="L9" s="24" t="s">
+      <c r="M9" s="24" t="s">
         <v>361</v>
-      </c>
-      <c r="M9" s="24" t="s">
-        <v>362</v>
       </c>
       <c r="N9" s="16"/>
       <c r="O9" s="35"/>
@@ -6868,7 +6877,7 @@
         <v>11</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G10" s="14" t="s">
         <v>77</v>
@@ -6877,10 +6886,10 @@
         <v>87</v>
       </c>
       <c r="I10" s="98" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="J10" s="98" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="K10" s="102"/>
       <c r="L10" s="5"/>
@@ -6898,7 +6907,7 @@
       <c r="X10" s="15"/>
       <c r="Y10" s="13"/>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:25" ht="14.25" customHeight="1">
       <c r="A11" s="75">
         <v>46121</v>
       </c>
@@ -6915,7 +6924,7 @@
         <v>11</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G11" s="14" t="s">
         <v>195</v>
@@ -6924,14 +6933,18 @@
         <v>87</v>
       </c>
       <c r="I11" s="98" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="J11" s="98" t="s">
-        <v>364</v>
-      </c>
-      <c r="K11" s="102"/>
+        <v>366</v>
+      </c>
+      <c r="K11" s="102" t="s">
+        <v>367</v>
+      </c>
       <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
+      <c r="M11" s="24" t="s">
+        <v>368</v>
+      </c>
       <c r="N11" s="16"/>
       <c r="O11" s="35"/>
       <c r="P11" s="5"/>
@@ -6964,7 +6977,7 @@
         <v>12</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="G12" s="14" t="s">
         <v>195</v>
@@ -6973,17 +6986,17 @@
         <v>78</v>
       </c>
       <c r="I12" s="98" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="J12" s="98" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="K12" s="102" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="L12" s="5"/>
       <c r="M12" s="24" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="N12" s="16"/>
       <c r="O12" s="35"/>
@@ -7015,7 +7028,7 @@
         <v>13</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="G13" s="14" t="s">
         <v>73</v>
@@ -7024,10 +7037,10 @@
         <v>95</v>
       </c>
       <c r="I13" s="98" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="J13" s="98" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="K13" s="102"/>
       <c r="L13" s="5"/>
@@ -7087,6 +7100,8 @@
     <hyperlink ref="L7" r:id="rId8" xr:uid="{B5519C91-F3AF-4FFA-92F0-015F0993FEC9}"/>
     <hyperlink ref="L6" r:id="rId9" xr:uid="{E20CE4D9-AFC3-FE4E-8238-9CE8FB74EA4B}"/>
     <hyperlink ref="M6" r:id="rId10" xr:uid="{6053315A-23DA-DA4E-9447-0140277816C3}"/>
+    <hyperlink ref="M11" r:id="rId11" xr:uid="{942C7964-68D4-4F8F-8947-80A84887C647}"/>
+    <hyperlink ref="K11" r:id="rId12" xr:uid="{460148DF-9775-4F8A-91F3-89030F1FC4E8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7229,19 +7244,19 @@
         <v>1</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H3" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="I3" s="98" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="J3" s="98" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="K3" s="73"/>
       <c r="L3" s="40"/>
@@ -7280,19 +7295,19 @@
         <v>3</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="I4" s="98" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="J4" s="98" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="K4" s="102"/>
       <c r="L4" s="5"/>
@@ -7331,19 +7346,19 @@
         <v>5</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="I5" s="98" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="J5" s="98" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="K5" s="102"/>
       <c r="L5" s="5"/>
@@ -7386,19 +7401,19 @@
         <v>7</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="I6" s="98" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="J6" s="98" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="K6" s="102"/>
       <c r="L6" s="5"/>
@@ -7437,19 +7452,19 @@
         <v>9</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="I7" s="98" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="J7" s="98" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="K7" s="102"/>
       <c r="L7" s="5"/>
@@ -7486,19 +7501,19 @@
         <v>11</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="I8" s="98" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="J8" s="98" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="K8" s="102"/>
       <c r="L8" s="5"/>
@@ -7524,7 +7539,7 @@
         <v>190</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="D9" s="27" t="s">
         <v>278</v>
@@ -7533,19 +7548,19 @@
         <v>13</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="I9" s="98" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="J9" s="98" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="K9" s="102"/>
       <c r="L9" s="5"/>
@@ -7611,23 +7626,23 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="55" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B2" s="54" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C2" s="54" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="136" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B3" s="137"/>
       <c r="C3" s="138" t="s">
@@ -7636,7 +7651,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="5" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B4" s="52"/>
       <c r="C4" s="50" t="s">
@@ -7645,19 +7660,19 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="52" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B5" s="52"/>
       <c r="C5" s="50" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="52" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B6" s="52" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C6" s="50" t="s">
         <v>87</v>
@@ -7665,10 +7680,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="52" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B7" s="52" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C7" s="50" t="s">
         <v>87</v>
@@ -7676,10 +7691,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="52" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B8" s="52" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C8" s="50" t="s">
         <v>101</v>
@@ -7687,75 +7702,75 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="52" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B9" s="52"/>
       <c r="C9" s="50"/>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="52" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B10" s="52" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C10" s="50" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="52" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B11" s="52" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C11" s="50" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="52" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B12" s="52" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C12" s="50" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="52" t="s">
+        <v>398</v>
+      </c>
+      <c r="B13" s="52" t="s">
+        <v>399</v>
+      </c>
+      <c r="C13" s="50" t="s">
         <v>395</v>
-      </c>
-      <c r="B13" s="52" t="s">
-        <v>396</v>
-      </c>
-      <c r="C13" s="50" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="52" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B14" s="52" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C14" s="50" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="52" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B15" s="52" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C15" s="50" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -7763,10 +7778,10 @@
         <v>321</v>
       </c>
       <c r="B16" s="137" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="C16" s="139" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -7774,18 +7789,18 @@
         <v>346</v>
       </c>
       <c r="B17" s="137" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C17" s="139" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="52" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B18" s="52" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C18" s="50" t="s">
         <v>87</v>
@@ -7793,21 +7808,21 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="53" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B19" s="53" t="s">
         <v>230</v>
       </c>
       <c r="C19" s="51" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B20" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
   </sheetData>
@@ -7834,10 +7849,10 @@
         <v>3</v>
       </c>
       <c r="B1" s="131" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C1" s="130" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -7848,7 +7863,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="170" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="F2" s="75"/>
       <c r="G2" s="77"/>
@@ -7865,7 +7880,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="170" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="F3" s="75"/>
       <c r="G3" s="2"/>
@@ -7882,7 +7897,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="170" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="F4" s="75"/>
       <c r="G4" s="2"/>
@@ -7899,7 +7914,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="170" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="F5" s="75"/>
       <c r="G5" s="2"/>
@@ -7916,7 +7931,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="134" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="F6" s="75"/>
       <c r="G6" s="2"/>
@@ -7933,7 +7948,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="134" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="F7" s="75"/>
       <c r="G7" s="2"/>
@@ -7950,7 +7965,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="134" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="F8" s="75"/>
       <c r="G8" s="2"/>
@@ -7967,7 +7982,7 @@
         <v>8</v>
       </c>
       <c r="C9" s="134" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="F9" s="75"/>
       <c r="G9" s="2"/>
@@ -7984,7 +7999,7 @@
         <v>9</v>
       </c>
       <c r="C10" s="134" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="F10" s="75"/>
       <c r="G10" s="2"/>
@@ -8001,7 +8016,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="134" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -8014,7 +8029,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="134" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -8027,7 +8042,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="134" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -8040,7 +8055,7 @@
         <v>13</v>
       </c>
       <c r="C14" s="134" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -8089,12 +8104,12 @@
   <sheetData>
     <row r="2" spans="1:9" ht="23.25">
       <c r="A2" s="91" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="18.75">
       <c r="A3" s="79" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="35.25">
@@ -8120,7 +8135,7 @@
         <v>9</v>
       </c>
       <c r="H5" s="82" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="I5" s="81" t="s">
         <v>11</v>
@@ -8150,7 +8165,7 @@
       </c>
       <c r="H6" s="85"/>
       <c r="I6" s="84" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="18.75">
@@ -8220,7 +8235,7 @@
         <v>198</v>
       </c>
       <c r="D9" s="94" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E9" s="94">
         <v>8</v>
@@ -8235,7 +8250,7 @@
         <v>206</v>
       </c>
       <c r="I9" s="86" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="18.75">
@@ -8282,14 +8297,14 @@
         <v>10</v>
       </c>
       <c r="F11" s="87" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="G11" s="87" t="s">
         <v>68</v>
       </c>
       <c r="H11" s="87"/>
       <c r="I11" s="86" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="18.75">
@@ -8318,7 +8333,7 @@
         <v>31</v>
       </c>
       <c r="I12" s="86" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="18.75">
@@ -8338,7 +8353,7 @@
         <v>12</v>
       </c>
       <c r="F13" s="87" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="G13" s="87"/>
       <c r="H13" s="87"/>
@@ -8361,7 +8376,7 @@
         <v>13</v>
       </c>
       <c r="F14" s="90" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="G14" s="90" t="s">
         <v>77</v>

--- a/data/MACSI seminar series.xlsx
+++ b/data/MACSI seminar series.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29912"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29917"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ulcampus-my.sharepoint.com/personal/david_osullivan_ul_ie/Documents/Academic_work/_Misc/MACSI Seminars/macsi-seminars.github.io/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="362" documentId="13_ncr:1_{12BE53B5-C8C7-44FE-8280-19C653D9122E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C389BF6-7B71-4379-89DC-61D8349F7487}"/>
+  <xr:revisionPtr revIDLastSave="379" documentId="13_ncr:1_{12BE53B5-C8C7-44FE-8280-19C653D9122E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46B3E0D4-3D9E-48F0-9E3C-83567FBEBCA1}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1021" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1029" uniqueCount="427">
   <si>
     <t>Fill in as much of the green boxes as possible. Ideally, this would be before you have finished your visitors travel dates (just to avoid double booking).</t>
   </si>
@@ -1219,6 +1219,13 @@
     <t>Carl Scarrott</t>
   </si>
   <si>
+    <t>Bayes-ically Fair:  Bayesian Ranking of Olympic Medal Performances</t>
+  </si>
+  <si>
+    <t>Evaluating a country's sporting success can provide insight into its decision-making and the infrastructure used to develop athletic talent. The Olympic Games serve as a global benchmark, yet conventional medal tables can be overly influenced by population size or highly variable, particularly for smaller nations where outcomes are more affected by stochastic fluctuations.
+We propose a Bayesian ranking scheme to rank the performance of National Olympic Committees by inferring an underlying `long-run' medals-to-population rate. The approach applies shrinkage to stabilise estimates for small-population countries while leaving large-population countries comparatively unchanged. The Bayesian framework yields posterior distributions over both the inferred medals-per-capita performance and the induced ranks, providing a principled measure of uncertainty in each country's ranking position.</t>
+  </si>
+  <si>
     <t>https://scholar.google.com/citations?user=kRgtZZcAAAAJ&amp;hl=en</t>
   </si>
   <si>
@@ -1228,10 +1235,16 @@
     <t>Andrew Keane</t>
   </si>
   <si>
+    <t>May</t>
+  </si>
+  <si>
+    <t>Alan Demlow</t>
+  </si>
+  <si>
+    <t>Texas A&amp;M</t>
+  </si>
+  <si>
     <t>Open</t>
-  </si>
-  <si>
-    <t>May</t>
   </si>
   <si>
     <t>This is a just a place for those who are interested but that dont have a specific date in mind. (Ideally, a couple of these are people that we could invite with relatively short notice to fill missing slots.)</t>
@@ -6958,7 +6971,7 @@
       <c r="X11" s="15"/>
       <c r="Y11" s="13"/>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:25" ht="16.5" customHeight="1">
       <c r="A12" s="75">
         <v>46128</v>
       </c>
@@ -6986,17 +6999,17 @@
         <v>78</v>
       </c>
       <c r="I12" s="98" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="J12" s="98" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="K12" s="102" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="L12" s="5"/>
       <c r="M12" s="24" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="N12" s="16"/>
       <c r="O12" s="35"/>
@@ -7028,7 +7041,7 @@
         <v>13</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="G13" s="14" t="s">
         <v>73</v>
@@ -7059,9 +7072,36 @@
       <c r="Y13" s="13"/>
     </row>
     <row r="14" spans="1:25">
-      <c r="A14" s="26"/>
-      <c r="B14" s="26"/>
-      <c r="C14" s="26"/>
+      <c r="A14" s="26">
+        <v>46156</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>190</v>
+      </c>
+      <c r="C14" s="26" t="s">
+        <v>375</v>
+      </c>
+      <c r="D14" t="s">
+        <v>278</v>
+      </c>
+      <c r="E14">
+        <v>16</v>
+      </c>
+      <c r="F14" t="s">
+        <v>376</v>
+      </c>
+      <c r="G14" t="s">
+        <v>377</v>
+      </c>
+      <c r="H14" t="s">
+        <v>40</v>
+      </c>
+      <c r="I14" t="s">
+        <v>363</v>
+      </c>
+      <c r="J14" t="s">
+        <v>363</v>
+      </c>
       <c r="X14" s="20"/>
       <c r="Y14" s="18"/>
     </row>
@@ -7244,7 +7284,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="G3" s="14" t="s">
         <v>363</v>
@@ -7295,7 +7335,7 @@
         <v>3</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="G4" s="14" t="s">
         <v>363</v>
@@ -7346,7 +7386,7 @@
         <v>5</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="G5" s="14" t="s">
         <v>363</v>
@@ -7401,7 +7441,7 @@
         <v>7</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="G6" s="14" t="s">
         <v>363</v>
@@ -7452,7 +7492,7 @@
         <v>9</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="G7" s="14" t="s">
         <v>363</v>
@@ -7501,7 +7541,7 @@
         <v>11</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="G8" s="14" t="s">
         <v>363</v>
@@ -7539,7 +7579,7 @@
         <v>190</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D9" s="27" t="s">
         <v>278</v>
@@ -7548,7 +7588,7 @@
         <v>13</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="G9" s="14" t="s">
         <v>363</v>
@@ -7626,23 +7666,23 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="55" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B2" s="54" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="C2" s="54" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="136" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="B3" s="137"/>
       <c r="C3" s="138" t="s">
@@ -7651,7 +7691,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="5" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="B4" s="52"/>
       <c r="C4" s="50" t="s">
@@ -7660,19 +7700,19 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="52" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B5" s="52"/>
       <c r="C5" s="50" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="52" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B6" s="52" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="C6" s="50" t="s">
         <v>87</v>
@@ -7680,10 +7720,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="52" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B7" s="52" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="C7" s="50" t="s">
         <v>87</v>
@@ -7691,10 +7731,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="52" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B8" s="52" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C8" s="50" t="s">
         <v>101</v>
@@ -7702,75 +7742,75 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="52" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B9" s="52"/>
       <c r="C9" s="50"/>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="52" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B10" s="52" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="C10" s="50" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="52" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="B11" s="52" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="C11" s="50" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="52" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="B12" s="52" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="C12" s="50" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="52" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="B13" s="52" t="s">
+        <v>403</v>
+      </c>
+      <c r="C13" s="50" t="s">
         <v>399</v>
-      </c>
-      <c r="C13" s="50" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="52" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="B14" s="52" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="C14" s="50" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="52" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B15" s="52" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C15" s="50" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -7778,10 +7818,10 @@
         <v>321</v>
       </c>
       <c r="B16" s="137" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="C16" s="139" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -7789,18 +7829,18 @@
         <v>346</v>
       </c>
       <c r="B17" s="137" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="C17" s="139" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="52" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="B18" s="52" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="C18" s="50" t="s">
         <v>87</v>
@@ -7808,21 +7848,21 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="53" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B19" s="53" t="s">
         <v>230</v>
       </c>
       <c r="C19" s="51" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B20" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
   </sheetData>
@@ -7849,10 +7889,10 @@
         <v>3</v>
       </c>
       <c r="B1" s="131" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="C1" s="130" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -7863,7 +7903,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="170" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="F2" s="75"/>
       <c r="G2" s="77"/>
@@ -7880,7 +7920,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="170" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="F3" s="75"/>
       <c r="G3" s="2"/>
@@ -7897,7 +7937,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="170" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="F4" s="75"/>
       <c r="G4" s="2"/>
@@ -7914,7 +7954,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="170" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="F5" s="75"/>
       <c r="G5" s="2"/>
@@ -7931,7 +7971,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="134" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="F6" s="75"/>
       <c r="G6" s="2"/>
@@ -7948,7 +7988,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="134" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="F7" s="75"/>
       <c r="G7" s="2"/>
@@ -7965,7 +8005,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="134" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="F8" s="75"/>
       <c r="G8" s="2"/>
@@ -7982,7 +8022,7 @@
         <v>8</v>
       </c>
       <c r="C9" s="134" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="F9" s="75"/>
       <c r="G9" s="2"/>
@@ -7999,7 +8039,7 @@
         <v>9</v>
       </c>
       <c r="C10" s="134" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="F10" s="75"/>
       <c r="G10" s="2"/>
@@ -8016,7 +8056,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="134" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -8029,7 +8069,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="134" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -8042,7 +8082,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="134" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -8055,7 +8095,7 @@
         <v>13</v>
       </c>
       <c r="C14" s="134" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -8104,12 +8144,12 @@
   <sheetData>
     <row r="2" spans="1:9" ht="23.25">
       <c r="A2" s="91" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="18.75">
       <c r="A3" s="79" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="35.25">
@@ -8135,7 +8175,7 @@
         <v>9</v>
       </c>
       <c r="H5" s="82" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="I5" s="81" t="s">
         <v>11</v>
@@ -8235,7 +8275,7 @@
         <v>198</v>
       </c>
       <c r="D9" s="94" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="E9" s="94">
         <v>8</v>
@@ -8297,7 +8337,7 @@
         <v>10</v>
       </c>
       <c r="F11" s="87" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="G11" s="87" t="s">
         <v>68</v>
@@ -8353,7 +8393,7 @@
         <v>12</v>
       </c>
       <c r="F13" s="87" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="G13" s="87"/>
       <c r="H13" s="87"/>
@@ -8376,7 +8416,7 @@
         <v>13</v>
       </c>
       <c r="F14" s="90" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="G14" s="90" t="s">
         <v>77</v>

--- a/data/MACSI seminar series.xlsx
+++ b/data/MACSI seminar series.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ulcampus-my.sharepoint.com/personal/david_osullivan_ul_ie/Documents/Academic_work/_Misc/MACSI Seminars/macsi-seminars.github.io/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="379" documentId="13_ncr:1_{12BE53B5-C8C7-44FE-8280-19C653D9122E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46B3E0D4-3D9E-48F0-9E3C-83567FBEBCA1}"/>
+  <xr:revisionPtr revIDLastSave="384" documentId="13_ncr:1_{12BE53B5-C8C7-44FE-8280-19C653D9122E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCC967C4-95DF-48D7-8A3B-9B5914B78022}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1029" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1029" uniqueCount="429">
   <si>
     <t>Fill in as much of the green boxes as possible. Ideally, this would be before you have finished your visitors travel dates (just to avoid double booking).</t>
   </si>
@@ -1198,7 +1198,10 @@
     <t xml:space="preserve">Chris Howland </t>
   </si>
   <si>
-    <t>TBC</t>
+    <t>Convection and phase changes in environmental flows</t>
+  </si>
+  <si>
+    <t>Many processes in the climate system can be related to the coupling of fluid convection and thermodynamic phase changes, from ice-ocean interactions in polar regions to the formation and evolution of clouds in the atmosphere. In this talk, I will discuss some recent work aimed at understanding the fundamental interactions between convection and phase changes in simple systems, with a focus on the effects of turbulence on ice melting. Firstly, motivated by the flows beside marine-terminating glaciers, I will describe work focused on understanding boundary layers in turbulent convection at vertical walls. I focus on the complexities introduced by a high Prandtl number (relevant to seawater) and the effect of an ambient flow, where a transition between buoyancy-driven and shear-driven boundary layers occurs. Secondly, I will outline a newly-developed immersed boundary technique for simulating melting objects in turbulent flows, which reveals the subtle effects that the free motion of melting ice objects can introduce.</t>
   </si>
   <si>
     <t>Michel Destrade</t>
@@ -1233,6 +1236,9 @@
   </si>
   <si>
     <t>Andrew Keane</t>
+  </si>
+  <si>
+    <t>TBC</t>
   </si>
   <si>
     <t>May</t>
@@ -6871,7 +6877,7 @@
       <c r="X9" s="15"/>
       <c r="Y9" s="13"/>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" ht="15" customHeight="1">
       <c r="A10" s="75">
         <v>46120</v>
       </c>
@@ -6902,7 +6908,7 @@
         <v>363</v>
       </c>
       <c r="J10" s="98" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K10" s="102"/>
       <c r="L10" s="5"/>
@@ -6937,7 +6943,7 @@
         <v>11</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G11" s="14" t="s">
         <v>195</v>
@@ -6946,17 +6952,17 @@
         <v>87</v>
       </c>
       <c r="I11" s="98" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="J11" s="98" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="K11" s="102" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L11" s="5"/>
       <c r="M11" s="24" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N11" s="16"/>
       <c r="O11" s="35"/>
@@ -6990,7 +6996,7 @@
         <v>12</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="G12" s="14" t="s">
         <v>195</v>
@@ -6999,17 +7005,17 @@
         <v>78</v>
       </c>
       <c r="I12" s="98" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="J12" s="98" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="K12" s="102" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L12" s="5"/>
       <c r="M12" s="24" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N12" s="16"/>
       <c r="O12" s="35"/>
@@ -7041,7 +7047,7 @@
         <v>13</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="G13" s="14" t="s">
         <v>73</v>
@@ -7050,10 +7056,10 @@
         <v>95</v>
       </c>
       <c r="I13" s="98" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="J13" s="98" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="K13" s="102"/>
       <c r="L13" s="5"/>
@@ -7079,7 +7085,7 @@
         <v>190</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D14" t="s">
         <v>278</v>
@@ -7088,19 +7094,19 @@
         <v>16</v>
       </c>
       <c r="F14" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="G14" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="H14" t="s">
         <v>40</v>
       </c>
       <c r="I14" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="J14" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="X14" s="20"/>
       <c r="Y14" s="18"/>
@@ -7284,19 +7290,19 @@
         <v>1</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="H3" s="14" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="I3" s="98" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="J3" s="98" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="K3" s="73"/>
       <c r="L3" s="40"/>
@@ -7335,19 +7341,19 @@
         <v>3</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="I4" s="98" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="J4" s="98" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="K4" s="102"/>
       <c r="L4" s="5"/>
@@ -7386,19 +7392,19 @@
         <v>5</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="I5" s="98" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="J5" s="98" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="K5" s="102"/>
       <c r="L5" s="5"/>
@@ -7441,19 +7447,19 @@
         <v>7</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="I6" s="98" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="J6" s="98" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="K6" s="102"/>
       <c r="L6" s="5"/>
@@ -7492,19 +7498,19 @@
         <v>9</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="I7" s="98" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="J7" s="98" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="K7" s="102"/>
       <c r="L7" s="5"/>
@@ -7541,19 +7547,19 @@
         <v>11</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="I8" s="98" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="J8" s="98" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="K8" s="102"/>
       <c r="L8" s="5"/>
@@ -7579,7 +7585,7 @@
         <v>190</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D9" s="27" t="s">
         <v>278</v>
@@ -7588,19 +7594,19 @@
         <v>13</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="I9" s="98" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="J9" s="98" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="K9" s="102"/>
       <c r="L9" s="5"/>
@@ -7666,23 +7672,23 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="55" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B2" s="54" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C2" s="54" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="136" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B3" s="137"/>
       <c r="C3" s="138" t="s">
@@ -7691,7 +7697,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="5" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B4" s="52"/>
       <c r="C4" s="50" t="s">
@@ -7700,19 +7706,19 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="52" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B5" s="52"/>
       <c r="C5" s="50" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="52" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B6" s="52" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C6" s="50" t="s">
         <v>87</v>
@@ -7720,10 +7726,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="52" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B7" s="52" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C7" s="50" t="s">
         <v>87</v>
@@ -7731,10 +7737,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="52" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B8" s="52" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C8" s="50" t="s">
         <v>101</v>
@@ -7742,75 +7748,75 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="52" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B9" s="52"/>
       <c r="C9" s="50"/>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="52" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B10" s="52" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C10" s="50" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="52" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B11" s="52" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C11" s="50" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="52" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B12" s="52" t="s">
+        <v>403</v>
+      </c>
+      <c r="C12" s="50" t="s">
         <v>401</v>
-      </c>
-      <c r="C12" s="50" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="52" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B13" s="52" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C13" s="50" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="52" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B14" s="52" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C14" s="50" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="52" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B15" s="52" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C15" s="50" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -7818,10 +7824,10 @@
         <v>321</v>
       </c>
       <c r="B16" s="137" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C16" s="139" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -7829,18 +7835,18 @@
         <v>346</v>
       </c>
       <c r="B17" s="137" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C17" s="139" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="52" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B18" s="52" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C18" s="50" t="s">
         <v>87</v>
@@ -7848,21 +7854,21 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="53" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B19" s="53" t="s">
         <v>230</v>
       </c>
       <c r="C19" s="51" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B20" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
   </sheetData>
@@ -7889,10 +7895,10 @@
         <v>3</v>
       </c>
       <c r="B1" s="131" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C1" s="130" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -7903,7 +7909,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="170" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="F2" s="75"/>
       <c r="G2" s="77"/>
@@ -7920,7 +7926,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="170" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F3" s="75"/>
       <c r="G3" s="2"/>
@@ -7937,7 +7943,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="170" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="F4" s="75"/>
       <c r="G4" s="2"/>
@@ -7954,7 +7960,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="170" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F5" s="75"/>
       <c r="G5" s="2"/>
@@ -7971,7 +7977,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="134" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="F6" s="75"/>
       <c r="G6" s="2"/>
@@ -7988,7 +7994,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="134" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F7" s="75"/>
       <c r="G7" s="2"/>
@@ -8005,7 +8011,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="134" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="F8" s="75"/>
       <c r="G8" s="2"/>
@@ -8022,7 +8028,7 @@
         <v>8</v>
       </c>
       <c r="C9" s="134" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="F9" s="75"/>
       <c r="G9" s="2"/>
@@ -8039,7 +8045,7 @@
         <v>9</v>
       </c>
       <c r="C10" s="134" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="F10" s="75"/>
       <c r="G10" s="2"/>
@@ -8056,7 +8062,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="134" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -8069,7 +8075,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="134" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -8082,7 +8088,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="134" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -8095,7 +8101,7 @@
         <v>13</v>
       </c>
       <c r="C14" s="134" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -8144,12 +8150,12 @@
   <sheetData>
     <row r="2" spans="1:9" ht="23.25">
       <c r="A2" s="91" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="18.75">
       <c r="A3" s="79" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="35.25">
@@ -8175,7 +8181,7 @@
         <v>9</v>
       </c>
       <c r="H5" s="82" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="I5" s="81" t="s">
         <v>11</v>
@@ -8205,7 +8211,7 @@
       </c>
       <c r="H6" s="85"/>
       <c r="I6" s="84" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="18.75">
@@ -8275,7 +8281,7 @@
         <v>198</v>
       </c>
       <c r="D9" s="94" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E9" s="94">
         <v>8</v>
@@ -8290,7 +8296,7 @@
         <v>206</v>
       </c>
       <c r="I9" s="86" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="18.75">
@@ -8337,14 +8343,14 @@
         <v>10</v>
       </c>
       <c r="F11" s="87" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G11" s="87" t="s">
         <v>68</v>
       </c>
       <c r="H11" s="87"/>
       <c r="I11" s="86" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="18.75">
@@ -8373,7 +8379,7 @@
         <v>31</v>
       </c>
       <c r="I12" s="86" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="18.75">
@@ -8393,7 +8399,7 @@
         <v>12</v>
       </c>
       <c r="F13" s="87" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="G13" s="87"/>
       <c r="H13" s="87"/>
@@ -8416,7 +8422,7 @@
         <v>13</v>
       </c>
       <c r="F14" s="90" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="G14" s="90" t="s">
         <v>77</v>

--- a/data/MACSI seminar series.xlsx
+++ b/data/MACSI seminar series.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29917"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29926"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ulcampus-my.sharepoint.com/personal/david_osullivan_ul_ie/Documents/Academic_work/_Misc/MACSI Seminars/macsi-seminars.github.io/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="384" documentId="13_ncr:1_{12BE53B5-C8C7-44FE-8280-19C653D9122E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCC967C4-95DF-48D7-8A3B-9B5914B78022}"/>
+  <xr:revisionPtr revIDLastSave="392" documentId="13_ncr:1_{12BE53B5-C8C7-44FE-8280-19C653D9122E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51A9EAEF-0951-4703-811A-ACF692EA70E2}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1029" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1030" uniqueCount="430">
   <si>
     <t>Fill in as much of the green boxes as possible. Ideally, this would be before you have finished your visitors travel dates (just to avoid double booking).</t>
   </si>
@@ -1239,6 +1239,9 @@
   </si>
   <si>
     <t>TBC</t>
+  </si>
+  <si>
+    <t>4pm</t>
   </si>
   <si>
     <t>May</t>
@@ -1935,7 +1938,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="172">
+  <cellXfs count="176">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -2222,6 +2225,12 @@
     <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="11" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -6390,7 +6399,7 @@
   <sheetPr>
     <tabColor theme="9"/>
   </sheetPr>
-  <dimension ref="A1:Y17"/>
+  <dimension ref="A1:Y18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.5703125" customWidth="1"/>
@@ -7077,46 +7086,71 @@
       <c r="X13" s="15"/>
       <c r="Y13" s="13"/>
     </row>
-    <row r="14" spans="1:25">
-      <c r="A14" s="26">
+    <row r="14" spans="1:25" ht="18.75" customHeight="1">
+      <c r="A14" s="75">
+        <v>46142</v>
+      </c>
+      <c r="B14" s="172" t="s">
+        <v>377</v>
+      </c>
+      <c r="C14" s="26"/>
+      <c r="D14" s="173"/>
+      <c r="F14" s="174"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="174"/>
+      <c r="I14" s="175"/>
+      <c r="J14" s="175"/>
+      <c r="K14" s="102"/>
+      <c r="L14" s="174"/>
+      <c r="M14" s="174"/>
+      <c r="N14" s="174"/>
+      <c r="O14" s="35"/>
+      <c r="P14" s="174"/>
+      <c r="Q14" s="174"/>
+      <c r="R14" s="174"/>
+      <c r="S14" s="174"/>
+      <c r="T14" s="35"/>
+      <c r="U14" s="174"/>
+      <c r="V14" s="174"/>
+      <c r="W14" s="174"/>
+      <c r="X14" s="15"/>
+      <c r="Y14" s="13"/>
+    </row>
+    <row r="15" spans="1:25">
+      <c r="A15" s="26">
         <v>46156</v>
       </c>
-      <c r="B14" s="26" t="s">
+      <c r="B15" s="26" t="s">
         <v>190</v>
       </c>
-      <c r="C14" s="26" t="s">
-        <v>377</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="C15" s="26" t="s">
+        <v>378</v>
+      </c>
+      <c r="D15" t="s">
         <v>278</v>
       </c>
-      <c r="E14">
+      <c r="E15">
         <v>16</v>
       </c>
-      <c r="F14" t="s">
-        <v>378</v>
-      </c>
-      <c r="G14" t="s">
+      <c r="F15" t="s">
         <v>379</v>
       </c>
-      <c r="H14" t="s">
+      <c r="G15" t="s">
+        <v>380</v>
+      </c>
+      <c r="H15" t="s">
         <v>40</v>
       </c>
-      <c r="I14" t="s">
+      <c r="I15" t="s">
         <v>376</v>
       </c>
-      <c r="J14" t="s">
+      <c r="J15" t="s">
         <v>376</v>
       </c>
-      <c r="X14" s="20"/>
-      <c r="Y14" s="18"/>
-    </row>
-    <row r="15" spans="1:25" ht="12.75" customHeight="1">
-      <c r="A15" s="26"/>
-      <c r="B15" s="26"/>
-      <c r="C15" s="26"/>
-    </row>
-    <row r="16" spans="1:25">
+      <c r="X15" s="20"/>
+      <c r="Y15" s="18"/>
+    </row>
+    <row r="16" spans="1:25" ht="12.75" customHeight="1">
       <c r="A16" s="26"/>
       <c r="B16" s="26"/>
       <c r="C16" s="26"/>
@@ -7126,13 +7160,18 @@
       <c r="B17" s="26"/>
       <c r="C17" s="26"/>
     </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="26"/>
+      <c r="B18" s="26"/>
+      <c r="C18" s="26"/>
+    </row>
   </sheetData>
   <protectedRanges>
-    <protectedRange algorithmName="SHA-512" hashValue="pQyTzP/d7t5ThMimBt5mu8gGozgAm1OwF6BMILsn5/kmtZ5mZf81NMi09wwU8mvtItxf0EVNWa6V4MCa0DKeSQ==" saltValue="NzZBiAQ1yFjat+SeIqh2Uw==" spinCount="100000" sqref="A3:E17" name="Range3_1"/>
+    <protectedRange algorithmName="SHA-512" hashValue="pQyTzP/d7t5ThMimBt5mu8gGozgAm1OwF6BMILsn5/kmtZ5mZf81NMi09wwU8mvtItxf0EVNWa6V4MCa0DKeSQ==" saltValue="NzZBiAQ1yFjat+SeIqh2Uw==" spinCount="100000" sqref="A3:E18" name="Range3_1"/>
     <protectedRange algorithmName="SHA-512" hashValue="JNB4nrqrfZD45ijUCOmyuk44ibTGOz2xPKKqUb8Fu6IzynfOW0Plt2J4MjvTXFpCm0cEkYqWWfoKwgUFnGztPw==" saltValue="gktf/myRKhBCN9s2pCislA==" spinCount="100000" sqref="A2:L2 N2:Y2" name="Range4_1"/>
-    <protectedRange algorithmName="SHA-512" hashValue="B/N8xqtMc7pXr3rfrr4k91A6IFAPX6lxEHUr9qsJ3yHA+MBnFuw+x27DjsTYKp86iL5C7QQh1TPFTQHueWpZbw==" saltValue="c0IR/echnZmip5yS1t29Rw==" spinCount="100000" sqref="T3:T13" name="Range6_1"/>
-    <protectedRange algorithmName="SHA-512" hashValue="BKDH3ki5lE3XQdc5qZnIH6o8wW8E0PkHgMZFCkv/XYDEa+b/qenui0oReDIqPDXHceUVJ+rEgU3I9CDBHraDYg==" saltValue="ruXqG4NOhhm7cSLor8wHfw==" spinCount="100000" sqref="O2:O13" name="Range7_1"/>
-    <protectedRange sqref="X14:Y14 F3:Y13" name="Range8_1"/>
+    <protectedRange algorithmName="SHA-512" hashValue="B/N8xqtMc7pXr3rfrr4k91A6IFAPX6lxEHUr9qsJ3yHA+MBnFuw+x27DjsTYKp86iL5C7QQh1TPFTQHueWpZbw==" saltValue="c0IR/echnZmip5yS1t29Rw==" spinCount="100000" sqref="T3:T14" name="Range6_1"/>
+    <protectedRange algorithmName="SHA-512" hashValue="BKDH3ki5lE3XQdc5qZnIH6o8wW8E0PkHgMZFCkv/XYDEa+b/qenui0oReDIqPDXHceUVJ+rEgU3I9CDBHraDYg==" saltValue="ruXqG4NOhhm7cSLor8wHfw==" spinCount="100000" sqref="O2:O14" name="Range7_1"/>
+    <protectedRange sqref="X15:Y15 F3:Y14" name="Range8_1"/>
     <protectedRange algorithmName="SHA-512" hashValue="JNB4nrqrfZD45ijUCOmyuk44ibTGOz2xPKKqUb8Fu6IzynfOW0Plt2J4MjvTXFpCm0cEkYqWWfoKwgUFnGztPw==" saltValue="gktf/myRKhBCN9s2pCislA==" spinCount="100000" sqref="M2" name="Range4_1_1"/>
   </protectedRanges>
   <hyperlinks>
@@ -7290,7 +7329,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="G3" s="14" t="s">
         <v>376</v>
@@ -7341,7 +7380,7 @@
         <v>3</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="G4" s="14" t="s">
         <v>376</v>
@@ -7392,7 +7431,7 @@
         <v>5</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="G5" s="14" t="s">
         <v>376</v>
@@ -7447,7 +7486,7 @@
         <v>7</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="G6" s="14" t="s">
         <v>376</v>
@@ -7498,7 +7537,7 @@
         <v>9</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="G7" s="14" t="s">
         <v>376</v>
@@ -7547,7 +7586,7 @@
         <v>11</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="G8" s="14" t="s">
         <v>376</v>
@@ -7585,7 +7624,7 @@
         <v>190</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D9" s="27" t="s">
         <v>278</v>
@@ -7594,7 +7633,7 @@
         <v>13</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="G9" s="14" t="s">
         <v>376</v>
@@ -7672,23 +7711,23 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="55" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B2" s="54" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C2" s="54" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="136" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B3" s="137"/>
       <c r="C3" s="138" t="s">
@@ -7697,7 +7736,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B4" s="52"/>
       <c r="C4" s="50" t="s">
@@ -7706,19 +7745,19 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="52" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B5" s="52"/>
       <c r="C5" s="50" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="52" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B6" s="52" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C6" s="50" t="s">
         <v>87</v>
@@ -7726,10 +7765,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="52" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B7" s="52" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C7" s="50" t="s">
         <v>87</v>
@@ -7737,10 +7776,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="52" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B8" s="52" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C8" s="50" t="s">
         <v>101</v>
@@ -7748,75 +7787,75 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="52" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B9" s="52"/>
       <c r="C9" s="50"/>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="52" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B10" s="52" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C10" s="50" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="52" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B11" s="52" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C11" s="50" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="52" t="s">
+        <v>403</v>
+      </c>
+      <c r="B12" s="52" t="s">
+        <v>404</v>
+      </c>
+      <c r="C12" s="50" t="s">
         <v>402</v>
-      </c>
-      <c r="B12" s="52" t="s">
-        <v>403</v>
-      </c>
-      <c r="C12" s="50" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="52" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B13" s="52" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C13" s="50" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="52" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B14" s="52" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C14" s="50" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="52" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B15" s="52" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C15" s="50" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -7824,10 +7863,10 @@
         <v>321</v>
       </c>
       <c r="B16" s="137" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C16" s="139" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -7835,18 +7874,18 @@
         <v>346</v>
       </c>
       <c r="B17" s="137" t="s">
+        <v>413</v>
+      </c>
+      <c r="C17" s="139" t="s">
         <v>412</v>
-      </c>
-      <c r="C17" s="139" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="52" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B18" s="52" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C18" s="50" t="s">
         <v>87</v>
@@ -7854,21 +7893,21 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="53" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B19" s="53" t="s">
         <v>230</v>
       </c>
       <c r="C19" s="51" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B20" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
   </sheetData>
@@ -7895,10 +7934,10 @@
         <v>3</v>
       </c>
       <c r="B1" s="131" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C1" s="130" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -7909,7 +7948,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="170" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F2" s="75"/>
       <c r="G2" s="77"/>
@@ -7926,7 +7965,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="170" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F3" s="75"/>
       <c r="G3" s="2"/>
@@ -7943,7 +7982,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="170" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F4" s="75"/>
       <c r="G4" s="2"/>
@@ -7960,7 +7999,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="170" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F5" s="75"/>
       <c r="G5" s="2"/>
@@ -7977,7 +8016,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="134" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F6" s="75"/>
       <c r="G6" s="2"/>
@@ -7994,7 +8033,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="134" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F7" s="75"/>
       <c r="G7" s="2"/>
@@ -8011,7 +8050,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="134" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F8" s="75"/>
       <c r="G8" s="2"/>
@@ -8028,7 +8067,7 @@
         <v>8</v>
       </c>
       <c r="C9" s="134" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F9" s="75"/>
       <c r="G9" s="2"/>
@@ -8045,7 +8084,7 @@
         <v>9</v>
       </c>
       <c r="C10" s="134" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F10" s="75"/>
       <c r="G10" s="2"/>
@@ -8062,7 +8101,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="134" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -8075,7 +8114,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="134" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -8088,7 +8127,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="134" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -8101,7 +8140,7 @@
         <v>13</v>
       </c>
       <c r="C14" s="134" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -8150,12 +8189,12 @@
   <sheetData>
     <row r="2" spans="1:9" ht="23.25">
       <c r="A2" s="91" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="18.75">
       <c r="A3" s="79" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="35.25">
@@ -8181,7 +8220,7 @@
         <v>9</v>
       </c>
       <c r="H5" s="82" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="I5" s="81" t="s">
         <v>11</v>
@@ -8281,7 +8320,7 @@
         <v>198</v>
       </c>
       <c r="D9" s="94" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E9" s="94">
         <v>8</v>
@@ -8343,7 +8382,7 @@
         <v>10</v>
       </c>
       <c r="F11" s="87" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="G11" s="87" t="s">
         <v>68</v>
@@ -8399,7 +8438,7 @@
         <v>12</v>
       </c>
       <c r="F13" s="87" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="G13" s="87"/>
       <c r="H13" s="87"/>
@@ -8422,7 +8461,7 @@
         <v>13</v>
       </c>
       <c r="F14" s="90" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="G14" s="90" t="s">
         <v>77</v>

--- a/data/MACSI seminar series.xlsx
+++ b/data/MACSI seminar series.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29926"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ulcampus-my.sharepoint.com/personal/david_osullivan_ul_ie/Documents/Academic_work/_Misc/MACSI Seminars/macsi-seminars.github.io/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="392" documentId="13_ncr:1_{12BE53B5-C8C7-44FE-8280-19C653D9122E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51A9EAEF-0951-4703-811A-ACF692EA70E2}"/>
+  <xr:revisionPtr revIDLastSave="413" documentId="13_ncr:1_{12BE53B5-C8C7-44FE-8280-19C653D9122E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55AEEDAA-4922-4987-932D-61D57203D954}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1030" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="437">
   <si>
     <t>Fill in as much of the green boxes as possible. Ideally, this would be before you have finished your visitors travel dates (just to avoid double booking).</t>
   </si>
@@ -1247,6 +1247,12 @@
     <t>May</t>
   </si>
   <si>
+    <t>Florian Faucher</t>
+  </si>
+  <si>
+    <t>University of Pau and Pays de l’Adour</t>
+  </si>
+  <si>
     <t>Alan Demlow</t>
   </si>
   <si>
@@ -1398,6 +1404,21 @@
   </si>
   <si>
     <t>Leornard Henckel</t>
+  </si>
+  <si>
+    <t>Romina Gaburro</t>
+  </si>
+  <si>
+    <t>Quantitative inverse wave problem for passive imaging using cross-correlation data.</t>
+  </si>
+  <si>
+    <t>We investigate the quantitative reconstruction of physical properties in the context of passive imaging, where ambient wavefields are used to probe a medium. These ambient signals correspond to oscillations of the system generated by stochastic events. We discuss in particular  helioseismology, where satellites observe solar oscillations that are driven by turbulent convective motion. Considering the data as a superposition of waves generated by stochastic sources, the expected value of the cross-correlation between signals is related to the deterministic Green's function. The inverse wave problem is then formulated through an iterative minimization procedure, in which the gradient of the misfit functional is computed via the adjoint-state method. We focus on time-harmonic acoustic wave propagation and carry out synthetic experiments, comparing inversions based on cross-correlation data with those using direct wavefield measurements in the configuration of active-source acquisitions.</t>
+  </si>
+  <si>
+    <t>https://ffaucher.gitlab.io/cv/</t>
+  </si>
+  <si>
+    <t>https://scholar.google.com/citations?user=KKQ8FvkAAAAJ&amp;hl=en</t>
   </si>
 </sst>
 </file>
@@ -1407,7 +1428,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1938,7 +1959,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="176">
+  <cellXfs count="172">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -2225,12 +2246,6 @@
     <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="11" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2271,9 +2286,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2311,7 +2326,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2417,7 +2432,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2559,7 +2574,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2568,7 +2583,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7958562-D4BB-4776-9668-682A6F2E2AD0}">
   <dimension ref="A1:Y20"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="11.140625" customWidth="1"/>
@@ -2593,7 +2608,7 @@
     <col min="25" max="25" width="37.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2604,7 +2619,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="27.75">
+    <row r="2" spans="1:25" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -2681,7 +2696,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="13.5" customHeight="1">
+    <row r="3" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>45317</v>
       </c>
@@ -2748,7 +2763,7 @@
       <c r="X3" s="13"/>
       <c r="Y3" s="13"/>
     </row>
-    <row r="4" spans="1:25" ht="13.5" customHeight="1">
+    <row r="4" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>45323</v>
       </c>
@@ -2811,7 +2826,7 @@
       <c r="X4" s="13"/>
       <c r="Y4" s="13"/>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>45324</v>
       </c>
@@ -2872,7 +2887,7 @@
       <c r="X5" s="13"/>
       <c r="Y5" s="13"/>
     </row>
-    <row r="6" spans="1:25" ht="12.75" customHeight="1">
+    <row r="6" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>45331</v>
       </c>
@@ -2939,7 +2954,7 @@
       <c r="X6" s="13"/>
       <c r="Y6" s="13"/>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>45338</v>
       </c>
@@ -3008,7 +3023,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="15" customHeight="1">
+    <row r="8" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>45345</v>
       </c>
@@ -3075,7 +3090,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="16.5" customHeight="1">
+    <row r="9" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>45359</v>
       </c>
@@ -3128,7 +3143,7 @@
       <c r="X9" s="13"/>
       <c r="Y9" s="13"/>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>45366</v>
       </c>
@@ -3197,7 +3212,7 @@
       <c r="X10" s="13"/>
       <c r="Y10" s="13"/>
     </row>
-    <row r="11" spans="1:25" ht="15" customHeight="1">
+    <row r="11" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>45379</v>
       </c>
@@ -3258,7 +3273,7 @@
       <c r="X11" s="13"/>
       <c r="Y11" s="13"/>
     </row>
-    <row r="12" spans="1:25" ht="13.5" customHeight="1">
+    <row r="12" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>45386</v>
       </c>
@@ -3321,7 +3336,7 @@
       <c r="X12" s="13"/>
       <c r="Y12" s="13"/>
     </row>
-    <row r="13" spans="1:25" ht="16.5" customHeight="1">
+    <row r="13" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>45387</v>
       </c>
@@ -3390,7 +3405,7 @@
       <c r="X13" s="13"/>
       <c r="Y13" s="13"/>
     </row>
-    <row r="14" spans="1:25" ht="15.75" customHeight="1">
+    <row r="14" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>45394</v>
       </c>
@@ -3451,7 +3466,7 @@
       <c r="X14" s="13"/>
       <c r="Y14" s="13"/>
     </row>
-    <row r="15" spans="1:25" ht="17.25" customHeight="1">
+    <row r="15" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>45398</v>
       </c>
@@ -3520,7 +3535,7 @@
       <c r="X15" s="13"/>
       <c r="Y15" s="13"/>
     </row>
-    <row r="16" spans="1:25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>45401</v>
       </c>
@@ -3583,7 +3598,7 @@
       <c r="X16" s="18"/>
       <c r="Y16" s="18"/>
     </row>
-    <row r="17" spans="1:25">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>45421</v>
       </c>
@@ -3654,7 +3669,7 @@
       <c r="X17" s="18"/>
       <c r="Y17" s="18"/>
     </row>
-    <row r="18" spans="1:25">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" s="26">
         <v>45474</v>
       </c>
@@ -3705,7 +3720,7 @@
       <c r="X18" s="18"/>
       <c r="Y18" s="18"/>
     </row>
-    <row r="19" spans="1:25" ht="17.25" customHeight="1" thickBot="1">
+    <row r="19" spans="1:25" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="26">
         <v>45505</v>
       </c>
@@ -3756,7 +3771,7 @@
       <c r="X19" s="18"/>
       <c r="Y19" s="18"/>
     </row>
-    <row r="20" spans="1:25">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20" s="26"/>
       <c r="B20" s="26"/>
       <c r="C20" s="26"/>
@@ -3791,14 +3806,14 @@
     <hyperlink ref="K11" r:id="rId12" xr:uid="{CA02B488-FA07-461F-AA14-616AE99D302F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId13"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y44"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="11.140625" customWidth="1"/>
@@ -3823,7 +3838,7 @@
     <col min="25" max="25" width="37.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3834,7 +3849,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="28.5" thickBot="1">
+    <row r="2" spans="1:25" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="145" t="s">
         <v>3</v>
       </c>
@@ -3911,7 +3926,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15" customHeight="1">
+    <row r="3" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>45548</v>
       </c>
@@ -3976,7 +3991,7 @@
       <c r="X3" s="46"/>
       <c r="Y3" s="44"/>
     </row>
-    <row r="4" spans="1:25" ht="15" customHeight="1">
+    <row r="4" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>45555</v>
       </c>
@@ -4025,7 +4040,7 @@
       <c r="X4" s="15"/>
       <c r="Y4" s="13"/>
     </row>
-    <row r="5" spans="1:25" ht="15" customHeight="1">
+    <row r="5" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>45562</v>
       </c>
@@ -4074,7 +4089,7 @@
       <c r="X5" s="15"/>
       <c r="Y5" s="13"/>
     </row>
-    <row r="6" spans="1:25" ht="15" customHeight="1">
+    <row r="6" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>45576</v>
       </c>
@@ -4123,7 +4138,7 @@
       <c r="X6" s="15"/>
       <c r="Y6" s="13"/>
     </row>
-    <row r="7" spans="1:25" ht="15" customHeight="1">
+    <row r="7" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>45583</v>
       </c>
@@ -4172,7 +4187,7 @@
       <c r="X7" s="15"/>
       <c r="Y7" s="13"/>
     </row>
-    <row r="8" spans="1:25" ht="15" customHeight="1">
+    <row r="8" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>45596</v>
       </c>
@@ -4221,7 +4236,7 @@
       <c r="X8" s="15"/>
       <c r="Y8" s="13"/>
     </row>
-    <row r="9" spans="1:25" ht="15" customHeight="1">
+    <row r="9" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>45604</v>
       </c>
@@ -4270,7 +4285,7 @@
       <c r="X9" s="15"/>
       <c r="Y9" s="13"/>
     </row>
-    <row r="10" spans="1:25" ht="15" customHeight="1">
+    <row r="10" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>45611</v>
       </c>
@@ -4319,7 +4334,7 @@
       <c r="X10" s="15"/>
       <c r="Y10" s="13"/>
     </row>
-    <row r="11" spans="1:25" ht="15" customHeight="1">
+    <row r="11" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>45625</v>
       </c>
@@ -4368,7 +4383,7 @@
       <c r="X11" s="15"/>
       <c r="Y11" s="13"/>
     </row>
-    <row r="12" spans="1:25" ht="15" customHeight="1" thickBot="1">
+    <row r="12" spans="1:25" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
         <v>45632</v>
       </c>
@@ -4425,20 +4440,20 @@
       <c r="X12" s="20"/>
       <c r="Y12" s="18"/>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13" s="26"/>
       <c r="B13" s="26"/>
       <c r="C13" s="26"/>
       <c r="D13" s="26"/>
       <c r="I13" s="3"/>
     </row>
-    <row r="14" spans="1:25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" s="26"/>
       <c r="B14" s="26"/>
       <c r="C14" s="26"/>
       <c r="D14" s="26"/>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="61"/>
       <c r="B29" s="61"/>
       <c r="C29" s="61"/>
@@ -4450,59 +4465,59 @@
       <c r="I29" s="61"/>
       <c r="J29" s="61"/>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="60"/>
       <c r="B31" s="60"/>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="60"/>
       <c r="B32" s="60"/>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="60"/>
       <c r="B33" s="60"/>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="60"/>
       <c r="B34" s="60"/>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="60"/>
       <c r="B35" s="60"/>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="60"/>
       <c r="B36" s="60"/>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="60"/>
       <c r="B37" s="60"/>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="60"/>
       <c r="B38" s="60"/>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="60"/>
       <c r="B39" s="60"/>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="60"/>
       <c r="B40" s="60"/>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="60"/>
       <c r="B41" s="60"/>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="60"/>
       <c r="B42" s="60"/>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="60"/>
       <c r="B43" s="60"/>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="60"/>
       <c r="B44" s="60"/>
     </row>
@@ -4531,7 +4546,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12299A9A-6C0C-4F92-957E-FBFCB6211744}">
   <dimension ref="A1:Y45"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.5703125" customWidth="1"/>
     <col min="2" max="2" width="5.85546875" bestFit="1" customWidth="1"/>
@@ -4559,7 +4574,7 @@
     <col min="25" max="25" width="37.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4570,7 +4585,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="27.75" customHeight="1" thickBot="1">
+    <row r="2" spans="1:25" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="64" t="s">
         <v>3</v>
       </c>
@@ -4647,7 +4662,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15" customHeight="1">
+    <row r="3" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>45694</v>
       </c>
@@ -4699,7 +4714,7 @@
       <c r="X3" s="46"/>
       <c r="Y3" s="44"/>
     </row>
-    <row r="4" spans="1:25" ht="14.25" customHeight="1">
+    <row r="4" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>45708</v>
       </c>
@@ -4757,7 +4772,7 @@
       <c r="X4" s="15"/>
       <c r="Y4" s="13"/>
     </row>
-    <row r="5" spans="1:25" ht="14.25" customHeight="1">
+    <row r="5" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>45722</v>
       </c>
@@ -4813,7 +4828,7 @@
       <c r="X5" s="15"/>
       <c r="Y5" s="13"/>
     </row>
-    <row r="6" spans="1:25" ht="16.5" customHeight="1">
+    <row r="6" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>45735</v>
       </c>
@@ -4869,7 +4884,7 @@
       <c r="X6" s="15"/>
       <c r="Y6" s="13"/>
     </row>
-    <row r="7" spans="1:25" ht="18" customHeight="1">
+    <row r="7" spans="1:25" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>45750</v>
       </c>
@@ -4923,7 +4938,7 @@
       <c r="X7" s="15"/>
       <c r="Y7" s="13"/>
     </row>
-    <row r="8" spans="1:25" ht="16.5" customHeight="1">
+    <row r="8" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>45751</v>
       </c>
@@ -4982,7 +4997,7 @@
       <c r="X8" s="15"/>
       <c r="Y8" s="13"/>
     </row>
-    <row r="9" spans="1:25" ht="15.75" customHeight="1">
+    <row r="9" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>45757</v>
       </c>
@@ -5044,7 +5059,7 @@
       <c r="X9" s="15"/>
       <c r="Y9" s="13"/>
     </row>
-    <row r="10" spans="1:25" ht="15.75" customHeight="1">
+    <row r="10" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>45758</v>
       </c>
@@ -5098,7 +5113,7 @@
       <c r="X10" s="20"/>
       <c r="Y10" s="18"/>
     </row>
-    <row r="11" spans="1:25" ht="15.75" customHeight="1">
+    <row r="11" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>45764</v>
       </c>
@@ -5158,7 +5173,7 @@
       <c r="X11" s="35"/>
       <c r="Y11" s="35"/>
     </row>
-    <row r="12" spans="1:25" ht="15.75" customHeight="1">
+    <row r="12" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>45771</v>
       </c>
@@ -5219,7 +5234,7 @@
       <c r="X12" s="35"/>
       <c r="Y12" s="35"/>
     </row>
-    <row r="13" spans="1:25" ht="15.75" customHeight="1">
+    <row r="13" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>45785</v>
       </c>
@@ -5272,7 +5287,7 @@
       <c r="X13" s="35"/>
       <c r="Y13" s="35"/>
     </row>
-    <row r="14" spans="1:25" ht="15.75" customHeight="1">
+    <row r="14" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>45799</v>
       </c>
@@ -5318,7 +5333,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="15.75" customHeight="1">
+    <row r="15" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>45805</v>
       </c>
@@ -5352,101 +5367,101 @@
         <v>250</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="15.75" customHeight="1">
+    <row r="16" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="75"/>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="26"/>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="26"/>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="26"/>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="75"/>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="26"/>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="75"/>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="26"/>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="26"/>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="26"/>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="26"/>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="26"/>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="26"/>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B31" s="60"/>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="60"/>
       <c r="B32" s="60"/>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="60"/>
       <c r="B33" s="60"/>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="60"/>
       <c r="B34" s="60"/>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="60"/>
       <c r="B35" s="60"/>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="60"/>
       <c r="B36" s="60"/>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="60"/>
       <c r="B37" s="60"/>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="60"/>
       <c r="B38" s="60"/>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="60"/>
       <c r="B39" s="60"/>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="60"/>
       <c r="B40" s="60"/>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="60"/>
       <c r="B41" s="60"/>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="60"/>
       <c r="B42" s="60"/>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="60"/>
       <c r="B43" s="60"/>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="60"/>
       <c r="B44" s="60"/>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="60"/>
     </row>
   </sheetData>
@@ -5464,14 +5479,14 @@
     <hyperlink ref="K5" r:id="rId1" xr:uid="{A25AAE96-B446-4537-A7A0-A851A065E52D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{243C2AD8-98F5-4435-96A3-1C2CAB922825}">
   <dimension ref="A1:Y26"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="14.5703125" customWidth="1"/>
@@ -5498,7 +5513,7 @@
     <col min="25" max="25" width="37.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5509,7 +5524,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="27.75">
+    <row r="2" spans="1:25" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="78" t="s">
         <v>3</v>
       </c>
@@ -5586,7 +5601,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15" customHeight="1" thickBot="1">
+    <row r="3" spans="1:25" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="159">
         <v>45911</v>
       </c>
@@ -5649,7 +5664,7 @@
       <c r="X3" s="46"/>
       <c r="Y3" s="44"/>
     </row>
-    <row r="4" spans="1:25" ht="15" customHeight="1">
+    <row r="4" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="160">
         <v>45917</v>
       </c>
@@ -5718,7 +5733,7 @@
       <c r="X4" s="15"/>
       <c r="Y4" s="13"/>
     </row>
-    <row r="5" spans="1:25" ht="15" customHeight="1">
+    <row r="5" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="160">
         <v>45926</v>
       </c>
@@ -5776,7 +5791,7 @@
       <c r="X5" s="15"/>
       <c r="Y5" s="13"/>
     </row>
-    <row r="6" spans="1:25" ht="15" customHeight="1">
+    <row r="6" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="160">
         <v>45939</v>
       </c>
@@ -5840,7 +5855,7 @@
       <c r="X6" s="15"/>
       <c r="Y6" s="13"/>
     </row>
-    <row r="7" spans="1:25" ht="15" customHeight="1">
+    <row r="7" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="160">
         <v>45946</v>
       </c>
@@ -5897,7 +5912,7 @@
       <c r="X7" s="15"/>
       <c r="Y7" s="13"/>
     </row>
-    <row r="8" spans="1:25" ht="15" customHeight="1">
+    <row r="8" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="160">
         <v>45953</v>
       </c>
@@ -5955,7 +5970,7 @@
       <c r="X8" s="15"/>
       <c r="Y8" s="13"/>
     </row>
-    <row r="9" spans="1:25" ht="15" customHeight="1">
+    <row r="9" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="160">
         <v>45967</v>
       </c>
@@ -6017,7 +6032,7 @@
       <c r="X9" s="15"/>
       <c r="Y9" s="13"/>
     </row>
-    <row r="10" spans="1:25" ht="15" customHeight="1">
+    <row r="10" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="160">
         <v>45974</v>
       </c>
@@ -6080,7 +6095,7 @@
       <c r="X10" s="15"/>
       <c r="Y10" s="13"/>
     </row>
-    <row r="11" spans="1:25" ht="15" customHeight="1">
+    <row r="11" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="160">
         <v>45980</v>
       </c>
@@ -6131,7 +6146,7 @@
       <c r="X11" s="35"/>
       <c r="Y11" s="35"/>
     </row>
-    <row r="12" spans="1:25" ht="16.5" customHeight="1">
+    <row r="12" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="160">
         <f>A10+7</f>
         <v>45981</v>
@@ -6184,7 +6199,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13" s="160">
         <v>45986</v>
       </c>
@@ -6220,7 +6235,7 @@
       <c r="M13" s="158"/>
       <c r="N13" s="158"/>
     </row>
-    <row r="14" spans="1:25" ht="15" customHeight="1">
+    <row r="14" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="160">
         <v>45988</v>
       </c>
@@ -6275,7 +6290,7 @@
       <c r="X14" s="15"/>
       <c r="Y14" s="13"/>
     </row>
-    <row r="15" spans="1:25" ht="15" customHeight="1" thickBot="1">
+    <row r="15" spans="1:25" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="161">
         <v>45995</v>
       </c>
@@ -6338,35 +6353,35 @@
       <c r="X15" s="15"/>
       <c r="Y15" s="13"/>
     </row>
-    <row r="16" spans="1:25" ht="15" customHeight="1" thickBot="1">
+    <row r="16" spans="1:25" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="26"/>
       <c r="B16" s="26"/>
       <c r="C16" s="26"/>
       <c r="X16" s="20"/>
       <c r="Y16" s="18"/>
     </row>
-    <row r="17" spans="1:3" ht="15" customHeight="1">
+    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="26"/>
       <c r="B17" s="26"/>
       <c r="C17" s="26"/>
     </row>
-    <row r="18" spans="1:3" ht="15" customHeight="1">
+    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="26"/>
       <c r="B18" s="26"/>
       <c r="C18" s="26"/>
     </row>
-    <row r="19" spans="1:3" ht="15" customHeight="1">
+    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="26"/>
       <c r="B19" s="26"/>
       <c r="C19" s="26"/>
     </row>
-    <row r="20" spans="1:3" ht="15" customHeight="1"/>
-    <row r="21" spans="1:3" ht="15" customHeight="1"/>
-    <row r="22" spans="1:3" ht="15" customHeight="1"/>
-    <row r="23" spans="1:3" ht="15" customHeight="1"/>
-    <row r="24" spans="1:3" ht="15" customHeight="1"/>
-    <row r="25" spans="1:3" ht="15" customHeight="1"/>
-    <row r="26" spans="1:3" ht="15" customHeight="1"/>
+    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <protectedRanges>
     <protectedRange algorithmName="SHA-512" hashValue="pQyTzP/d7t5ThMimBt5mu8gGozgAm1OwF6BMILsn5/kmtZ5mZf81NMi09wwU8mvtItxf0EVNWa6V4MCa0DKeSQ==" saltValue="NzZBiAQ1yFjat+SeIqh2Uw==" spinCount="100000" sqref="A3:E19" name="Range3_1"/>
@@ -6400,7 +6415,7 @@
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="A1:Y18"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.5703125" customWidth="1"/>
     <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
@@ -6427,7 +6442,7 @@
     <col min="25" max="25" width="37.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6438,7 +6453,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="27.75">
+    <row r="2" spans="1:25" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="64" t="s">
         <v>3</v>
       </c>
@@ -6515,7 +6530,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15" customHeight="1">
+    <row r="3" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="75">
         <v>46051</v>
       </c>
@@ -6564,7 +6579,7 @@
       <c r="X3" s="46"/>
       <c r="Y3" s="44"/>
     </row>
-    <row r="4" spans="1:25" ht="15.75" customHeight="1">
+    <row r="4" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="75">
         <f>A3+12</f>
         <v>46063</v>
@@ -6615,7 +6630,7 @@
       <c r="X4" s="15"/>
       <c r="Y4" s="13"/>
     </row>
-    <row r="5" spans="1:25" ht="18.75" customHeight="1">
+    <row r="5" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="75">
         <f>A4+16</f>
         <v>46079</v>
@@ -6670,7 +6685,7 @@
       <c r="X5" s="15"/>
       <c r="Y5" s="13"/>
     </row>
-    <row r="6" spans="1:25" ht="15.75" customHeight="1">
+    <row r="6" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="75">
         <f>A5+14</f>
         <v>46093</v>
@@ -6725,7 +6740,7 @@
       <c r="X6" s="15"/>
       <c r="Y6" s="13"/>
     </row>
-    <row r="7" spans="1:25" ht="15.75" customHeight="1">
+    <row r="7" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="75">
         <f>A6+7</f>
         <v>46100</v>
@@ -6779,7 +6794,7 @@
       <c r="X7" s="15"/>
       <c r="Y7" s="13"/>
     </row>
-    <row r="8" spans="1:25" ht="17.25" customHeight="1">
+    <row r="8" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="75">
         <f>A6+14</f>
         <v>46107</v>
@@ -6832,7 +6847,7 @@
       <c r="X8" s="15"/>
       <c r="Y8" s="13"/>
     </row>
-    <row r="9" spans="1:25" ht="18" customHeight="1">
+    <row r="9" spans="1:25" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="75">
         <f>A8+7</f>
         <v>46114</v>
@@ -6886,7 +6901,7 @@
       <c r="X9" s="15"/>
       <c r="Y9" s="13"/>
     </row>
-    <row r="10" spans="1:25" ht="15" customHeight="1">
+    <row r="10" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="75">
         <v>46120</v>
       </c>
@@ -6935,7 +6950,7 @@
       <c r="X10" s="15"/>
       <c r="Y10" s="13"/>
     </row>
-    <row r="11" spans="1:25" ht="14.25" customHeight="1">
+    <row r="11" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="75">
         <v>46121</v>
       </c>
@@ -6986,7 +7001,7 @@
       <c r="X11" s="15"/>
       <c r="Y11" s="13"/>
     </row>
-    <row r="12" spans="1:25" ht="16.5" customHeight="1">
+    <row r="12" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="75">
         <v>46128</v>
       </c>
@@ -7039,7 +7054,7 @@
       <c r="X12" s="15"/>
       <c r="Y12" s="13"/>
     </row>
-    <row r="13" spans="1:25" ht="18.75" customHeight="1">
+    <row r="13" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="75">
         <v>46135</v>
       </c>
@@ -7086,37 +7101,58 @@
       <c r="X13" s="15"/>
       <c r="Y13" s="13"/>
     </row>
-    <row r="14" spans="1:25" ht="18.75" customHeight="1">
+    <row r="14" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="75">
         <v>46142</v>
       </c>
-      <c r="B14" s="172" t="s">
+      <c r="B14" s="26" t="s">
         <v>377</v>
       </c>
-      <c r="C14" s="26"/>
-      <c r="D14" s="173"/>
-      <c r="F14" s="174"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="174"/>
-      <c r="I14" s="175"/>
-      <c r="J14" s="175"/>
-      <c r="K14" s="102"/>
-      <c r="L14" s="174"/>
-      <c r="M14" s="174"/>
-      <c r="N14" s="174"/>
+      <c r="C14" s="26" t="s">
+        <v>378</v>
+      </c>
+      <c r="D14" s="27" t="s">
+        <v>278</v>
+      </c>
+      <c r="E14">
+        <v>14</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>379</v>
+      </c>
+      <c r="G14" s="14" t="s">
+        <v>380</v>
+      </c>
+      <c r="H14" s="14" t="s">
+        <v>432</v>
+      </c>
+      <c r="I14" s="14" t="s">
+        <v>433</v>
+      </c>
+      <c r="J14" s="107" t="s">
+        <v>434</v>
+      </c>
+      <c r="K14" s="102" t="s">
+        <v>436</v>
+      </c>
+      <c r="L14" s="14"/>
+      <c r="M14" s="102" t="s">
+        <v>435</v>
+      </c>
+      <c r="N14" s="14"/>
       <c r="O14" s="35"/>
-      <c r="P14" s="174"/>
-      <c r="Q14" s="174"/>
-      <c r="R14" s="174"/>
-      <c r="S14" s="174"/>
+      <c r="P14" s="14"/>
+      <c r="Q14" s="14"/>
+      <c r="R14" s="14"/>
+      <c r="S14" s="14"/>
       <c r="T14" s="35"/>
-      <c r="U14" s="174"/>
-      <c r="V14" s="174"/>
-      <c r="W14" s="174"/>
+      <c r="U14" s="14"/>
+      <c r="V14" s="14"/>
+      <c r="W14" s="14"/>
       <c r="X14" s="15"/>
       <c r="Y14" s="13"/>
     </row>
-    <row r="15" spans="1:25">
+    <row r="15" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="26">
         <v>46156</v>
       </c>
@@ -7133,10 +7169,10 @@
         <v>16</v>
       </c>
       <c r="F15" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="G15" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="H15" t="s">
         <v>40</v>
@@ -7150,17 +7186,17 @@
       <c r="X15" s="20"/>
       <c r="Y15" s="18"/>
     </row>
-    <row r="16" spans="1:25" ht="12.75" customHeight="1">
+    <row r="16" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="26"/>
       <c r="B16" s="26"/>
       <c r="C16" s="26"/>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="26"/>
       <c r="B17" s="26"/>
       <c r="C17" s="26"/>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="26"/>
       <c r="B18" s="26"/>
       <c r="C18" s="26"/>
@@ -7187,6 +7223,8 @@
     <hyperlink ref="M6" r:id="rId10" xr:uid="{6053315A-23DA-DA4E-9447-0140277816C3}"/>
     <hyperlink ref="M11" r:id="rId11" xr:uid="{942C7964-68D4-4F8F-8947-80A84887C647}"/>
     <hyperlink ref="K11" r:id="rId12" xr:uid="{460148DF-9775-4F8A-91F3-89030F1FC4E8}"/>
+    <hyperlink ref="M14" r:id="rId13" xr:uid="{8D133BC0-60B4-4F75-84B7-5C8F4452AAD4}"/>
+    <hyperlink ref="K14" r:id="rId14" xr:uid="{F5CA8E46-DA4D-40A2-B71F-BC8C3D5249DB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7195,7 +7233,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A33E49C-EC2E-42B7-80E4-DD607C0B7A89}">
   <dimension ref="A1:Y13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.5703125" customWidth="1"/>
     <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
@@ -7222,7 +7260,7 @@
     <col min="25" max="25" width="37.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="15.75" thickBot="1">
+    <row r="1" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7233,7 +7271,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="28.5" thickBot="1">
+    <row r="2" spans="1:25" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="64" t="s">
         <v>3</v>
       </c>
@@ -7310,7 +7348,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15" customHeight="1">
+    <row r="3" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="75">
         <v>46275</v>
       </c>
@@ -7329,7 +7367,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="G3" s="14" t="s">
         <v>376</v>
@@ -7359,7 +7397,7 @@
       <c r="X3" s="46"/>
       <c r="Y3" s="44"/>
     </row>
-    <row r="4" spans="1:25" ht="15.75" customHeight="1">
+    <row r="4" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="75">
         <f>A3+14</f>
         <v>46289</v>
@@ -7380,7 +7418,7 @@
         <v>3</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="G4" s="14" t="s">
         <v>376</v>
@@ -7410,7 +7448,7 @@
       <c r="X4" s="15"/>
       <c r="Y4" s="13"/>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" s="75">
         <f t="shared" ref="A5" si="2">A4+14</f>
         <v>46303</v>
@@ -7431,7 +7469,7 @@
         <v>5</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="G5" s="14" t="s">
         <v>376</v>
@@ -7465,7 +7503,7 @@
       <c r="X5" s="15"/>
       <c r="Y5" s="13"/>
     </row>
-    <row r="6" spans="1:25" ht="15.75" customHeight="1">
+    <row r="6" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="75">
         <f>A5+14</f>
         <v>46317</v>
@@ -7486,7 +7524,7 @@
         <v>7</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="G6" s="14" t="s">
         <v>376</v>
@@ -7516,7 +7554,7 @@
       <c r="X6" s="15"/>
       <c r="Y6" s="13"/>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" s="75">
         <f>A6+14</f>
         <v>46331</v>
@@ -7537,7 +7575,7 @@
         <v>9</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="G7" s="14" t="s">
         <v>376</v>
@@ -7567,7 +7605,7 @@
       <c r="X7" s="15"/>
       <c r="Y7" s="13"/>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" s="75">
         <f>A7+14</f>
         <v>46345</v>
@@ -7586,7 +7624,7 @@
         <v>11</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="G8" s="14" t="s">
         <v>376</v>
@@ -7616,7 +7654,7 @@
       <c r="X8" s="15"/>
       <c r="Y8" s="13"/>
     </row>
-    <row r="9" spans="1:25" ht="18.75" customHeight="1">
+    <row r="9" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="75">
         <v>46121</v>
       </c>
@@ -7633,7 +7671,7 @@
         <v>13</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="G9" s="14" t="s">
         <v>376</v>
@@ -7663,24 +7701,24 @@
       <c r="X9" s="15"/>
       <c r="Y9" s="13"/>
     </row>
-    <row r="10" spans="1:25" ht="15.75" thickBot="1">
+    <row r="10" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="26"/>
       <c r="B10" s="26"/>
       <c r="C10" s="26"/>
       <c r="X10" s="20"/>
       <c r="Y10" s="18"/>
     </row>
-    <row r="11" spans="1:25" ht="12.75" customHeight="1">
+    <row r="11" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="26"/>
       <c r="B11" s="26"/>
       <c r="C11" s="26"/>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12" s="26"/>
       <c r="B12" s="26"/>
       <c r="C12" s="26"/>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13" s="26"/>
       <c r="B13" s="26"/>
       <c r="C13" s="26"/>
@@ -7702,212 +7740,212 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AEC079F-155A-491D-9189-1418FC903287}">
   <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.28515625" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
     <col min="3" max="3" width="20.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="55" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B2" s="54" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C2" s="54" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="136" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B3" s="137"/>
       <c r="C3" s="138" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B4" s="52"/>
       <c r="C4" s="50" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="52" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B5" s="52"/>
       <c r="C5" s="50" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="52" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B6" s="52" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C6" s="50" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="52" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B7" s="52" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C7" s="50" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="52" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B8" s="52" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C8" s="50" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="52" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B9" s="52"/>
       <c r="C9" s="50"/>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="52" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B10" s="52" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C10" s="50" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="52" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B11" s="52" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C11" s="50" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="52" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B12" s="52" t="s">
+        <v>406</v>
+      </c>
+      <c r="C12" s="50" t="s">
         <v>404</v>
       </c>
-      <c r="C12" s="50" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="52" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B13" s="52" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C13" s="50" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="52" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B14" s="52" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C14" s="50" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="52" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B15" s="52" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C15" s="50" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="137" t="s">
         <v>321</v>
       </c>
       <c r="B16" s="137" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C16" s="139" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="137" t="s">
         <v>346</v>
       </c>
       <c r="B17" s="137" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C17" s="139" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="52" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B18" s="52" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C18" s="50" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="53" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B19" s="53" t="s">
         <v>230</v>
       </c>
       <c r="C19" s="51" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B20" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
   </sheetData>
@@ -7923,24 +7961,24 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AD19DE5-C22F-4D41-B540-76D70438E18B}">
   <dimension ref="A1:I16"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.85546875" customWidth="1"/>
     <col min="6" max="6" width="14.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" thickBot="1">
+    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="135" t="s">
         <v>3</v>
       </c>
       <c r="B1" s="131" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C1" s="130" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="169">
         <v>46051</v>
       </c>
@@ -7948,14 +7986,14 @@
         <v>1</v>
       </c>
       <c r="C2" s="170" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="F2" s="75"/>
       <c r="G2" s="77"/>
       <c r="H2" s="29"/>
       <c r="I2" s="55"/>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="171">
         <f>A2+7</f>
         <v>46058</v>
@@ -7965,14 +8003,14 @@
         <v>2</v>
       </c>
       <c r="C3" s="170" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F3" s="75"/>
       <c r="G3" s="2"/>
       <c r="H3" s="26"/>
       <c r="I3" s="27"/>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="171">
         <f t="shared" ref="A4:A12" si="0">A3+7</f>
         <v>46065</v>
@@ -7982,14 +8020,14 @@
         <v>3</v>
       </c>
       <c r="C4" s="170" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="F4" s="75"/>
       <c r="G4" s="2"/>
       <c r="H4" s="26"/>
       <c r="I4" s="27"/>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="171">
         <f t="shared" si="0"/>
         <v>46072</v>
@@ -7999,14 +8037,14 @@
         <v>4</v>
       </c>
       <c r="C5" s="170" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F5" s="75"/>
       <c r="G5" s="2"/>
       <c r="H5" s="26"/>
       <c r="I5" s="27"/>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="133">
         <f t="shared" si="0"/>
         <v>46079</v>
@@ -8016,14 +8054,14 @@
         <v>5</v>
       </c>
       <c r="C6" s="134" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="F6" s="75"/>
       <c r="G6" s="2"/>
       <c r="H6" s="26"/>
       <c r="I6" s="27"/>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="133">
         <f t="shared" si="0"/>
         <v>46086</v>
@@ -8033,14 +8071,14 @@
         <v>6</v>
       </c>
       <c r="C7" s="134" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F7" s="75"/>
       <c r="G7" s="2"/>
       <c r="H7" s="26"/>
       <c r="I7" s="27"/>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="133">
         <f t="shared" si="0"/>
         <v>46093</v>
@@ -8050,14 +8088,14 @@
         <v>7</v>
       </c>
       <c r="C8" s="134" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="F8" s="75"/>
       <c r="G8" s="2"/>
       <c r="H8" s="26"/>
       <c r="I8" s="27"/>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="133">
         <f t="shared" si="0"/>
         <v>46100</v>
@@ -8067,14 +8105,14 @@
         <v>8</v>
       </c>
       <c r="C9" s="134" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="F9" s="75"/>
       <c r="G9" s="2"/>
       <c r="H9" s="26"/>
       <c r="I9" s="27"/>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="133">
         <f t="shared" si="0"/>
         <v>46107</v>
@@ -8084,14 +8122,14 @@
         <v>9</v>
       </c>
       <c r="C10" s="134" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="F10" s="75"/>
       <c r="G10" s="2"/>
       <c r="H10" s="26"/>
       <c r="I10" s="27"/>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="133">
         <f t="shared" si="0"/>
         <v>46114</v>
@@ -8101,10 +8139,10 @@
         <v>10</v>
       </c>
       <c r="C11" s="134" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="133">
         <f t="shared" si="0"/>
         <v>46121</v>
@@ -8114,10 +8152,10 @@
         <v>11</v>
       </c>
       <c r="C12" s="134" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="133">
         <f t="shared" ref="A13:A14" si="3">A12+7</f>
         <v>46128</v>
@@ -8127,10 +8165,10 @@
         <v>12</v>
       </c>
       <c r="C13" s="134" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="133">
         <f t="shared" si="3"/>
         <v>46135</v>
@@ -8140,15 +8178,15 @@
         <v>13</v>
       </c>
       <c r="C14" s="134" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="133"/>
       <c r="B15" s="134"/>
       <c r="C15" s="134"/>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="G16" s="26"/>
     </row>
   </sheetData>
@@ -8175,7 +8213,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2BB5C5F-5790-4A91-A6E8-8841719DA1FC}">
   <dimension ref="A2:I20"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.42578125" customWidth="1"/>
     <col min="2" max="2" width="9.140625" customWidth="1"/>
@@ -8187,17 +8225,17 @@
     <col min="9" max="9" width="64.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" ht="23.25">
+    <row r="2" spans="1:9" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A2" s="91" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="18.75">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A3" s="79" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="35.25">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A5" s="80" t="s">
         <v>3</v>
       </c>
@@ -8220,13 +8258,13 @@
         <v>9</v>
       </c>
       <c r="H5" s="82" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="I5" s="81" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="18.75">
+    <row r="6" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A6" s="92">
         <v>45694</v>
       </c>
@@ -8253,7 +8291,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="18.75">
+    <row r="7" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A7" s="83">
         <v>45708</v>
       </c>
@@ -8282,7 +8320,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="18.75">
+    <row r="8" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A8" s="83">
         <v>45722</v>
       </c>
@@ -8309,7 +8347,7 @@
       </c>
       <c r="I8" s="86"/>
     </row>
-    <row r="9" spans="1:9" ht="18.75">
+    <row r="9" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A9" s="83">
         <v>45735</v>
       </c>
@@ -8320,7 +8358,7 @@
         <v>198</v>
       </c>
       <c r="D9" s="94" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E9" s="94">
         <v>8</v>
@@ -8338,7 +8376,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="18.75">
+    <row r="10" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A10" s="83">
         <v>45744</v>
       </c>
@@ -8365,7 +8403,7 @@
       </c>
       <c r="I10" s="86"/>
     </row>
-    <row r="11" spans="1:9" ht="18.75">
+    <row r="11" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A11" s="83">
         <v>45750</v>
       </c>
@@ -8382,7 +8420,7 @@
         <v>10</v>
       </c>
       <c r="F11" s="87" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="G11" s="87" t="s">
         <v>68</v>
@@ -8392,7 +8430,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="18.75">
+    <row r="12" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A12" s="83">
         <v>45758</v>
       </c>
@@ -8421,7 +8459,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="18.75">
+    <row r="13" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A13" s="83">
         <v>45764</v>
       </c>
@@ -8438,13 +8476,13 @@
         <v>12</v>
       </c>
       <c r="F13" s="87" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="G13" s="87"/>
       <c r="H13" s="87"/>
       <c r="I13" s="86"/>
     </row>
-    <row r="14" spans="1:9" ht="18.75">
+    <row r="14" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A14" s="88">
         <v>45771</v>
       </c>
@@ -8461,7 +8499,7 @@
         <v>13</v>
       </c>
       <c r="F14" s="90" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="G14" s="90" t="s">
         <v>77</v>
@@ -8473,7 +8511,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="20" spans="8:8" ht="18.75">
+    <row r="20" spans="8:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="H20" s="79"/>
     </row>
   </sheetData>

--- a/data/MACSI seminar series.xlsx
+++ b/data/MACSI seminar series.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ulcampus-my.sharepoint.com/personal/david_osullivan_ul_ie/Documents/Academic_work/_Misc/MACSI Seminars/macsi-seminars.github.io/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="413" documentId="13_ncr:1_{12BE53B5-C8C7-44FE-8280-19C653D9122E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55AEEDAA-4922-4987-932D-61D57203D954}"/>
+  <xr:revisionPtr revIDLastSave="414" documentId="13_ncr:1_{12BE53B5-C8C7-44FE-8280-19C653D9122E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A2A1BF9-C7FF-45AC-8963-FB752E233DAB}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="436">
   <si>
     <t>Fill in as much of the green boxes as possible. Ideally, this would be before you have finished your visitors travel dates (just to avoid double booking).</t>
   </si>
@@ -1239,9 +1239,6 @@
   </si>
   <si>
     <t>TBC</t>
-  </si>
-  <si>
-    <t>4pm</t>
   </si>
   <si>
     <t>May</t>
@@ -7106,10 +7103,10 @@
         <v>46142</v>
       </c>
       <c r="B14" s="26" t="s">
+        <v>259</v>
+      </c>
+      <c r="C14" s="26" t="s">
         <v>377</v>
-      </c>
-      <c r="C14" s="26" t="s">
-        <v>378</v>
       </c>
       <c r="D14" s="27" t="s">
         <v>278</v>
@@ -7118,26 +7115,26 @@
         <v>14</v>
       </c>
       <c r="F14" s="14" t="s">
+        <v>378</v>
+      </c>
+      <c r="G14" s="14" t="s">
         <v>379</v>
       </c>
-      <c r="G14" s="14" t="s">
-        <v>380</v>
-      </c>
       <c r="H14" s="14" t="s">
+        <v>431</v>
+      </c>
+      <c r="I14" s="14" t="s">
         <v>432</v>
       </c>
-      <c r="I14" s="14" t="s">
+      <c r="J14" s="107" t="s">
         <v>433</v>
       </c>
-      <c r="J14" s="107" t="s">
-        <v>434</v>
-      </c>
       <c r="K14" s="102" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="L14" s="14"/>
       <c r="M14" s="102" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="N14" s="14"/>
       <c r="O14" s="35"/>
@@ -7160,7 +7157,7 @@
         <v>190</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D15" t="s">
         <v>278</v>
@@ -7169,10 +7166,10 @@
         <v>16</v>
       </c>
       <c r="F15" t="s">
+        <v>380</v>
+      </c>
+      <c r="G15" t="s">
         <v>381</v>
-      </c>
-      <c r="G15" t="s">
-        <v>382</v>
       </c>
       <c r="H15" t="s">
         <v>40</v>
@@ -7367,7 +7364,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="G3" s="14" t="s">
         <v>376</v>
@@ -7418,7 +7415,7 @@
         <v>3</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="G4" s="14" t="s">
         <v>376</v>
@@ -7469,7 +7466,7 @@
         <v>5</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="G5" s="14" t="s">
         <v>376</v>
@@ -7524,7 +7521,7 @@
         <v>7</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="G6" s="14" t="s">
         <v>376</v>
@@ -7575,7 +7572,7 @@
         <v>9</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="G7" s="14" t="s">
         <v>376</v>
@@ -7624,7 +7621,7 @@
         <v>11</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="G8" s="14" t="s">
         <v>376</v>
@@ -7662,7 +7659,7 @@
         <v>190</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D9" s="27" t="s">
         <v>278</v>
@@ -7671,7 +7668,7 @@
         <v>13</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="G9" s="14" t="s">
         <v>376</v>
@@ -7749,23 +7746,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="55" t="s">
+        <v>384</v>
+      </c>
+      <c r="B2" s="54" t="s">
         <v>385</v>
       </c>
-      <c r="B2" s="54" t="s">
+      <c r="C2" s="54" t="s">
         <v>386</v>
-      </c>
-      <c r="C2" s="54" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="136" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B3" s="137"/>
       <c r="C3" s="138" t="s">
@@ -7774,7 +7771,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B4" s="52"/>
       <c r="C4" s="50" t="s">
@@ -7783,19 +7780,19 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="52" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B5" s="52"/>
       <c r="C5" s="50" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="52" t="s">
+        <v>391</v>
+      </c>
+      <c r="B6" s="52" t="s">
         <v>392</v>
-      </c>
-      <c r="B6" s="52" t="s">
-        <v>393</v>
       </c>
       <c r="C6" s="50" t="s">
         <v>87</v>
@@ -7803,10 +7800,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="52" t="s">
+        <v>393</v>
+      </c>
+      <c r="B7" s="52" t="s">
         <v>394</v>
-      </c>
-      <c r="B7" s="52" t="s">
-        <v>395</v>
       </c>
       <c r="C7" s="50" t="s">
         <v>87</v>
@@ -7814,10 +7811,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="52" t="s">
+        <v>395</v>
+      </c>
+      <c r="B8" s="52" t="s">
         <v>396</v>
-      </c>
-      <c r="B8" s="52" t="s">
-        <v>397</v>
       </c>
       <c r="C8" s="50" t="s">
         <v>101</v>
@@ -7825,75 +7822,75 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="52" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B9" s="52"/>
       <c r="C9" s="50"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="52" t="s">
+        <v>398</v>
+      </c>
+      <c r="B10" s="52" t="s">
         <v>399</v>
       </c>
-      <c r="B10" s="52" t="s">
+      <c r="C10" s="50" t="s">
         <v>400</v>
-      </c>
-      <c r="C10" s="50" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="52" t="s">
+        <v>401</v>
+      </c>
+      <c r="B11" s="52" t="s">
         <v>402</v>
       </c>
-      <c r="B11" s="52" t="s">
+      <c r="C11" s="50" t="s">
         <v>403</v>
-      </c>
-      <c r="C11" s="50" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="52" t="s">
+        <v>404</v>
+      </c>
+      <c r="B12" s="52" t="s">
         <v>405</v>
       </c>
-      <c r="B12" s="52" t="s">
-        <v>406</v>
-      </c>
       <c r="C12" s="50" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="52" t="s">
+        <v>406</v>
+      </c>
+      <c r="B13" s="52" t="s">
         <v>407</v>
       </c>
-      <c r="B13" s="52" t="s">
-        <v>408</v>
-      </c>
       <c r="C13" s="50" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="52" t="s">
+        <v>408</v>
+      </c>
+      <c r="B14" s="52" t="s">
         <v>409</v>
       </c>
-      <c r="B14" s="52" t="s">
-        <v>410</v>
-      </c>
       <c r="C14" s="50" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="52" t="s">
+        <v>410</v>
+      </c>
+      <c r="B15" s="52" t="s">
         <v>411</v>
       </c>
-      <c r="B15" s="52" t="s">
-        <v>412</v>
-      </c>
       <c r="C15" s="50" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -7901,10 +7898,10 @@
         <v>321</v>
       </c>
       <c r="B16" s="137" t="s">
+        <v>412</v>
+      </c>
+      <c r="C16" s="139" t="s">
         <v>413</v>
-      </c>
-      <c r="C16" s="139" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -7912,18 +7909,18 @@
         <v>346</v>
       </c>
       <c r="B17" s="137" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C17" s="139" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="52" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B18" s="52" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C18" s="50" t="s">
         <v>87</v>
@@ -7931,21 +7928,21 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="53" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B19" s="53" t="s">
         <v>230</v>
       </c>
       <c r="C19" s="51" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>418</v>
+      </c>
+      <c r="B20" t="s">
         <v>419</v>
-      </c>
-      <c r="B20" t="s">
-        <v>420</v>
       </c>
     </row>
   </sheetData>
@@ -7972,10 +7969,10 @@
         <v>3</v>
       </c>
       <c r="B1" s="131" t="s">
+        <v>420</v>
+      </c>
+      <c r="C1" s="130" t="s">
         <v>421</v>
-      </c>
-      <c r="C1" s="130" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -7986,7 +7983,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="170" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F2" s="75"/>
       <c r="G2" s="77"/>
@@ -8003,7 +8000,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="170" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="F3" s="75"/>
       <c r="G3" s="2"/>
@@ -8020,7 +8017,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="170" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F4" s="75"/>
       <c r="G4" s="2"/>
@@ -8037,7 +8034,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="170" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="F5" s="75"/>
       <c r="G5" s="2"/>
@@ -8054,7 +8051,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="134" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F6" s="75"/>
       <c r="G6" s="2"/>
@@ -8071,7 +8068,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="134" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="F7" s="75"/>
       <c r="G7" s="2"/>
@@ -8088,7 +8085,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="134" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="F8" s="75"/>
       <c r="G8" s="2"/>
@@ -8105,7 +8102,7 @@
         <v>8</v>
       </c>
       <c r="C9" s="134" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F9" s="75"/>
       <c r="G9" s="2"/>
@@ -8122,7 +8119,7 @@
         <v>9</v>
       </c>
       <c r="C10" s="134" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="F10" s="75"/>
       <c r="G10" s="2"/>
@@ -8139,7 +8136,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="134" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -8152,7 +8149,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="134" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -8165,7 +8162,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="134" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -8178,7 +8175,7 @@
         <v>13</v>
       </c>
       <c r="C14" s="134" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -8227,12 +8224,12 @@
   <sheetData>
     <row r="2" spans="1:9" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A2" s="91" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A3" s="79" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="37.5" x14ac:dyDescent="0.25">
@@ -8258,7 +8255,7 @@
         <v>9</v>
       </c>
       <c r="H5" s="82" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="I5" s="81" t="s">
         <v>11</v>
@@ -8358,7 +8355,7 @@
         <v>198</v>
       </c>
       <c r="D9" s="94" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E9" s="94">
         <v>8</v>
@@ -8420,7 +8417,7 @@
         <v>10</v>
       </c>
       <c r="F11" s="87" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="G11" s="87" t="s">
         <v>68</v>
@@ -8476,7 +8473,7 @@
         <v>12</v>
       </c>
       <c r="F13" s="87" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G13" s="87"/>
       <c r="H13" s="87"/>
@@ -8499,7 +8496,7 @@
         <v>13</v>
       </c>
       <c r="F14" s="90" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G14" s="90" t="s">
         <v>77</v>

--- a/data/MACSI seminar series.xlsx
+++ b/data/MACSI seminar series.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30015"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ulcampus-my.sharepoint.com/personal/david_osullivan_ul_ie/Documents/Academic_work/_Misc/MACSI Seminars/macsi-seminars.github.io/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="414" documentId="13_ncr:1_{12BE53B5-C8C7-44FE-8280-19C653D9122E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A2A1BF9-C7FF-45AC-8963-FB752E233DAB}"/>
+  <xr:revisionPtr revIDLastSave="416" documentId="13_ncr:1_{12BE53B5-C8C7-44FE-8280-19C653D9122E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8ABB13C-981A-4743-ABF0-CA69466D205E}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="438">
   <si>
     <t>Fill in as much of the green boxes as possible. Ideally, this would be before you have finished your visitors travel dates (just to avoid double booking).</t>
   </si>
@@ -1238,24 +1238,45 @@
     <t>Andrew Keane</t>
   </si>
   <si>
+    <t>Fragmented tipping of the Atlantic Meridional Ocean Circulation</t>
+  </si>
+  <si>
+    <t>The tipping of the Atlantic Meridional Overturning Circulation (AMOC) to a ‘shutdown’ state due to changes in the freshwater forcing of the ocean is of particular interest and concern due to its widespread ramifications, including a dramatic climatic shift for much of Europe. A clear understanding of how such a shutdown would unfold requires analyses of models from across the complexity spectrum. For example, detailed simulations of sophisticated Earth System Models have identified scenarios of ‘fragmented’ tipping towards a complete shutdown of AMOC, in which deep-water formation first ceases in the Labrador Sea before ceasing in the Nordic Seas. Here, we study a simple ocean box model with two polar boxes designed to represent deep-water formation at these two distinct sites. A bifurcation analysis reveals how, depending on the differences of freshwater and thermal forcing between the two polar boxes, transitions to ‘partial shutdown’ states are possible. Our results shed light on the nature of the tipping of AMOC and clarify dynamical features observed in more sophisticated models.</t>
+  </si>
+  <si>
+    <t>May</t>
+  </si>
+  <si>
+    <t>Florian Faucher</t>
+  </si>
+  <si>
+    <t>University of Pau and Pays de l’Adour</t>
+  </si>
+  <si>
+    <t>Romina Gaburro</t>
+  </si>
+  <si>
+    <t>Quantitative inverse wave problem for passive imaging using cross-correlation data.</t>
+  </si>
+  <si>
+    <t>We investigate the quantitative reconstruction of physical properties in the context of passive imaging, where ambient wavefields are used to probe a medium. These ambient signals correspond to oscillations of the system generated by stochastic events. We discuss in particular  helioseismology, where satellites observe solar oscillations that are driven by turbulent convective motion. Considering the data as a superposition of waves generated by stochastic sources, the expected value of the cross-correlation between signals is related to the deterministic Green's function. The inverse wave problem is then formulated through an iterative minimization procedure, in which the gradient of the misfit functional is computed via the adjoint-state method. We focus on time-harmonic acoustic wave propagation and carry out synthetic experiments, comparing inversions based on cross-correlation data with those using direct wavefield measurements in the configuration of active-source acquisitions.</t>
+  </si>
+  <si>
+    <t>https://scholar.google.com/citations?user=KKQ8FvkAAAAJ&amp;hl=en</t>
+  </si>
+  <si>
+    <t>https://ffaucher.gitlab.io/cv/</t>
+  </si>
+  <si>
+    <t>Alan Demlow</t>
+  </si>
+  <si>
+    <t>Texas A&amp;M</t>
+  </si>
+  <si>
     <t>TBC</t>
   </si>
   <si>
-    <t>May</t>
-  </si>
-  <si>
-    <t>Florian Faucher</t>
-  </si>
-  <si>
-    <t>University of Pau and Pays de l’Adour</t>
-  </si>
-  <si>
-    <t>Alan Demlow</t>
-  </si>
-  <si>
-    <t>Texas A&amp;M</t>
-  </si>
-  <si>
     <t>Open</t>
   </si>
   <si>
@@ -1401,21 +1422,6 @@
   </si>
   <si>
     <t>Leornard Henckel</t>
-  </si>
-  <si>
-    <t>Romina Gaburro</t>
-  </si>
-  <si>
-    <t>Quantitative inverse wave problem for passive imaging using cross-correlation data.</t>
-  </si>
-  <si>
-    <t>We investigate the quantitative reconstruction of physical properties in the context of passive imaging, where ambient wavefields are used to probe a medium. These ambient signals correspond to oscillations of the system generated by stochastic events. We discuss in particular  helioseismology, where satellites observe solar oscillations that are driven by turbulent convective motion. Considering the data as a superposition of waves generated by stochastic sources, the expected value of the cross-correlation between signals is related to the deterministic Green's function. The inverse wave problem is then formulated through an iterative minimization procedure, in which the gradient of the misfit functional is computed via the adjoint-state method. We focus on time-harmonic acoustic wave propagation and carry out synthetic experiments, comparing inversions based on cross-correlation data with those using direct wavefield measurements in the configuration of active-source acquisitions.</t>
-  </si>
-  <si>
-    <t>https://ffaucher.gitlab.io/cv/</t>
-  </si>
-  <si>
-    <t>https://scholar.google.com/citations?user=KKQ8FvkAAAAJ&amp;hl=en</t>
   </si>
 </sst>
 </file>
@@ -1425,7 +1431,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2283,9 +2289,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2323,7 +2329,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2429,7 +2435,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2571,7 +2577,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2580,7 +2586,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7958562-D4BB-4776-9668-682A6F2E2AD0}">
   <dimension ref="A1:Y20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="11.140625" customWidth="1"/>
@@ -2605,7 +2611,7 @@
     <col min="25" max="25" width="37.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2616,7 +2622,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" ht="30">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -2693,7 +2699,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" ht="13.5" customHeight="1">
       <c r="A3" s="2">
         <v>45317</v>
       </c>
@@ -2760,7 +2766,7 @@
       <c r="X3" s="13"/>
       <c r="Y3" s="13"/>
     </row>
-    <row r="4" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" ht="13.5" customHeight="1">
       <c r="A4" s="2">
         <v>45323</v>
       </c>
@@ -2823,7 +2829,7 @@
       <c r="X4" s="13"/>
       <c r="Y4" s="13"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25">
       <c r="A5" s="2">
         <v>45324</v>
       </c>
@@ -2884,7 +2890,7 @@
       <c r="X5" s="13"/>
       <c r="Y5" s="13"/>
     </row>
-    <row r="6" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" ht="12.75" customHeight="1">
       <c r="A6" s="2">
         <v>45331</v>
       </c>
@@ -2951,7 +2957,7 @@
       <c r="X6" s="13"/>
       <c r="Y6" s="13"/>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25">
       <c r="A7" s="2">
         <v>45338</v>
       </c>
@@ -3020,7 +3026,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" ht="15" customHeight="1">
       <c r="A8" s="2">
         <v>45345</v>
       </c>
@@ -3087,7 +3093,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" ht="16.5" customHeight="1">
       <c r="A9" s="2">
         <v>45359</v>
       </c>
@@ -3140,7 +3146,7 @@
       <c r="X9" s="13"/>
       <c r="Y9" s="13"/>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25">
       <c r="A10" s="2">
         <v>45366</v>
       </c>
@@ -3209,7 +3215,7 @@
       <c r="X10" s="13"/>
       <c r="Y10" s="13"/>
     </row>
-    <row r="11" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" ht="15" customHeight="1">
       <c r="A11" s="2">
         <v>45379</v>
       </c>
@@ -3270,7 +3276,7 @@
       <c r="X11" s="13"/>
       <c r="Y11" s="13"/>
     </row>
-    <row r="12" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" ht="13.5" customHeight="1">
       <c r="A12" s="2">
         <v>45386</v>
       </c>
@@ -3333,7 +3339,7 @@
       <c r="X12" s="13"/>
       <c r="Y12" s="13"/>
     </row>
-    <row r="13" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" ht="16.5" customHeight="1">
       <c r="A13" s="2">
         <v>45387</v>
       </c>
@@ -3402,7 +3408,7 @@
       <c r="X13" s="13"/>
       <c r="Y13" s="13"/>
     </row>
-    <row r="14" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" ht="15.75" customHeight="1">
       <c r="A14" s="2">
         <v>45394</v>
       </c>
@@ -3463,7 +3469,7 @@
       <c r="X14" s="13"/>
       <c r="Y14" s="13"/>
     </row>
-    <row r="15" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" ht="17.25" customHeight="1">
       <c r="A15" s="2">
         <v>45398</v>
       </c>
@@ -3532,7 +3538,7 @@
       <c r="X15" s="13"/>
       <c r="Y15" s="13"/>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25">
       <c r="A16" s="2">
         <v>45401</v>
       </c>
@@ -3595,7 +3601,7 @@
       <c r="X16" s="18"/>
       <c r="Y16" s="18"/>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25">
       <c r="A17" s="4">
         <v>45421</v>
       </c>
@@ -3666,7 +3672,7 @@
       <c r="X17" s="18"/>
       <c r="Y17" s="18"/>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25">
       <c r="A18" s="26">
         <v>45474</v>
       </c>
@@ -3717,7 +3723,7 @@
       <c r="X18" s="18"/>
       <c r="Y18" s="18"/>
     </row>
-    <row r="19" spans="1:25" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:25" ht="17.25" customHeight="1" thickBot="1">
       <c r="A19" s="26">
         <v>45505</v>
       </c>
@@ -3768,7 +3774,7 @@
       <c r="X19" s="18"/>
       <c r="Y19" s="18"/>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25">
       <c r="A20" s="26"/>
       <c r="B20" s="26"/>
       <c r="C20" s="26"/>
@@ -3810,7 +3816,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y44"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="11.140625" customWidth="1"/>
@@ -3835,7 +3841,7 @@
     <col min="25" max="25" width="37.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3846,7 +3852,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" ht="30.75" thickBot="1">
       <c r="A2" s="145" t="s">
         <v>3</v>
       </c>
@@ -3923,7 +3929,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" ht="15" customHeight="1">
       <c r="A3" s="2">
         <v>45548</v>
       </c>
@@ -3988,7 +3994,7 @@
       <c r="X3" s="46"/>
       <c r="Y3" s="44"/>
     </row>
-    <row r="4" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" ht="15" customHeight="1">
       <c r="A4" s="2">
         <v>45555</v>
       </c>
@@ -4037,7 +4043,7 @@
       <c r="X4" s="15"/>
       <c r="Y4" s="13"/>
     </row>
-    <row r="5" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" ht="15" customHeight="1">
       <c r="A5" s="2">
         <v>45562</v>
       </c>
@@ -4086,7 +4092,7 @@
       <c r="X5" s="15"/>
       <c r="Y5" s="13"/>
     </row>
-    <row r="6" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" ht="15" customHeight="1">
       <c r="A6" s="2">
         <v>45576</v>
       </c>
@@ -4135,7 +4141,7 @@
       <c r="X6" s="15"/>
       <c r="Y6" s="13"/>
     </row>
-    <row r="7" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" ht="15" customHeight="1">
       <c r="A7" s="2">
         <v>45583</v>
       </c>
@@ -4184,7 +4190,7 @@
       <c r="X7" s="15"/>
       <c r="Y7" s="13"/>
     </row>
-    <row r="8" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" ht="15" customHeight="1">
       <c r="A8" s="2">
         <v>45596</v>
       </c>
@@ -4233,7 +4239,7 @@
       <c r="X8" s="15"/>
       <c r="Y8" s="13"/>
     </row>
-    <row r="9" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" ht="15" customHeight="1">
       <c r="A9" s="2">
         <v>45604</v>
       </c>
@@ -4282,7 +4288,7 @@
       <c r="X9" s="15"/>
       <c r="Y9" s="13"/>
     </row>
-    <row r="10" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" ht="15" customHeight="1">
       <c r="A10" s="2">
         <v>45611</v>
       </c>
@@ -4331,7 +4337,7 @@
       <c r="X10" s="15"/>
       <c r="Y10" s="13"/>
     </row>
-    <row r="11" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" ht="15" customHeight="1">
       <c r="A11" s="2">
         <v>45625</v>
       </c>
@@ -4380,7 +4386,7 @@
       <c r="X11" s="15"/>
       <c r="Y11" s="13"/>
     </row>
-    <row r="12" spans="1:25" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25" ht="15" customHeight="1" thickBot="1">
       <c r="A12" s="4">
         <v>45632</v>
       </c>
@@ -4437,20 +4443,20 @@
       <c r="X12" s="20"/>
       <c r="Y12" s="18"/>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25">
       <c r="A13" s="26"/>
       <c r="B13" s="26"/>
       <c r="C13" s="26"/>
       <c r="D13" s="26"/>
       <c r="I13" s="3"/>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25">
       <c r="A14" s="26"/>
       <c r="B14" s="26"/>
       <c r="C14" s="26"/>
       <c r="D14" s="26"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10">
       <c r="A29" s="61"/>
       <c r="B29" s="61"/>
       <c r="C29" s="61"/>
@@ -4462,59 +4468,59 @@
       <c r="I29" s="61"/>
       <c r="J29" s="61"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10">
       <c r="A31" s="60"/>
       <c r="B31" s="60"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10">
       <c r="A32" s="60"/>
       <c r="B32" s="60"/>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2">
       <c r="A33" s="60"/>
       <c r="B33" s="60"/>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2">
       <c r="A34" s="60"/>
       <c r="B34" s="60"/>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2">
       <c r="A35" s="60"/>
       <c r="B35" s="60"/>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2">
       <c r="A36" s="60"/>
       <c r="B36" s="60"/>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2">
       <c r="A37" s="60"/>
       <c r="B37" s="60"/>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2">
       <c r="A38" s="60"/>
       <c r="B38" s="60"/>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2">
       <c r="A39" s="60"/>
       <c r="B39" s="60"/>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2">
       <c r="A40" s="60"/>
       <c r="B40" s="60"/>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2">
       <c r="A41" s="60"/>
       <c r="B41" s="60"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2">
       <c r="A42" s="60"/>
       <c r="B42" s="60"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2">
       <c r="A43" s="60"/>
       <c r="B43" s="60"/>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2">
       <c r="A44" s="60"/>
       <c r="B44" s="60"/>
     </row>
@@ -4543,7 +4549,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12299A9A-6C0C-4F92-957E-FBFCB6211744}">
   <dimension ref="A1:Y45"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.5703125" customWidth="1"/>
     <col min="2" max="2" width="5.85546875" bestFit="1" customWidth="1"/>
@@ -4571,7 +4577,7 @@
     <col min="25" max="25" width="37.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4582,7 +4588,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" ht="27.75" customHeight="1" thickBot="1">
       <c r="A2" s="64" t="s">
         <v>3</v>
       </c>
@@ -4659,7 +4665,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" ht="15" customHeight="1">
       <c r="A3" s="2">
         <v>45694</v>
       </c>
@@ -4711,7 +4717,7 @@
       <c r="X3" s="46"/>
       <c r="Y3" s="44"/>
     </row>
-    <row r="4" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" ht="14.25" customHeight="1">
       <c r="A4" s="2">
         <v>45708</v>
       </c>
@@ -4769,7 +4775,7 @@
       <c r="X4" s="15"/>
       <c r="Y4" s="13"/>
     </row>
-    <row r="5" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" ht="14.25" customHeight="1">
       <c r="A5" s="2">
         <v>45722</v>
       </c>
@@ -4825,7 +4831,7 @@
       <c r="X5" s="15"/>
       <c r="Y5" s="13"/>
     </row>
-    <row r="6" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" ht="16.5" customHeight="1">
       <c r="A6" s="2">
         <v>45735</v>
       </c>
@@ -4881,7 +4887,7 @@
       <c r="X6" s="15"/>
       <c r="Y6" s="13"/>
     </row>
-    <row r="7" spans="1:25" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" ht="18" customHeight="1">
       <c r="A7" s="2">
         <v>45750</v>
       </c>
@@ -4935,7 +4941,7 @@
       <c r="X7" s="15"/>
       <c r="Y7" s="13"/>
     </row>
-    <row r="8" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" ht="16.5" customHeight="1">
       <c r="A8" s="2">
         <v>45751</v>
       </c>
@@ -4994,7 +5000,7 @@
       <c r="X8" s="15"/>
       <c r="Y8" s="13"/>
     </row>
-    <row r="9" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" ht="15.75" customHeight="1">
       <c r="A9" s="2">
         <v>45757</v>
       </c>
@@ -5056,7 +5062,7 @@
       <c r="X9" s="15"/>
       <c r="Y9" s="13"/>
     </row>
-    <row r="10" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" ht="15.75" customHeight="1">
       <c r="A10" s="2">
         <v>45758</v>
       </c>
@@ -5110,7 +5116,7 @@
       <c r="X10" s="20"/>
       <c r="Y10" s="18"/>
     </row>
-    <row r="11" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" ht="15.75" customHeight="1">
       <c r="A11" s="4">
         <v>45764</v>
       </c>
@@ -5170,7 +5176,7 @@
       <c r="X11" s="35"/>
       <c r="Y11" s="35"/>
     </row>
-    <row r="12" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" ht="15.75" customHeight="1">
       <c r="A12" s="4">
         <v>45771</v>
       </c>
@@ -5231,7 +5237,7 @@
       <c r="X12" s="35"/>
       <c r="Y12" s="35"/>
     </row>
-    <row r="13" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" ht="15.75" customHeight="1">
       <c r="A13" s="2">
         <v>45785</v>
       </c>
@@ -5284,7 +5290,7 @@
       <c r="X13" s="35"/>
       <c r="Y13" s="35"/>
     </row>
-    <row r="14" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" ht="15.75" customHeight="1">
       <c r="A14" s="4">
         <v>45799</v>
       </c>
@@ -5330,7 +5336,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" ht="15.75" customHeight="1">
       <c r="A15" s="4">
         <v>45805</v>
       </c>
@@ -5364,101 +5370,101 @@
         <v>250</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" ht="15.75" customHeight="1">
       <c r="A16" s="75"/>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2">
       <c r="A17" s="26"/>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2">
       <c r="A18" s="26"/>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2">
       <c r="A19" s="26"/>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2">
       <c r="A20" s="75"/>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2">
       <c r="A21" s="26"/>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2">
       <c r="A22" s="75"/>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2">
       <c r="A23" s="26"/>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2">
       <c r="A24" s="26"/>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2">
       <c r="A25" s="26"/>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2">
       <c r="A26" s="26"/>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2">
       <c r="A27" s="26"/>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2">
       <c r="A28" s="26"/>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2">
       <c r="B31" s="60"/>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2">
       <c r="A32" s="60"/>
       <c r="B32" s="60"/>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2">
       <c r="A33" s="60"/>
       <c r="B33" s="60"/>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2">
       <c r="A34" s="60"/>
       <c r="B34" s="60"/>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2">
       <c r="A35" s="60"/>
       <c r="B35" s="60"/>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2">
       <c r="A36" s="60"/>
       <c r="B36" s="60"/>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2">
       <c r="A37" s="60"/>
       <c r="B37" s="60"/>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2">
       <c r="A38" s="60"/>
       <c r="B38" s="60"/>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2">
       <c r="A39" s="60"/>
       <c r="B39" s="60"/>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2">
       <c r="A40" s="60"/>
       <c r="B40" s="60"/>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2">
       <c r="A41" s="60"/>
       <c r="B41" s="60"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2">
       <c r="A42" s="60"/>
       <c r="B42" s="60"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2">
       <c r="A43" s="60"/>
       <c r="B43" s="60"/>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2">
       <c r="A44" s="60"/>
       <c r="B44" s="60"/>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2">
       <c r="A45" s="60"/>
     </row>
   </sheetData>
@@ -5483,7 +5489,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{243C2AD8-98F5-4435-96A3-1C2CAB922825}">
   <dimension ref="A1:Y26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="14.5703125" customWidth="1"/>
@@ -5510,7 +5516,7 @@
     <col min="25" max="25" width="37.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5521,7 +5527,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" ht="30">
       <c r="A2" s="78" t="s">
         <v>3</v>
       </c>
@@ -5598,7 +5604,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" ht="15" customHeight="1" thickBot="1">
       <c r="A3" s="159">
         <v>45911</v>
       </c>
@@ -5661,7 +5667,7 @@
       <c r="X3" s="46"/>
       <c r="Y3" s="44"/>
     </row>
-    <row r="4" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" ht="15" customHeight="1">
       <c r="A4" s="160">
         <v>45917</v>
       </c>
@@ -5730,7 +5736,7 @@
       <c r="X4" s="15"/>
       <c r="Y4" s="13"/>
     </row>
-    <row r="5" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" ht="15" customHeight="1">
       <c r="A5" s="160">
         <v>45926</v>
       </c>
@@ -5788,7 +5794,7 @@
       <c r="X5" s="15"/>
       <c r="Y5" s="13"/>
     </row>
-    <row r="6" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" ht="15" customHeight="1">
       <c r="A6" s="160">
         <v>45939</v>
       </c>
@@ -5852,7 +5858,7 @@
       <c r="X6" s="15"/>
       <c r="Y6" s="13"/>
     </row>
-    <row r="7" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" ht="15" customHeight="1">
       <c r="A7" s="160">
         <v>45946</v>
       </c>
@@ -5909,7 +5915,7 @@
       <c r="X7" s="15"/>
       <c r="Y7" s="13"/>
     </row>
-    <row r="8" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" ht="15" customHeight="1">
       <c r="A8" s="160">
         <v>45953</v>
       </c>
@@ -5967,7 +5973,7 @@
       <c r="X8" s="15"/>
       <c r="Y8" s="13"/>
     </row>
-    <row r="9" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" ht="15" customHeight="1">
       <c r="A9" s="160">
         <v>45967</v>
       </c>
@@ -6029,7 +6035,7 @@
       <c r="X9" s="15"/>
       <c r="Y9" s="13"/>
     </row>
-    <row r="10" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" ht="15" customHeight="1">
       <c r="A10" s="160">
         <v>45974</v>
       </c>
@@ -6092,7 +6098,7 @@
       <c r="X10" s="15"/>
       <c r="Y10" s="13"/>
     </row>
-    <row r="11" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" ht="15" customHeight="1">
       <c r="A11" s="160">
         <v>45980</v>
       </c>
@@ -6143,7 +6149,7 @@
       <c r="X11" s="35"/>
       <c r="Y11" s="35"/>
     </row>
-    <row r="12" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" ht="16.5" customHeight="1">
       <c r="A12" s="160">
         <f>A10+7</f>
         <v>45981</v>
@@ -6196,7 +6202,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25">
       <c r="A13" s="160">
         <v>45986</v>
       </c>
@@ -6232,7 +6238,7 @@
       <c r="M13" s="158"/>
       <c r="N13" s="158"/>
     </row>
-    <row r="14" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" ht="15" customHeight="1">
       <c r="A14" s="160">
         <v>45988</v>
       </c>
@@ -6287,7 +6293,7 @@
       <c r="X14" s="15"/>
       <c r="Y14" s="13"/>
     </row>
-    <row r="15" spans="1:25" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25" ht="15" customHeight="1" thickBot="1">
       <c r="A15" s="161">
         <v>45995</v>
       </c>
@@ -6350,35 +6356,35 @@
       <c r="X15" s="15"/>
       <c r="Y15" s="13"/>
     </row>
-    <row r="16" spans="1:25" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:25" ht="15" customHeight="1" thickBot="1">
       <c r="A16" s="26"/>
       <c r="B16" s="26"/>
       <c r="C16" s="26"/>
       <c r="X16" s="20"/>
       <c r="Y16" s="18"/>
     </row>
-    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="15" customHeight="1">
       <c r="A17" s="26"/>
       <c r="B17" s="26"/>
       <c r="C17" s="26"/>
     </row>
-    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="15" customHeight="1">
       <c r="A18" s="26"/>
       <c r="B18" s="26"/>
       <c r="C18" s="26"/>
     </row>
-    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="15" customHeight="1">
       <c r="A19" s="26"/>
       <c r="B19" s="26"/>
       <c r="C19" s="26"/>
     </row>
-    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="1:3" ht="15" customHeight="1"/>
+    <row r="21" spans="1:3" ht="15" customHeight="1"/>
+    <row r="22" spans="1:3" ht="15" customHeight="1"/>
+    <row r="23" spans="1:3" ht="15" customHeight="1"/>
+    <row r="24" spans="1:3" ht="15" customHeight="1"/>
+    <row r="25" spans="1:3" ht="15" customHeight="1"/>
+    <row r="26" spans="1:3" ht="15" customHeight="1"/>
   </sheetData>
   <protectedRanges>
     <protectedRange algorithmName="SHA-512" hashValue="pQyTzP/d7t5ThMimBt5mu8gGozgAm1OwF6BMILsn5/kmtZ5mZf81NMi09wwU8mvtItxf0EVNWa6V4MCa0DKeSQ==" saltValue="NzZBiAQ1yFjat+SeIqh2Uw==" spinCount="100000" sqref="A3:E19" name="Range3_1"/>
@@ -6412,7 +6418,7 @@
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="A1:Y18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.5703125" customWidth="1"/>
     <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
@@ -6439,7 +6445,7 @@
     <col min="25" max="25" width="37.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6450,7 +6456,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" ht="30">
       <c r="A2" s="64" t="s">
         <v>3</v>
       </c>
@@ -6527,7 +6533,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" ht="15" customHeight="1">
       <c r="A3" s="75">
         <v>46051</v>
       </c>
@@ -6576,7 +6582,7 @@
       <c r="X3" s="46"/>
       <c r="Y3" s="44"/>
     </row>
-    <row r="4" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" ht="15.75" customHeight="1">
       <c r="A4" s="75">
         <f>A3+12</f>
         <v>46063</v>
@@ -6627,7 +6633,7 @@
       <c r="X4" s="15"/>
       <c r="Y4" s="13"/>
     </row>
-    <row r="5" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" ht="18.75" customHeight="1">
       <c r="A5" s="75">
         <f>A4+16</f>
         <v>46079</v>
@@ -6682,7 +6688,7 @@
       <c r="X5" s="15"/>
       <c r="Y5" s="13"/>
     </row>
-    <row r="6" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" ht="15.75" customHeight="1">
       <c r="A6" s="75">
         <f>A5+14</f>
         <v>46093</v>
@@ -6737,7 +6743,7 @@
       <c r="X6" s="15"/>
       <c r="Y6" s="13"/>
     </row>
-    <row r="7" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" ht="15.75" customHeight="1">
       <c r="A7" s="75">
         <f>A6+7</f>
         <v>46100</v>
@@ -6791,7 +6797,7 @@
       <c r="X7" s="15"/>
       <c r="Y7" s="13"/>
     </row>
-    <row r="8" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" ht="17.25" customHeight="1">
       <c r="A8" s="75">
         <f>A6+14</f>
         <v>46107</v>
@@ -6844,7 +6850,7 @@
       <c r="X8" s="15"/>
       <c r="Y8" s="13"/>
     </row>
-    <row r="9" spans="1:25" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" ht="18" customHeight="1">
       <c r="A9" s="75">
         <f>A8+7</f>
         <v>46114</v>
@@ -6898,7 +6904,7 @@
       <c r="X9" s="15"/>
       <c r="Y9" s="13"/>
     </row>
-    <row r="10" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" ht="15" customHeight="1">
       <c r="A10" s="75">
         <v>46120</v>
       </c>
@@ -6947,7 +6953,7 @@
       <c r="X10" s="15"/>
       <c r="Y10" s="13"/>
     </row>
-    <row r="11" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" ht="14.25" customHeight="1">
       <c r="A11" s="75">
         <v>46121</v>
       </c>
@@ -6998,7 +7004,7 @@
       <c r="X11" s="15"/>
       <c r="Y11" s="13"/>
     </row>
-    <row r="12" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" ht="16.5" customHeight="1">
       <c r="A12" s="75">
         <v>46128</v>
       </c>
@@ -7051,7 +7057,7 @@
       <c r="X12" s="15"/>
       <c r="Y12" s="13"/>
     </row>
-    <row r="13" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" ht="18.75" customHeight="1">
       <c r="A13" s="75">
         <v>46135</v>
       </c>
@@ -7080,7 +7086,7 @@
         <v>376</v>
       </c>
       <c r="J13" s="98" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K13" s="102"/>
       <c r="L13" s="5"/>
@@ -7098,7 +7104,7 @@
       <c r="X13" s="15"/>
       <c r="Y13" s="13"/>
     </row>
-    <row r="14" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" ht="18.75" customHeight="1">
       <c r="A14" s="75">
         <v>46142</v>
       </c>
@@ -7106,7 +7112,7 @@
         <v>259</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D14" s="27" t="s">
         <v>278</v>
@@ -7115,26 +7121,26 @@
         <v>14</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H14" s="14" t="s">
-        <v>431</v>
+        <v>381</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>432</v>
+        <v>382</v>
       </c>
       <c r="J14" s="107" t="s">
-        <v>433</v>
+        <v>383</v>
       </c>
       <c r="K14" s="102" t="s">
-        <v>435</v>
+        <v>384</v>
       </c>
       <c r="L14" s="14"/>
       <c r="M14" s="102" t="s">
-        <v>434</v>
+        <v>385</v>
       </c>
       <c r="N14" s="14"/>
       <c r="O14" s="35"/>
@@ -7149,7 +7155,7 @@
       <c r="X14" s="15"/>
       <c r="Y14" s="13"/>
     </row>
-    <row r="15" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25" ht="15.75" thickBot="1">
       <c r="A15" s="26">
         <v>46156</v>
       </c>
@@ -7157,7 +7163,7 @@
         <v>190</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D15" t="s">
         <v>278</v>
@@ -7166,34 +7172,34 @@
         <v>16</v>
       </c>
       <c r="F15" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="G15" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="H15" t="s">
         <v>40</v>
       </c>
       <c r="I15" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="J15" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="X15" s="20"/>
       <c r="Y15" s="18"/>
     </row>
-    <row r="16" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" ht="12.75" customHeight="1">
       <c r="A16" s="26"/>
       <c r="B16" s="26"/>
       <c r="C16" s="26"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3">
       <c r="A17" s="26"/>
       <c r="B17" s="26"/>
       <c r="C17" s="26"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3">
       <c r="A18" s="26"/>
       <c r="B18" s="26"/>
       <c r="C18" s="26"/>
@@ -7230,7 +7236,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A33E49C-EC2E-42B7-80E4-DD607C0B7A89}">
   <dimension ref="A1:Y13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.5703125" customWidth="1"/>
     <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
@@ -7257,7 +7263,7 @@
     <col min="25" max="25" width="37.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" ht="15.75" thickBot="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7268,7 +7274,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" ht="30.75" thickBot="1">
       <c r="A2" s="64" t="s">
         <v>3</v>
       </c>
@@ -7345,7 +7351,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" ht="15" customHeight="1">
       <c r="A3" s="75">
         <v>46275</v>
       </c>
@@ -7364,19 +7370,19 @@
         <v>1</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="H3" s="14" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="I3" s="98" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="J3" s="98" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="K3" s="73"/>
       <c r="L3" s="40"/>
@@ -7394,7 +7400,7 @@
       <c r="X3" s="46"/>
       <c r="Y3" s="44"/>
     </row>
-    <row r="4" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" ht="15.75" customHeight="1">
       <c r="A4" s="75">
         <f>A3+14</f>
         <v>46289</v>
@@ -7415,19 +7421,19 @@
         <v>3</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="I4" s="98" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="J4" s="98" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="K4" s="102"/>
       <c r="L4" s="5"/>
@@ -7445,7 +7451,7 @@
       <c r="X4" s="15"/>
       <c r="Y4" s="13"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25">
       <c r="A5" s="75">
         <f t="shared" ref="A5" si="2">A4+14</f>
         <v>46303</v>
@@ -7466,19 +7472,19 @@
         <v>5</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="I5" s="98" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="J5" s="98" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="K5" s="102"/>
       <c r="L5" s="5"/>
@@ -7500,7 +7506,7 @@
       <c r="X5" s="15"/>
       <c r="Y5" s="13"/>
     </row>
-    <row r="6" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" ht="15.75" customHeight="1">
       <c r="A6" s="75">
         <f>A5+14</f>
         <v>46317</v>
@@ -7521,19 +7527,19 @@
         <v>7</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="I6" s="98" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="J6" s="98" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="K6" s="102"/>
       <c r="L6" s="5"/>
@@ -7551,7 +7557,7 @@
       <c r="X6" s="15"/>
       <c r="Y6" s="13"/>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25">
       <c r="A7" s="75">
         <f>A6+14</f>
         <v>46331</v>
@@ -7572,19 +7578,19 @@
         <v>9</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="I7" s="98" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="J7" s="98" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="K7" s="102"/>
       <c r="L7" s="5"/>
@@ -7602,7 +7608,7 @@
       <c r="X7" s="15"/>
       <c r="Y7" s="13"/>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25">
       <c r="A8" s="75">
         <f>A7+14</f>
         <v>46345</v>
@@ -7621,19 +7627,19 @@
         <v>11</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="I8" s="98" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="J8" s="98" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="K8" s="102"/>
       <c r="L8" s="5"/>
@@ -7651,7 +7657,7 @@
       <c r="X8" s="15"/>
       <c r="Y8" s="13"/>
     </row>
-    <row r="9" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" ht="18.75" customHeight="1">
       <c r="A9" s="75">
         <v>46121</v>
       </c>
@@ -7659,7 +7665,7 @@
         <v>190</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D9" s="27" t="s">
         <v>278</v>
@@ -7668,19 +7674,19 @@
         <v>13</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="I9" s="98" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="J9" s="98" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="K9" s="102"/>
       <c r="L9" s="5"/>
@@ -7698,24 +7704,24 @@
       <c r="X9" s="15"/>
       <c r="Y9" s="13"/>
     </row>
-    <row r="10" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25" ht="15.75" thickBot="1">
       <c r="A10" s="26"/>
       <c r="B10" s="26"/>
       <c r="C10" s="26"/>
       <c r="X10" s="20"/>
       <c r="Y10" s="18"/>
     </row>
-    <row r="11" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" ht="12.75" customHeight="1">
       <c r="A11" s="26"/>
       <c r="B11" s="26"/>
       <c r="C11" s="26"/>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25">
       <c r="A12" s="26"/>
       <c r="B12" s="26"/>
       <c r="C12" s="26"/>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25">
       <c r="A13" s="26"/>
       <c r="B13" s="26"/>
       <c r="C13" s="26"/>
@@ -7737,212 +7743,212 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AEC079F-155A-491D-9189-1418FC903287}">
   <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.28515625" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
     <col min="3" max="3" width="20.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" s="55" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="B2" s="54" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="C2" s="54" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" s="136" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="B3" s="137"/>
       <c r="C3" s="138" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" s="5" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="B4" s="52"/>
       <c r="C4" s="50" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" s="52" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="B5" s="52"/>
       <c r="C5" s="50" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" s="52" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="B6" s="52" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="C6" s="50" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" s="52" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="B7" s="52" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="C7" s="50" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" s="52" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="B8" s="52" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="C8" s="50" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" s="52" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="B9" s="52"/>
       <c r="C9" s="50"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" s="52" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="B10" s="52" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="C10" s="50" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
       <c r="A11" s="52" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="B11" s="52" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="C11" s="50" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
       <c r="A12" s="52" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="B12" s="52" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="C12" s="50" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
       <c r="A13" s="52" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="B13" s="52" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="C13" s="50" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
       <c r="A14" s="52" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="B14" s="52" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="C14" s="50" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
       <c r="A15" s="52" t="s">
+        <v>417</v>
+      </c>
+      <c r="B15" s="52" t="s">
+        <v>418</v>
+      </c>
+      <c r="C15" s="50" t="s">
         <v>410</v>
       </c>
-      <c r="B15" s="52" t="s">
-        <v>411</v>
-      </c>
-      <c r="C15" s="50" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:3">
       <c r="A16" s="137" t="s">
         <v>321</v>
       </c>
       <c r="B16" s="137" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="C16" s="139" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17" s="137" t="s">
         <v>346</v>
       </c>
       <c r="B17" s="137" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="C17" s="139" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18" s="52" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="B18" s="52" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="C18" s="50" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3">
       <c r="A19" s="53" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="B19" s="53" t="s">
         <v>230</v>
       </c>
       <c r="C19" s="51" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="B20" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
     </row>
   </sheetData>
@@ -7958,24 +7964,24 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AD19DE5-C22F-4D41-B540-76D70438E18B}">
   <dimension ref="A1:I16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.85546875" customWidth="1"/>
     <col min="6" max="6" width="14.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="15.75" thickBot="1">
       <c r="A1" s="135" t="s">
         <v>3</v>
       </c>
       <c r="B1" s="131" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="C1" s="130" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="169">
         <v>46051</v>
       </c>
@@ -7983,14 +7989,14 @@
         <v>1</v>
       </c>
       <c r="C2" s="170" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="F2" s="75"/>
       <c r="G2" s="77"/>
       <c r="H2" s="29"/>
       <c r="I2" s="55"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9">
       <c r="A3" s="171">
         <f>A2+7</f>
         <v>46058</v>
@@ -8000,14 +8006,14 @@
         <v>2</v>
       </c>
       <c r="C3" s="170" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="F3" s="75"/>
       <c r="G3" s="2"/>
       <c r="H3" s="26"/>
       <c r="I3" s="27"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9">
       <c r="A4" s="171">
         <f t="shared" ref="A4:A12" si="0">A3+7</f>
         <v>46065</v>
@@ -8017,14 +8023,14 @@
         <v>3</v>
       </c>
       <c r="C4" s="170" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="F4" s="75"/>
       <c r="G4" s="2"/>
       <c r="H4" s="26"/>
       <c r="I4" s="27"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9">
       <c r="A5" s="171">
         <f t="shared" si="0"/>
         <v>46072</v>
@@ -8034,14 +8040,14 @@
         <v>4</v>
       </c>
       <c r="C5" s="170" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="F5" s="75"/>
       <c r="G5" s="2"/>
       <c r="H5" s="26"/>
       <c r="I5" s="27"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9">
       <c r="A6" s="133">
         <f t="shared" si="0"/>
         <v>46079</v>
@@ -8051,14 +8057,14 @@
         <v>5</v>
       </c>
       <c r="C6" s="134" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="F6" s="75"/>
       <c r="G6" s="2"/>
       <c r="H6" s="26"/>
       <c r="I6" s="27"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9">
       <c r="A7" s="133">
         <f t="shared" si="0"/>
         <v>46086</v>
@@ -8068,14 +8074,14 @@
         <v>6</v>
       </c>
       <c r="C7" s="134" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="F7" s="75"/>
       <c r="G7" s="2"/>
       <c r="H7" s="26"/>
       <c r="I7" s="27"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9">
       <c r="A8" s="133">
         <f t="shared" si="0"/>
         <v>46093</v>
@@ -8085,14 +8091,14 @@
         <v>7</v>
       </c>
       <c r="C8" s="134" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="F8" s="75"/>
       <c r="G8" s="2"/>
       <c r="H8" s="26"/>
       <c r="I8" s="27"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9">
       <c r="A9" s="133">
         <f t="shared" si="0"/>
         <v>46100</v>
@@ -8102,14 +8108,14 @@
         <v>8</v>
       </c>
       <c r="C9" s="134" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="F9" s="75"/>
       <c r="G9" s="2"/>
       <c r="H9" s="26"/>
       <c r="I9" s="27"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9">
       <c r="A10" s="133">
         <f t="shared" si="0"/>
         <v>46107</v>
@@ -8119,14 +8125,14 @@
         <v>9</v>
       </c>
       <c r="C10" s="134" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="F10" s="75"/>
       <c r="G10" s="2"/>
       <c r="H10" s="26"/>
       <c r="I10" s="27"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9">
       <c r="A11" s="133">
         <f t="shared" si="0"/>
         <v>46114</v>
@@ -8136,10 +8142,10 @@
         <v>10</v>
       </c>
       <c r="C11" s="134" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="133">
         <f t="shared" si="0"/>
         <v>46121</v>
@@ -8149,10 +8155,10 @@
         <v>11</v>
       </c>
       <c r="C12" s="134" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="133">
         <f t="shared" ref="A13:A14" si="3">A12+7</f>
         <v>46128</v>
@@ -8162,10 +8168,10 @@
         <v>12</v>
       </c>
       <c r="C13" s="134" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="133">
         <f t="shared" si="3"/>
         <v>46135</v>
@@ -8175,15 +8181,15 @@
         <v>13</v>
       </c>
       <c r="C14" s="134" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="133"/>
       <c r="B15" s="134"/>
       <c r="C15" s="134"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9">
       <c r="G16" s="26"/>
     </row>
   </sheetData>
@@ -8210,7 +8216,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2BB5C5F-5790-4A91-A6E8-8841719DA1FC}">
   <dimension ref="A2:I20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.42578125" customWidth="1"/>
     <col min="2" max="2" width="9.140625" customWidth="1"/>
@@ -8222,17 +8228,17 @@
     <col min="9" max="9" width="64.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" ht="23.25">
       <c r="A2" s="91" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="18.75">
       <c r="A3" s="79" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="37.5" x14ac:dyDescent="0.25">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="37.5">
       <c r="A5" s="80" t="s">
         <v>3</v>
       </c>
@@ -8255,13 +8261,13 @@
         <v>9</v>
       </c>
       <c r="H5" s="82" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="I5" s="81" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="18.75">
       <c r="A6" s="92">
         <v>45694</v>
       </c>
@@ -8285,10 +8291,10 @@
       </c>
       <c r="H6" s="85"/>
       <c r="I6" s="84" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="18.75">
       <c r="A7" s="83">
         <v>45708</v>
       </c>
@@ -8317,7 +8323,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="18.75">
       <c r="A8" s="83">
         <v>45722</v>
       </c>
@@ -8344,7 +8350,7 @@
       </c>
       <c r="I8" s="86"/>
     </row>
-    <row r="9" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="18.75">
       <c r="A9" s="83">
         <v>45735</v>
       </c>
@@ -8355,7 +8361,7 @@
         <v>198</v>
       </c>
       <c r="D9" s="94" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="E9" s="94">
         <v>8</v>
@@ -8370,10 +8376,10 @@
         <v>206</v>
       </c>
       <c r="I9" s="86" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="18.75">
       <c r="A10" s="83">
         <v>45744</v>
       </c>
@@ -8400,7 +8406,7 @@
       </c>
       <c r="I10" s="86"/>
     </row>
-    <row r="11" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="18.75">
       <c r="A11" s="83">
         <v>45750</v>
       </c>
@@ -8417,17 +8423,17 @@
         <v>10</v>
       </c>
       <c r="F11" s="87" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="G11" s="87" t="s">
         <v>68</v>
       </c>
       <c r="H11" s="87"/>
       <c r="I11" s="86" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="18.75">
       <c r="A12" s="83">
         <v>45758</v>
       </c>
@@ -8453,10 +8459,10 @@
         <v>31</v>
       </c>
       <c r="I12" s="86" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="18.75">
       <c r="A13" s="83">
         <v>45764</v>
       </c>
@@ -8473,13 +8479,13 @@
         <v>12</v>
       </c>
       <c r="F13" s="87" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="G13" s="87"/>
       <c r="H13" s="87"/>
       <c r="I13" s="86"/>
     </row>
-    <row r="14" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="18.75">
       <c r="A14" s="88">
         <v>45771</v>
       </c>
@@ -8496,7 +8502,7 @@
         <v>13</v>
       </c>
       <c r="F14" s="90" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="G14" s="90" t="s">
         <v>77</v>
@@ -8508,7 +8514,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="20" spans="8:8" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="20" spans="8:8" ht="18.75">
       <c r="H20" s="79"/>
     </row>
   </sheetData>

--- a/data/MACSI seminar series.xlsx
+++ b/data/MACSI seminar series.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ulcampus-my.sharepoint.com/personal/david_osullivan_ul_ie/Documents/Academic_work/_Misc/MACSI Seminars/macsi-seminars.github.io/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="416" documentId="13_ncr:1_{12BE53B5-C8C7-44FE-8280-19C653D9122E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8ABB13C-981A-4743-ABF0-CA69466D205E}"/>
+  <xr:revisionPtr revIDLastSave="420" documentId="13_ncr:1_{12BE53B5-C8C7-44FE-8280-19C653D9122E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C7A8884-F82B-402B-8234-55823CB0D8A3}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1268,6 +1268,9 @@
     <t>https://ffaucher.gitlab.io/cv/</t>
   </si>
   <si>
+    <t>Wednesday</t>
+  </si>
+  <si>
     <t>Alan Demlow</t>
   </si>
   <si>
@@ -1410,9 +1413,6 @@
   </si>
   <si>
     <t>Deptartmental contact</t>
-  </si>
-  <si>
-    <t>Wednesday</t>
   </si>
   <si>
     <t>Robery Garvey</t>
@@ -7157,7 +7157,7 @@
     </row>
     <row r="15" spans="1:25" ht="15.75" thickBot="1">
       <c r="A15" s="26">
-        <v>46156</v>
+        <v>46155</v>
       </c>
       <c r="B15" s="26" t="s">
         <v>190</v>
@@ -7166,25 +7166,25 @@
         <v>378</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>386</v>
       </c>
       <c r="E15">
         <v>16</v>
       </c>
       <c r="F15" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="G15" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H15" t="s">
         <v>40</v>
       </c>
       <c r="I15" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J15" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="X15" s="20"/>
       <c r="Y15" s="18"/>
@@ -7370,19 +7370,19 @@
         <v>1</v>
       </c>
       <c r="F3" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="G3" s="14" t="s">
         <v>389</v>
       </c>
-      <c r="G3" s="14" t="s">
-        <v>388</v>
-      </c>
       <c r="H3" s="14" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I3" s="98" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J3" s="98" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K3" s="73"/>
       <c r="L3" s="40"/>
@@ -7421,19 +7421,19 @@
         <v>3</v>
       </c>
       <c r="F4" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="G4" s="14" t="s">
         <v>389</v>
       </c>
-      <c r="G4" s="14" t="s">
-        <v>388</v>
-      </c>
       <c r="H4" s="5" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I4" s="98" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J4" s="98" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K4" s="102"/>
       <c r="L4" s="5"/>
@@ -7472,19 +7472,19 @@
         <v>5</v>
       </c>
       <c r="F5" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="G5" s="14" t="s">
         <v>389</v>
       </c>
-      <c r="G5" s="14" t="s">
-        <v>388</v>
-      </c>
       <c r="H5" s="14" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I5" s="98" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J5" s="98" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K5" s="102"/>
       <c r="L5" s="5"/>
@@ -7527,19 +7527,19 @@
         <v>7</v>
       </c>
       <c r="F6" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="G6" s="14" t="s">
         <v>389</v>
       </c>
-      <c r="G6" s="14" t="s">
-        <v>388</v>
-      </c>
       <c r="H6" s="14" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I6" s="98" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J6" s="98" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K6" s="102"/>
       <c r="L6" s="5"/>
@@ -7578,19 +7578,19 @@
         <v>9</v>
       </c>
       <c r="F7" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="G7" s="14" t="s">
         <v>389</v>
       </c>
-      <c r="G7" s="14" t="s">
-        <v>388</v>
-      </c>
       <c r="H7" s="14" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I7" s="98" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J7" s="98" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K7" s="102"/>
       <c r="L7" s="5"/>
@@ -7627,19 +7627,19 @@
         <v>11</v>
       </c>
       <c r="F8" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="G8" s="14" t="s">
         <v>389</v>
       </c>
-      <c r="G8" s="14" t="s">
-        <v>388</v>
-      </c>
       <c r="H8" s="14" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I8" s="98" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J8" s="98" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K8" s="102"/>
       <c r="L8" s="5"/>
@@ -7674,19 +7674,19 @@
         <v>13</v>
       </c>
       <c r="F9" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="G9" s="14" t="s">
         <v>389</v>
       </c>
-      <c r="G9" s="14" t="s">
-        <v>388</v>
-      </c>
       <c r="H9" s="14" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I9" s="98" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J9" s="98" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K9" s="102"/>
       <c r="L9" s="5"/>
@@ -7752,23 +7752,23 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="55" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B2" s="54" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C2" s="54" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="136" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B3" s="137"/>
       <c r="C3" s="138" t="s">
@@ -7777,7 +7777,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="5" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B4" s="52"/>
       <c r="C4" s="50" t="s">
@@ -7786,19 +7786,19 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="52" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B5" s="52"/>
       <c r="C5" s="50" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="52" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B6" s="52" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C6" s="50" t="s">
         <v>87</v>
@@ -7806,10 +7806,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="52" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B7" s="52" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C7" s="50" t="s">
         <v>87</v>
@@ -7817,10 +7817,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="52" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B8" s="52" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C8" s="50" t="s">
         <v>101</v>
@@ -7828,75 +7828,75 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="52" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B9" s="52"/>
       <c r="C9" s="50"/>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="52" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B10" s="52" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C10" s="50" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="52" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B11" s="52" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C11" s="50" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="52" t="s">
+        <v>412</v>
+      </c>
+      <c r="B12" s="52" t="s">
+        <v>413</v>
+      </c>
+      <c r="C12" s="50" t="s">
         <v>411</v>
-      </c>
-      <c r="B12" s="52" t="s">
-        <v>412</v>
-      </c>
-      <c r="C12" s="50" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="52" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B13" s="52" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C13" s="50" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="52" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B14" s="52" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C14" s="50" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="52" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B15" s="52" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C15" s="50" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -7904,10 +7904,10 @@
         <v>321</v>
       </c>
       <c r="B16" s="137" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C16" s="139" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -7915,18 +7915,18 @@
         <v>346</v>
       </c>
       <c r="B17" s="137" t="s">
+        <v>422</v>
+      </c>
+      <c r="C17" s="139" t="s">
         <v>421</v>
-      </c>
-      <c r="C17" s="139" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="52" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B18" s="52" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C18" s="50" t="s">
         <v>87</v>
@@ -7934,21 +7934,21 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="53" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B19" s="53" t="s">
         <v>230</v>
       </c>
       <c r="C19" s="51" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B20" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
   </sheetData>
@@ -7975,10 +7975,10 @@
         <v>3</v>
       </c>
       <c r="B1" s="131" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C1" s="130" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -7989,7 +7989,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="170" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F2" s="75"/>
       <c r="G2" s="77"/>
@@ -8006,7 +8006,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="170" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F3" s="75"/>
       <c r="G3" s="2"/>
@@ -8023,7 +8023,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="170" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F4" s="75"/>
       <c r="G4" s="2"/>
@@ -8040,7 +8040,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="170" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F5" s="75"/>
       <c r="G5" s="2"/>
@@ -8057,7 +8057,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="134" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F6" s="75"/>
       <c r="G6" s="2"/>
@@ -8074,7 +8074,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="134" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F7" s="75"/>
       <c r="G7" s="2"/>
@@ -8091,7 +8091,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="134" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F8" s="75"/>
       <c r="G8" s="2"/>
@@ -8108,7 +8108,7 @@
         <v>8</v>
       </c>
       <c r="C9" s="134" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F9" s="75"/>
       <c r="G9" s="2"/>
@@ -8125,7 +8125,7 @@
         <v>9</v>
       </c>
       <c r="C10" s="134" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F10" s="75"/>
       <c r="G10" s="2"/>
@@ -8142,7 +8142,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="134" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -8155,7 +8155,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="134" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -8168,7 +8168,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="134" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -8181,7 +8181,7 @@
         <v>13</v>
       </c>
       <c r="C14" s="134" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -8230,12 +8230,12 @@
   <sheetData>
     <row r="2" spans="1:9" ht="23.25">
       <c r="A2" s="91" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="18.75">
       <c r="A3" s="79" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="37.5">
@@ -8261,7 +8261,7 @@
         <v>9</v>
       </c>
       <c r="H5" s="82" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="I5" s="81" t="s">
         <v>11</v>
@@ -8291,7 +8291,7 @@
       </c>
       <c r="H6" s="85"/>
       <c r="I6" s="84" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="18.75">
@@ -8361,7 +8361,7 @@
         <v>198</v>
       </c>
       <c r="D9" s="94" t="s">
-        <v>434</v>
+        <v>386</v>
       </c>
       <c r="E9" s="94">
         <v>8</v>
@@ -8376,7 +8376,7 @@
         <v>206</v>
       </c>
       <c r="I9" s="86" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="18.75">
@@ -8430,7 +8430,7 @@
       </c>
       <c r="H11" s="87"/>
       <c r="I11" s="86" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="18.75">
@@ -8459,7 +8459,7 @@
         <v>31</v>
       </c>
       <c r="I12" s="86" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="18.75">

--- a/data/MACSI seminar series.xlsx
+++ b/data/MACSI seminar series.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30015"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30023"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ulcampus-my.sharepoint.com/personal/david_osullivan_ul_ie/Documents/Academic_work/_Misc/MACSI Seminars/macsi-seminars.github.io/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="420" documentId="13_ncr:1_{12BE53B5-C8C7-44FE-8280-19C653D9122E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C7A8884-F82B-402B-8234-55823CB0D8A3}"/>
+  <xr:revisionPtr revIDLastSave="425" documentId="13_ncr:1_{12BE53B5-C8C7-44FE-8280-19C653D9122E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E089D2C8-8CBB-4B2D-8A10-033012470ED4}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="440">
   <si>
     <t>Fill in as much of the green boxes as possible. Ideally, this would be before you have finished your visitors travel dates (just to avoid double booking).</t>
   </si>
@@ -1277,10 +1277,17 @@
     <t>Texas A&amp;M</t>
   </si>
   <si>
+    <t>Finite element methods for the surface Stokes equations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The surface Navier-Stokes equations are used to describe fluid flows on surfaces.  A paradigm physical example is modeling the deformation of fluidic membranes.  Constructing finite element methods for surface Stokes problems has proved challenging because the canonical finite element methods for Euclidean Stokes problems do not easily translate to the surface context.  In this talk we will first review the basics of finite element methods for scalar elliptic problems posed on Euclidean domains and surfaces.  We will then briefly discuss construction of finite element methods for Euclidean Stokes problems and describe obstacles to the development of surface Stokes FEM.   Finally, we describe a new approach that yields effective translation of Euclidean Stokes elements such as the canonical Taylor-Hood elements to the surface Stokes context.  
+</t>
+  </si>
+  <si>
+    <t>Open</t>
+  </si>
+  <si>
     <t>TBC</t>
-  </si>
-  <si>
-    <t>Open</t>
   </si>
   <si>
     <t>This is a just a place for those who are interested but that dont have a specific date in mind. (Ideally, a couple of these are people that we could invite with relatively short notice to fill missing slots.)</t>
@@ -7155,7 +7162,7 @@
       <c r="X14" s="15"/>
       <c r="Y14" s="13"/>
     </row>
-    <row r="15" spans="1:25" ht="15.75" thickBot="1">
+    <row r="15" spans="1:25" ht="20.25" customHeight="1">
       <c r="A15" s="26">
         <v>46155</v>
       </c>
@@ -7183,8 +7190,8 @@
       <c r="I15" t="s">
         <v>389</v>
       </c>
-      <c r="J15" t="s">
-        <v>389</v>
+      <c r="J15" s="129" t="s">
+        <v>390</v>
       </c>
       <c r="X15" s="20"/>
       <c r="Y15" s="18"/>
@@ -7370,19 +7377,19 @@
         <v>1</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="H3" s="14" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="I3" s="98" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="J3" s="98" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="K3" s="73"/>
       <c r="L3" s="40"/>
@@ -7421,19 +7428,19 @@
         <v>3</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="I4" s="98" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="J4" s="98" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="K4" s="102"/>
       <c r="L4" s="5"/>
@@ -7472,19 +7479,19 @@
         <v>5</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="I5" s="98" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="J5" s="98" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="K5" s="102"/>
       <c r="L5" s="5"/>
@@ -7527,19 +7534,19 @@
         <v>7</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="I6" s="98" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="J6" s="98" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="K6" s="102"/>
       <c r="L6" s="5"/>
@@ -7578,19 +7585,19 @@
         <v>9</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="I7" s="98" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="J7" s="98" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="K7" s="102"/>
       <c r="L7" s="5"/>
@@ -7627,19 +7634,19 @@
         <v>11</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="I8" s="98" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="J8" s="98" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="K8" s="102"/>
       <c r="L8" s="5"/>
@@ -7674,19 +7681,19 @@
         <v>13</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="I9" s="98" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="J9" s="98" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="K9" s="102"/>
       <c r="L9" s="5"/>
@@ -7752,23 +7759,23 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="55" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B2" s="54" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C2" s="54" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="136" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B3" s="137"/>
       <c r="C3" s="138" t="s">
@@ -7777,7 +7784,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="5" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B4" s="52"/>
       <c r="C4" s="50" t="s">
@@ -7786,19 +7793,19 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="52" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B5" s="52"/>
       <c r="C5" s="50" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="52" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B6" s="52" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C6" s="50" t="s">
         <v>87</v>
@@ -7806,10 +7813,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="52" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B7" s="52" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C7" s="50" t="s">
         <v>87</v>
@@ -7817,10 +7824,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="52" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B8" s="52" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C8" s="50" t="s">
         <v>101</v>
@@ -7828,75 +7835,75 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="52" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B9" s="52"/>
       <c r="C9" s="50"/>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="52" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B10" s="52" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C10" s="50" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="52" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B11" s="52" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C11" s="50" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="52" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B12" s="52" t="s">
+        <v>415</v>
+      </c>
+      <c r="C12" s="50" t="s">
         <v>413</v>
-      </c>
-      <c r="C12" s="50" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="52" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B13" s="52" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C13" s="50" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="52" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B14" s="52" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C14" s="50" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="52" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B15" s="52" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C15" s="50" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -7904,10 +7911,10 @@
         <v>321</v>
       </c>
       <c r="B16" s="137" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C16" s="139" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -7915,18 +7922,18 @@
         <v>346</v>
       </c>
       <c r="B17" s="137" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C17" s="139" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="52" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B18" s="52" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C18" s="50" t="s">
         <v>87</v>
@@ -7934,21 +7941,21 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="53" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B19" s="53" t="s">
         <v>230</v>
       </c>
       <c r="C19" s="51" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B20" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
   </sheetData>
@@ -7975,10 +7982,10 @@
         <v>3</v>
       </c>
       <c r="B1" s="131" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C1" s="130" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -7989,7 +7996,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="170" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F2" s="75"/>
       <c r="G2" s="77"/>
@@ -8006,7 +8013,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="170" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F3" s="75"/>
       <c r="G3" s="2"/>
@@ -8023,7 +8030,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="170" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F4" s="75"/>
       <c r="G4" s="2"/>
@@ -8040,7 +8047,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="170" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F5" s="75"/>
       <c r="G5" s="2"/>
@@ -8057,7 +8064,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="134" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F6" s="75"/>
       <c r="G6" s="2"/>
@@ -8074,7 +8081,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="134" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F7" s="75"/>
       <c r="G7" s="2"/>
@@ -8091,7 +8098,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="134" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="F8" s="75"/>
       <c r="G8" s="2"/>
@@ -8108,7 +8115,7 @@
         <v>8</v>
       </c>
       <c r="C9" s="134" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F9" s="75"/>
       <c r="G9" s="2"/>
@@ -8125,7 +8132,7 @@
         <v>9</v>
       </c>
       <c r="C10" s="134" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="F10" s="75"/>
       <c r="G10" s="2"/>
@@ -8142,7 +8149,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="134" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -8155,7 +8162,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="134" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -8168,7 +8175,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="134" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -8181,7 +8188,7 @@
         <v>13</v>
       </c>
       <c r="C14" s="134" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -8230,12 +8237,12 @@
   <sheetData>
     <row r="2" spans="1:9" ht="23.25">
       <c r="A2" s="91" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="18.75">
       <c r="A3" s="79" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="37.5">
@@ -8261,7 +8268,7 @@
         <v>9</v>
       </c>
       <c r="H5" s="82" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="I5" s="81" t="s">
         <v>11</v>
@@ -8291,7 +8298,7 @@
       </c>
       <c r="H6" s="85"/>
       <c r="I6" s="84" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="18.75">
@@ -8376,7 +8383,7 @@
         <v>206</v>
       </c>
       <c r="I9" s="86" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="18.75">
@@ -8423,14 +8430,14 @@
         <v>10</v>
       </c>
       <c r="F11" s="87" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="G11" s="87" t="s">
         <v>68</v>
       </c>
       <c r="H11" s="87"/>
       <c r="I11" s="86" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="18.75">
@@ -8459,7 +8466,7 @@
         <v>31</v>
       </c>
       <c r="I12" s="86" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="18.75">
@@ -8479,7 +8486,7 @@
         <v>12</v>
       </c>
       <c r="F13" s="87" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="G13" s="87"/>
       <c r="H13" s="87"/>
@@ -8502,7 +8509,7 @@
         <v>13</v>
       </c>
       <c r="F14" s="90" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="G14" s="90" t="s">
         <v>77</v>

--- a/data/MACSI seminar series.xlsx
+++ b/data/MACSI seminar series.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30023"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30110"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ulcampus-my.sharepoint.com/personal/david_osullivan_ul_ie/Documents/Academic_work/_Misc/MACSI Seminars/macsi-seminars.github.io/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="425" documentId="13_ncr:1_{12BE53B5-C8C7-44FE-8280-19C653D9122E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E089D2C8-8CBB-4B2D-8A10-033012470ED4}"/>
+  <xr:revisionPtr revIDLastSave="440" documentId="13_ncr:1_{12BE53B5-C8C7-44FE-8280-19C653D9122E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BACF11D6-FBAB-4DAF-90D2-E3CDAB0DBA6A}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1044" uniqueCount="442">
   <si>
     <t>Fill in as much of the green boxes as possible. Ideally, this would be before you have finished your visitors travel dates (just to avoid double booking).</t>
   </si>
@@ -1282,6 +1282,12 @@
   <si>
     <t xml:space="preserve">The surface Navier-Stokes equations are used to describe fluid flows on surfaces.  A paradigm physical example is modeling the deformation of fluidic membranes.  Constructing finite element methods for surface Stokes problems has proved challenging because the canonical finite element methods for Euclidean Stokes problems do not easily translate to the surface context.  In this talk we will first review the basics of finite element methods for scalar elliptic problems posed on Euclidean domains and surfaces.  We will then briefly discuss construction of finite element methods for Euclidean Stokes problems and describe obstacles to the development of surface Stokes FEM.   Finally, we describe a new approach that yields effective translation of Euclidean Stokes elements such as the canonical Taylor-Hood elements to the surface Stokes context.  
 </t>
+  </si>
+  <si>
+    <t>June</t>
+  </si>
+  <si>
+    <t>Warwick University</t>
   </si>
   <si>
     <t>Open</t>
@@ -7197,9 +7203,27 @@
       <c r="Y15" s="18"/>
     </row>
     <row r="16" spans="1:25" ht="12.75" customHeight="1">
-      <c r="A16" s="26"/>
-      <c r="B16" s="26"/>
-      <c r="C16" s="26"/>
+      <c r="A16" s="26">
+        <v>46175</v>
+      </c>
+      <c r="B16" t="s">
+        <v>190</v>
+      </c>
+      <c r="C16" s="26" t="s">
+        <v>391</v>
+      </c>
+      <c r="D16" t="s">
+        <v>311</v>
+      </c>
+      <c r="E16">
+        <v>19</v>
+      </c>
+      <c r="G16" t="s">
+        <v>392</v>
+      </c>
+      <c r="H16" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="26"/>
@@ -7377,19 +7401,19 @@
         <v>1</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="H3" s="14" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I3" s="98" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="J3" s="98" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K3" s="73"/>
       <c r="L3" s="40"/>
@@ -7428,19 +7452,19 @@
         <v>3</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I4" s="98" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="J4" s="98" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K4" s="102"/>
       <c r="L4" s="5"/>
@@ -7479,19 +7503,19 @@
         <v>5</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I5" s="98" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="J5" s="98" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K5" s="102"/>
       <c r="L5" s="5"/>
@@ -7534,19 +7558,19 @@
         <v>7</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I6" s="98" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="J6" s="98" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K6" s="102"/>
       <c r="L6" s="5"/>
@@ -7585,19 +7609,19 @@
         <v>9</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I7" s="98" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="J7" s="98" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K7" s="102"/>
       <c r="L7" s="5"/>
@@ -7634,19 +7658,19 @@
         <v>11</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I8" s="98" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="J8" s="98" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K8" s="102"/>
       <c r="L8" s="5"/>
@@ -7681,19 +7705,19 @@
         <v>13</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I9" s="98" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="J9" s="98" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K9" s="102"/>
       <c r="L9" s="5"/>
@@ -7759,23 +7783,23 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="55" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B2" s="54" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C2" s="54" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="136" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B3" s="137"/>
       <c r="C3" s="138" t="s">
@@ -7784,7 +7808,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="5" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B4" s="52"/>
       <c r="C4" s="50" t="s">
@@ -7793,19 +7817,19 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="52" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B5" s="52"/>
       <c r="C5" s="50" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="52" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B6" s="52" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C6" s="50" t="s">
         <v>87</v>
@@ -7813,10 +7837,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="52" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B7" s="52" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C7" s="50" t="s">
         <v>87</v>
@@ -7824,10 +7848,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="52" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B8" s="52" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C8" s="50" t="s">
         <v>101</v>
@@ -7835,75 +7859,75 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="52" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B9" s="52"/>
       <c r="C9" s="50"/>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="52" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B10" s="52" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C10" s="50" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="52" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B11" s="52" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C11" s="50" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="52" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B12" s="52" t="s">
+        <v>417</v>
+      </c>
+      <c r="C12" s="50" t="s">
         <v>415</v>
-      </c>
-      <c r="C12" s="50" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="52" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B13" s="52" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C13" s="50" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="52" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B14" s="52" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C14" s="50" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="52" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B15" s="52" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C15" s="50" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -7911,10 +7935,10 @@
         <v>321</v>
       </c>
       <c r="B16" s="137" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C16" s="139" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -7922,18 +7946,18 @@
         <v>346</v>
       </c>
       <c r="B17" s="137" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C17" s="139" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="52" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B18" s="52" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C18" s="50" t="s">
         <v>87</v>
@@ -7941,21 +7965,21 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="53" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B19" s="53" t="s">
         <v>230</v>
       </c>
       <c r="C19" s="51" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B20" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
   </sheetData>
@@ -7982,10 +8006,10 @@
         <v>3</v>
       </c>
       <c r="B1" s="131" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C1" s="130" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -7996,7 +8020,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="170" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="F2" s="75"/>
       <c r="G2" s="77"/>
@@ -8013,7 +8037,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="170" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F3" s="75"/>
       <c r="G3" s="2"/>
@@ -8030,7 +8054,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="170" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="F4" s="75"/>
       <c r="G4" s="2"/>
@@ -8047,7 +8071,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="170" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F5" s="75"/>
       <c r="G5" s="2"/>
@@ -8064,7 +8088,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="134" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="F6" s="75"/>
       <c r="G6" s="2"/>
@@ -8081,7 +8105,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="134" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F7" s="75"/>
       <c r="G7" s="2"/>
@@ -8098,7 +8122,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="134" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F8" s="75"/>
       <c r="G8" s="2"/>
@@ -8115,7 +8139,7 @@
         <v>8</v>
       </c>
       <c r="C9" s="134" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="F9" s="75"/>
       <c r="G9" s="2"/>
@@ -8132,7 +8156,7 @@
         <v>9</v>
       </c>
       <c r="C10" s="134" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F10" s="75"/>
       <c r="G10" s="2"/>
@@ -8149,7 +8173,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="134" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -8162,7 +8186,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="134" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -8175,7 +8199,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="134" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -8188,7 +8212,7 @@
         <v>13</v>
       </c>
       <c r="C14" s="134" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -8237,12 +8261,12 @@
   <sheetData>
     <row r="2" spans="1:9" ht="23.25">
       <c r="A2" s="91" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="18.75">
       <c r="A3" s="79" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="37.5">
@@ -8268,7 +8292,7 @@
         <v>9</v>
       </c>
       <c r="H5" s="82" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="I5" s="81" t="s">
         <v>11</v>
@@ -8298,7 +8322,7 @@
       </c>
       <c r="H6" s="85"/>
       <c r="I6" s="84" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="18.75">
@@ -8383,7 +8407,7 @@
         <v>206</v>
       </c>
       <c r="I9" s="86" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="18.75">
@@ -8430,14 +8454,14 @@
         <v>10</v>
       </c>
       <c r="F11" s="87" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="G11" s="87" t="s">
         <v>68</v>
       </c>
       <c r="H11" s="87"/>
       <c r="I11" s="86" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="18.75">
@@ -8466,7 +8490,7 @@
         <v>31</v>
       </c>
       <c r="I12" s="86" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="18.75">
@@ -8486,7 +8510,7 @@
         <v>12</v>
       </c>
       <c r="F13" s="87" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="G13" s="87"/>
       <c r="H13" s="87"/>
@@ -8509,7 +8533,7 @@
         <v>13</v>
       </c>
       <c r="F14" s="90" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="G14" s="90" t="s">
         <v>77</v>

--- a/data/MACSI seminar series.xlsx
+++ b/data/MACSI seminar series.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ulcampus-my.sharepoint.com/personal/david_osullivan_ul_ie/Documents/Academic_work/_Misc/MACSI Seminars/macsi-seminars.github.io/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="440" documentId="13_ncr:1_{12BE53B5-C8C7-44FE-8280-19C653D9122E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BACF11D6-FBAB-4DAF-90D2-E3CDAB0DBA6A}"/>
+  <xr:revisionPtr revIDLastSave="444" documentId="13_ncr:1_{12BE53B5-C8C7-44FE-8280-19C653D9122E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B65A9E4-15AD-47F3-AF5C-6B2EA0E64C24}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4410" yWindow="4185" windowWidth="21600" windowHeight="11295" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AY2023-2024 Sem 2" sheetId="3" state="hidden" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1044" uniqueCount="442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1047" uniqueCount="443">
   <si>
     <t>Fill in as much of the green boxes as possible. Ideally, this would be before you have finished your visitors travel dates (just to avoid double booking).</t>
   </si>
@@ -1287,15 +1287,15 @@
     <t>June</t>
   </si>
   <si>
+    <t>TBC</t>
+  </si>
+  <si>
     <t>Warwick University</t>
   </si>
   <si>
     <t>Open</t>
   </si>
   <si>
-    <t>TBC</t>
-  </si>
-  <si>
     <t>This is a just a place for those who are interested but that dont have a specific date in mind. (Ideally, a couple of these are people that we could invite with relatively short notice to fill missing slots.)</t>
   </si>
   <si>
@@ -1435,6 +1435,9 @@
   </si>
   <si>
     <t>Leornard Henckel</t>
+  </si>
+  <si>
+    <t>Martine Barons</t>
   </si>
 </sst>
 </file>
@@ -1444,7 +1447,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2302,9 +2305,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2342,7 +2345,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2448,7 +2451,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2590,7 +2593,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2599,7 +2602,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7958562-D4BB-4776-9668-682A6F2E2AD0}">
   <dimension ref="A1:Y20"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="11.140625" customWidth="1"/>
@@ -2624,7 +2627,7 @@
     <col min="25" max="25" width="37.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2635,7 +2638,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="30">
+    <row r="2" spans="1:25" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -2712,7 +2715,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="13.5" customHeight="1">
+    <row r="3" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>45317</v>
       </c>
@@ -2779,7 +2782,7 @@
       <c r="X3" s="13"/>
       <c r="Y3" s="13"/>
     </row>
-    <row r="4" spans="1:25" ht="13.5" customHeight="1">
+    <row r="4" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>45323</v>
       </c>
@@ -2842,7 +2845,7 @@
       <c r="X4" s="13"/>
       <c r="Y4" s="13"/>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>45324</v>
       </c>
@@ -2903,7 +2906,7 @@
       <c r="X5" s="13"/>
       <c r="Y5" s="13"/>
     </row>
-    <row r="6" spans="1:25" ht="12.75" customHeight="1">
+    <row r="6" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>45331</v>
       </c>
@@ -2970,7 +2973,7 @@
       <c r="X6" s="13"/>
       <c r="Y6" s="13"/>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>45338</v>
       </c>
@@ -3039,7 +3042,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="15" customHeight="1">
+    <row r="8" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>45345</v>
       </c>
@@ -3106,7 +3109,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="16.5" customHeight="1">
+    <row r="9" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>45359</v>
       </c>
@@ -3159,7 +3162,7 @@
       <c r="X9" s="13"/>
       <c r="Y9" s="13"/>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>45366</v>
       </c>
@@ -3228,7 +3231,7 @@
       <c r="X10" s="13"/>
       <c r="Y10" s="13"/>
     </row>
-    <row r="11" spans="1:25" ht="15" customHeight="1">
+    <row r="11" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>45379</v>
       </c>
@@ -3289,7 +3292,7 @@
       <c r="X11" s="13"/>
       <c r="Y11" s="13"/>
     </row>
-    <row r="12" spans="1:25" ht="13.5" customHeight="1">
+    <row r="12" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>45386</v>
       </c>
@@ -3352,7 +3355,7 @@
       <c r="X12" s="13"/>
       <c r="Y12" s="13"/>
     </row>
-    <row r="13" spans="1:25" ht="16.5" customHeight="1">
+    <row r="13" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>45387</v>
       </c>
@@ -3421,7 +3424,7 @@
       <c r="X13" s="13"/>
       <c r="Y13" s="13"/>
     </row>
-    <row r="14" spans="1:25" ht="15.75" customHeight="1">
+    <row r="14" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>45394</v>
       </c>
@@ -3482,7 +3485,7 @@
       <c r="X14" s="13"/>
       <c r="Y14" s="13"/>
     </row>
-    <row r="15" spans="1:25" ht="17.25" customHeight="1">
+    <row r="15" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>45398</v>
       </c>
@@ -3551,7 +3554,7 @@
       <c r="X15" s="13"/>
       <c r="Y15" s="13"/>
     </row>
-    <row r="16" spans="1:25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>45401</v>
       </c>
@@ -3614,7 +3617,7 @@
       <c r="X16" s="18"/>
       <c r="Y16" s="18"/>
     </row>
-    <row r="17" spans="1:25">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>45421</v>
       </c>
@@ -3685,7 +3688,7 @@
       <c r="X17" s="18"/>
       <c r="Y17" s="18"/>
     </row>
-    <row r="18" spans="1:25">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" s="26">
         <v>45474</v>
       </c>
@@ -3736,7 +3739,7 @@
       <c r="X18" s="18"/>
       <c r="Y18" s="18"/>
     </row>
-    <row r="19" spans="1:25" ht="17.25" customHeight="1" thickBot="1">
+    <row r="19" spans="1:25" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="26">
         <v>45505</v>
       </c>
@@ -3787,7 +3790,7 @@
       <c r="X19" s="18"/>
       <c r="Y19" s="18"/>
     </row>
-    <row r="20" spans="1:25">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20" s="26"/>
       <c r="B20" s="26"/>
       <c r="C20" s="26"/>
@@ -3829,7 +3832,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y44"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="11.140625" customWidth="1"/>
@@ -3854,7 +3857,7 @@
     <col min="25" max="25" width="37.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3865,7 +3868,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="30.75" thickBot="1">
+    <row r="2" spans="1:25" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="145" t="s">
         <v>3</v>
       </c>
@@ -3942,7 +3945,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15" customHeight="1">
+    <row r="3" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>45548</v>
       </c>
@@ -4007,7 +4010,7 @@
       <c r="X3" s="46"/>
       <c r="Y3" s="44"/>
     </row>
-    <row r="4" spans="1:25" ht="15" customHeight="1">
+    <row r="4" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>45555</v>
       </c>
@@ -4056,7 +4059,7 @@
       <c r="X4" s="15"/>
       <c r="Y4" s="13"/>
     </row>
-    <row r="5" spans="1:25" ht="15" customHeight="1">
+    <row r="5" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>45562</v>
       </c>
@@ -4105,7 +4108,7 @@
       <c r="X5" s="15"/>
       <c r="Y5" s="13"/>
     </row>
-    <row r="6" spans="1:25" ht="15" customHeight="1">
+    <row r="6" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>45576</v>
       </c>
@@ -4154,7 +4157,7 @@
       <c r="X6" s="15"/>
       <c r="Y6" s="13"/>
     </row>
-    <row r="7" spans="1:25" ht="15" customHeight="1">
+    <row r="7" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>45583</v>
       </c>
@@ -4203,7 +4206,7 @@
       <c r="X7" s="15"/>
       <c r="Y7" s="13"/>
     </row>
-    <row r="8" spans="1:25" ht="15" customHeight="1">
+    <row r="8" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>45596</v>
       </c>
@@ -4252,7 +4255,7 @@
       <c r="X8" s="15"/>
       <c r="Y8" s="13"/>
     </row>
-    <row r="9" spans="1:25" ht="15" customHeight="1">
+    <row r="9" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>45604</v>
       </c>
@@ -4301,7 +4304,7 @@
       <c r="X9" s="15"/>
       <c r="Y9" s="13"/>
     </row>
-    <row r="10" spans="1:25" ht="15" customHeight="1">
+    <row r="10" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>45611</v>
       </c>
@@ -4350,7 +4353,7 @@
       <c r="X10" s="15"/>
       <c r="Y10" s="13"/>
     </row>
-    <row r="11" spans="1:25" ht="15" customHeight="1">
+    <row r="11" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>45625</v>
       </c>
@@ -4399,7 +4402,7 @@
       <c r="X11" s="15"/>
       <c r="Y11" s="13"/>
     </row>
-    <row r="12" spans="1:25" ht="15" customHeight="1" thickBot="1">
+    <row r="12" spans="1:25" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
         <v>45632</v>
       </c>
@@ -4456,20 +4459,20 @@
       <c r="X12" s="20"/>
       <c r="Y12" s="18"/>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13" s="26"/>
       <c r="B13" s="26"/>
       <c r="C13" s="26"/>
       <c r="D13" s="26"/>
       <c r="I13" s="3"/>
     </row>
-    <row r="14" spans="1:25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" s="26"/>
       <c r="B14" s="26"/>
       <c r="C14" s="26"/>
       <c r="D14" s="26"/>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="61"/>
       <c r="B29" s="61"/>
       <c r="C29" s="61"/>
@@ -4481,59 +4484,59 @@
       <c r="I29" s="61"/>
       <c r="J29" s="61"/>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="60"/>
       <c r="B31" s="60"/>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="60"/>
       <c r="B32" s="60"/>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="60"/>
       <c r="B33" s="60"/>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="60"/>
       <c r="B34" s="60"/>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="60"/>
       <c r="B35" s="60"/>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="60"/>
       <c r="B36" s="60"/>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="60"/>
       <c r="B37" s="60"/>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="60"/>
       <c r="B38" s="60"/>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="60"/>
       <c r="B39" s="60"/>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="60"/>
       <c r="B40" s="60"/>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="60"/>
       <c r="B41" s="60"/>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="60"/>
       <c r="B42" s="60"/>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="60"/>
       <c r="B43" s="60"/>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="60"/>
       <c r="B44" s="60"/>
     </row>
@@ -4562,7 +4565,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12299A9A-6C0C-4F92-957E-FBFCB6211744}">
   <dimension ref="A1:Y45"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.5703125" customWidth="1"/>
     <col min="2" max="2" width="5.85546875" bestFit="1" customWidth="1"/>
@@ -4590,7 +4593,7 @@
     <col min="25" max="25" width="37.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4601,7 +4604,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="27.75" customHeight="1" thickBot="1">
+    <row r="2" spans="1:25" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="64" t="s">
         <v>3</v>
       </c>
@@ -4678,7 +4681,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15" customHeight="1">
+    <row r="3" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>45694</v>
       </c>
@@ -4730,7 +4733,7 @@
       <c r="X3" s="46"/>
       <c r="Y3" s="44"/>
     </row>
-    <row r="4" spans="1:25" ht="14.25" customHeight="1">
+    <row r="4" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>45708</v>
       </c>
@@ -4788,7 +4791,7 @@
       <c r="X4" s="15"/>
       <c r="Y4" s="13"/>
     </row>
-    <row r="5" spans="1:25" ht="14.25" customHeight="1">
+    <row r="5" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>45722</v>
       </c>
@@ -4844,7 +4847,7 @@
       <c r="X5" s="15"/>
       <c r="Y5" s="13"/>
     </row>
-    <row r="6" spans="1:25" ht="16.5" customHeight="1">
+    <row r="6" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>45735</v>
       </c>
@@ -4900,7 +4903,7 @@
       <c r="X6" s="15"/>
       <c r="Y6" s="13"/>
     </row>
-    <row r="7" spans="1:25" ht="18" customHeight="1">
+    <row r="7" spans="1:25" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>45750</v>
       </c>
@@ -4954,7 +4957,7 @@
       <c r="X7" s="15"/>
       <c r="Y7" s="13"/>
     </row>
-    <row r="8" spans="1:25" ht="16.5" customHeight="1">
+    <row r="8" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>45751</v>
       </c>
@@ -5013,7 +5016,7 @@
       <c r="X8" s="15"/>
       <c r="Y8" s="13"/>
     </row>
-    <row r="9" spans="1:25" ht="15.75" customHeight="1">
+    <row r="9" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>45757</v>
       </c>
@@ -5075,7 +5078,7 @@
       <c r="X9" s="15"/>
       <c r="Y9" s="13"/>
     </row>
-    <row r="10" spans="1:25" ht="15.75" customHeight="1">
+    <row r="10" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>45758</v>
       </c>
@@ -5129,7 +5132,7 @@
       <c r="X10" s="20"/>
       <c r="Y10" s="18"/>
     </row>
-    <row r="11" spans="1:25" ht="15.75" customHeight="1">
+    <row r="11" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>45764</v>
       </c>
@@ -5189,7 +5192,7 @@
       <c r="X11" s="35"/>
       <c r="Y11" s="35"/>
     </row>
-    <row r="12" spans="1:25" ht="15.75" customHeight="1">
+    <row r="12" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>45771</v>
       </c>
@@ -5250,7 +5253,7 @@
       <c r="X12" s="35"/>
       <c r="Y12" s="35"/>
     </row>
-    <row r="13" spans="1:25" ht="15.75" customHeight="1">
+    <row r="13" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>45785</v>
       </c>
@@ -5303,7 +5306,7 @@
       <c r="X13" s="35"/>
       <c r="Y13" s="35"/>
     </row>
-    <row r="14" spans="1:25" ht="15.75" customHeight="1">
+    <row r="14" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>45799</v>
       </c>
@@ -5349,7 +5352,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="15.75" customHeight="1">
+    <row r="15" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>45805</v>
       </c>
@@ -5383,101 +5386,101 @@
         <v>250</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="15.75" customHeight="1">
+    <row r="16" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="75"/>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="26"/>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="26"/>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="26"/>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="75"/>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="26"/>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="75"/>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="26"/>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="26"/>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="26"/>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="26"/>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="26"/>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="26"/>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B31" s="60"/>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="60"/>
       <c r="B32" s="60"/>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="60"/>
       <c r="B33" s="60"/>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="60"/>
       <c r="B34" s="60"/>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="60"/>
       <c r="B35" s="60"/>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="60"/>
       <c r="B36" s="60"/>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="60"/>
       <c r="B37" s="60"/>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="60"/>
       <c r="B38" s="60"/>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="60"/>
       <c r="B39" s="60"/>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="60"/>
       <c r="B40" s="60"/>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="60"/>
       <c r="B41" s="60"/>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="60"/>
       <c r="B42" s="60"/>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="60"/>
       <c r="B43" s="60"/>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="60"/>
       <c r="B44" s="60"/>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="60"/>
     </row>
   </sheetData>
@@ -5502,7 +5505,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{243C2AD8-98F5-4435-96A3-1C2CAB922825}">
   <dimension ref="A1:Y26"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="14.5703125" customWidth="1"/>
@@ -5529,7 +5532,7 @@
     <col min="25" max="25" width="37.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5540,7 +5543,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="30">
+    <row r="2" spans="1:25" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="78" t="s">
         <v>3</v>
       </c>
@@ -5617,7 +5620,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15" customHeight="1" thickBot="1">
+    <row r="3" spans="1:25" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="159">
         <v>45911</v>
       </c>
@@ -5680,7 +5683,7 @@
       <c r="X3" s="46"/>
       <c r="Y3" s="44"/>
     </row>
-    <row r="4" spans="1:25" ht="15" customHeight="1">
+    <row r="4" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="160">
         <v>45917</v>
       </c>
@@ -5749,7 +5752,7 @@
       <c r="X4" s="15"/>
       <c r="Y4" s="13"/>
     </row>
-    <row r="5" spans="1:25" ht="15" customHeight="1">
+    <row r="5" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="160">
         <v>45926</v>
       </c>
@@ -5807,7 +5810,7 @@
       <c r="X5" s="15"/>
       <c r="Y5" s="13"/>
     </row>
-    <row r="6" spans="1:25" ht="15" customHeight="1">
+    <row r="6" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="160">
         <v>45939</v>
       </c>
@@ -5871,7 +5874,7 @@
       <c r="X6" s="15"/>
       <c r="Y6" s="13"/>
     </row>
-    <row r="7" spans="1:25" ht="15" customHeight="1">
+    <row r="7" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="160">
         <v>45946</v>
       </c>
@@ -5928,7 +5931,7 @@
       <c r="X7" s="15"/>
       <c r="Y7" s="13"/>
     </row>
-    <row r="8" spans="1:25" ht="15" customHeight="1">
+    <row r="8" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="160">
         <v>45953</v>
       </c>
@@ -5986,7 +5989,7 @@
       <c r="X8" s="15"/>
       <c r="Y8" s="13"/>
     </row>
-    <row r="9" spans="1:25" ht="15" customHeight="1">
+    <row r="9" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="160">
         <v>45967</v>
       </c>
@@ -6048,7 +6051,7 @@
       <c r="X9" s="15"/>
       <c r="Y9" s="13"/>
     </row>
-    <row r="10" spans="1:25" ht="15" customHeight="1">
+    <row r="10" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="160">
         <v>45974</v>
       </c>
@@ -6111,7 +6114,7 @@
       <c r="X10" s="15"/>
       <c r="Y10" s="13"/>
     </row>
-    <row r="11" spans="1:25" ht="15" customHeight="1">
+    <row r="11" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="160">
         <v>45980</v>
       </c>
@@ -6162,7 +6165,7 @@
       <c r="X11" s="35"/>
       <c r="Y11" s="35"/>
     </row>
-    <row r="12" spans="1:25" ht="16.5" customHeight="1">
+    <row r="12" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="160">
         <f>A10+7</f>
         <v>45981</v>
@@ -6215,7 +6218,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13" s="160">
         <v>45986</v>
       </c>
@@ -6251,7 +6254,7 @@
       <c r="M13" s="158"/>
       <c r="N13" s="158"/>
     </row>
-    <row r="14" spans="1:25" ht="15" customHeight="1">
+    <row r="14" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="160">
         <v>45988</v>
       </c>
@@ -6306,7 +6309,7 @@
       <c r="X14" s="15"/>
       <c r="Y14" s="13"/>
     </row>
-    <row r="15" spans="1:25" ht="15" customHeight="1" thickBot="1">
+    <row r="15" spans="1:25" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="161">
         <v>45995</v>
       </c>
@@ -6369,35 +6372,35 @@
       <c r="X15" s="15"/>
       <c r="Y15" s="13"/>
     </row>
-    <row r="16" spans="1:25" ht="15" customHeight="1" thickBot="1">
+    <row r="16" spans="1:25" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="26"/>
       <c r="B16" s="26"/>
       <c r="C16" s="26"/>
       <c r="X16" s="20"/>
       <c r="Y16" s="18"/>
     </row>
-    <row r="17" spans="1:3" ht="15" customHeight="1">
+    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="26"/>
       <c r="B17" s="26"/>
       <c r="C17" s="26"/>
     </row>
-    <row r="18" spans="1:3" ht="15" customHeight="1">
+    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="26"/>
       <c r="B18" s="26"/>
       <c r="C18" s="26"/>
     </row>
-    <row r="19" spans="1:3" ht="15" customHeight="1">
+    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="26"/>
       <c r="B19" s="26"/>
       <c r="C19" s="26"/>
     </row>
-    <row r="20" spans="1:3" ht="15" customHeight="1"/>
-    <row r="21" spans="1:3" ht="15" customHeight="1"/>
-    <row r="22" spans="1:3" ht="15" customHeight="1"/>
-    <row r="23" spans="1:3" ht="15" customHeight="1"/>
-    <row r="24" spans="1:3" ht="15" customHeight="1"/>
-    <row r="25" spans="1:3" ht="15" customHeight="1"/>
-    <row r="26" spans="1:3" ht="15" customHeight="1"/>
+    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <protectedRanges>
     <protectedRange algorithmName="SHA-512" hashValue="pQyTzP/d7t5ThMimBt5mu8gGozgAm1OwF6BMILsn5/kmtZ5mZf81NMi09wwU8mvtItxf0EVNWa6V4MCa0DKeSQ==" saltValue="NzZBiAQ1yFjat+SeIqh2Uw==" spinCount="100000" sqref="A3:E19" name="Range3_1"/>
@@ -6431,7 +6434,7 @@
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="A1:Y18"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.5703125" customWidth="1"/>
     <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
@@ -6458,7 +6461,7 @@
     <col min="25" max="25" width="37.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6469,7 +6472,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="30">
+    <row r="2" spans="1:25" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="64" t="s">
         <v>3</v>
       </c>
@@ -6546,7 +6549,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15" customHeight="1">
+    <row r="3" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="75">
         <v>46051</v>
       </c>
@@ -6595,7 +6598,7 @@
       <c r="X3" s="46"/>
       <c r="Y3" s="44"/>
     </row>
-    <row r="4" spans="1:25" ht="15.75" customHeight="1">
+    <row r="4" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="75">
         <f>A3+12</f>
         <v>46063</v>
@@ -6646,7 +6649,7 @@
       <c r="X4" s="15"/>
       <c r="Y4" s="13"/>
     </row>
-    <row r="5" spans="1:25" ht="18.75" customHeight="1">
+    <row r="5" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="75">
         <f>A4+16</f>
         <v>46079</v>
@@ -6701,7 +6704,7 @@
       <c r="X5" s="15"/>
       <c r="Y5" s="13"/>
     </row>
-    <row r="6" spans="1:25" ht="15.75" customHeight="1">
+    <row r="6" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="75">
         <f>A5+14</f>
         <v>46093</v>
@@ -6756,7 +6759,7 @@
       <c r="X6" s="15"/>
       <c r="Y6" s="13"/>
     </row>
-    <row r="7" spans="1:25" ht="15.75" customHeight="1">
+    <row r="7" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="75">
         <f>A6+7</f>
         <v>46100</v>
@@ -6810,7 +6813,7 @@
       <c r="X7" s="15"/>
       <c r="Y7" s="13"/>
     </row>
-    <row r="8" spans="1:25" ht="17.25" customHeight="1">
+    <row r="8" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="75">
         <f>A6+14</f>
         <v>46107</v>
@@ -6863,7 +6866,7 @@
       <c r="X8" s="15"/>
       <c r="Y8" s="13"/>
     </row>
-    <row r="9" spans="1:25" ht="18" customHeight="1">
+    <row r="9" spans="1:25" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="75">
         <f>A8+7</f>
         <v>46114</v>
@@ -6917,7 +6920,7 @@
       <c r="X9" s="15"/>
       <c r="Y9" s="13"/>
     </row>
-    <row r="10" spans="1:25" ht="15" customHeight="1">
+    <row r="10" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="75">
         <v>46120</v>
       </c>
@@ -6966,7 +6969,7 @@
       <c r="X10" s="15"/>
       <c r="Y10" s="13"/>
     </row>
-    <row r="11" spans="1:25" ht="14.25" customHeight="1">
+    <row r="11" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="75">
         <v>46121</v>
       </c>
@@ -7017,7 +7020,7 @@
       <c r="X11" s="15"/>
       <c r="Y11" s="13"/>
     </row>
-    <row r="12" spans="1:25" ht="16.5" customHeight="1">
+    <row r="12" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="75">
         <v>46128</v>
       </c>
@@ -7070,7 +7073,7 @@
       <c r="X12" s="15"/>
       <c r="Y12" s="13"/>
     </row>
-    <row r="13" spans="1:25" ht="18.75" customHeight="1">
+    <row r="13" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="75">
         <v>46135</v>
       </c>
@@ -7117,7 +7120,7 @@
       <c r="X13" s="15"/>
       <c r="Y13" s="13"/>
     </row>
-    <row r="14" spans="1:25" ht="18.75" customHeight="1">
+    <row r="14" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="75">
         <v>46142</v>
       </c>
@@ -7168,7 +7171,7 @@
       <c r="X14" s="15"/>
       <c r="Y14" s="13"/>
     </row>
-    <row r="15" spans="1:25" ht="20.25" customHeight="1">
+    <row r="15" spans="1:25" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="26">
         <v>46155</v>
       </c>
@@ -7202,7 +7205,7 @@
       <c r="X15" s="20"/>
       <c r="Y15" s="18"/>
     </row>
-    <row r="16" spans="1:25" ht="12.75" customHeight="1">
+    <row r="16" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="26">
         <v>46175</v>
       </c>
@@ -7218,19 +7221,28 @@
       <c r="E16">
         <v>19</v>
       </c>
+      <c r="F16" t="s">
+        <v>442</v>
+      </c>
       <c r="G16" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H16" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
+      <c r="I16" t="s">
+        <v>392</v>
+      </c>
+      <c r="J16" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="26"/>
       <c r="B17" s="26"/>
       <c r="C17" s="26"/>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="26"/>
       <c r="B18" s="26"/>
       <c r="C18" s="26"/>
@@ -7267,7 +7279,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A33E49C-EC2E-42B7-80E4-DD607C0B7A89}">
   <dimension ref="A1:Y13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.5703125" customWidth="1"/>
     <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
@@ -7294,7 +7306,7 @@
     <col min="25" max="25" width="37.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="15.75" thickBot="1">
+    <row r="1" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7305,7 +7317,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="30.75" thickBot="1">
+    <row r="2" spans="1:25" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="64" t="s">
         <v>3</v>
       </c>
@@ -7382,7 +7394,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15" customHeight="1">
+    <row r="3" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="75">
         <v>46275</v>
       </c>
@@ -7401,19 +7413,19 @@
         <v>1</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H3" s="14" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="I3" s="98" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="J3" s="98" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="K3" s="73"/>
       <c r="L3" s="40"/>
@@ -7431,7 +7443,7 @@
       <c r="X3" s="46"/>
       <c r="Y3" s="44"/>
     </row>
-    <row r="4" spans="1:25" ht="15.75" customHeight="1">
+    <row r="4" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="75">
         <f>A3+14</f>
         <v>46289</v>
@@ -7452,19 +7464,19 @@
         <v>3</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="I4" s="98" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="J4" s="98" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="K4" s="102"/>
       <c r="L4" s="5"/>
@@ -7482,7 +7494,7 @@
       <c r="X4" s="15"/>
       <c r="Y4" s="13"/>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" s="75">
         <f t="shared" ref="A5" si="2">A4+14</f>
         <v>46303</v>
@@ -7503,19 +7515,19 @@
         <v>5</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="I5" s="98" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="J5" s="98" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="K5" s="102"/>
       <c r="L5" s="5"/>
@@ -7537,7 +7549,7 @@
       <c r="X5" s="15"/>
       <c r="Y5" s="13"/>
     </row>
-    <row r="6" spans="1:25" ht="15.75" customHeight="1">
+    <row r="6" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="75">
         <f>A5+14</f>
         <v>46317</v>
@@ -7558,19 +7570,19 @@
         <v>7</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="I6" s="98" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="J6" s="98" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="K6" s="102"/>
       <c r="L6" s="5"/>
@@ -7588,7 +7600,7 @@
       <c r="X6" s="15"/>
       <c r="Y6" s="13"/>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" s="75">
         <f>A6+14</f>
         <v>46331</v>
@@ -7609,19 +7621,19 @@
         <v>9</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="I7" s="98" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="J7" s="98" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="K7" s="102"/>
       <c r="L7" s="5"/>
@@ -7639,7 +7651,7 @@
       <c r="X7" s="15"/>
       <c r="Y7" s="13"/>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" s="75">
         <f>A7+14</f>
         <v>46345</v>
@@ -7658,19 +7670,19 @@
         <v>11</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="I8" s="98" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="J8" s="98" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="K8" s="102"/>
       <c r="L8" s="5"/>
@@ -7688,7 +7700,7 @@
       <c r="X8" s="15"/>
       <c r="Y8" s="13"/>
     </row>
-    <row r="9" spans="1:25" ht="18.75" customHeight="1">
+    <row r="9" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="75">
         <v>46121</v>
       </c>
@@ -7705,19 +7717,19 @@
         <v>13</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="I9" s="98" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="J9" s="98" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="K9" s="102"/>
       <c r="L9" s="5"/>
@@ -7735,24 +7747,24 @@
       <c r="X9" s="15"/>
       <c r="Y9" s="13"/>
     </row>
-    <row r="10" spans="1:25" ht="15.75" thickBot="1">
+    <row r="10" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="26"/>
       <c r="B10" s="26"/>
       <c r="C10" s="26"/>
       <c r="X10" s="20"/>
       <c r="Y10" s="18"/>
     </row>
-    <row r="11" spans="1:25" ht="12.75" customHeight="1">
+    <row r="11" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="26"/>
       <c r="B11" s="26"/>
       <c r="C11" s="26"/>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12" s="26"/>
       <c r="B12" s="26"/>
       <c r="C12" s="26"/>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13" s="26"/>
       <c r="B13" s="26"/>
       <c r="C13" s="26"/>
@@ -7774,19 +7786,19 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AEC079F-155A-491D-9189-1418FC903287}">
   <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.28515625" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
     <col min="3" max="3" width="20.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="55" t="s">
         <v>396</v>
       </c>
@@ -7797,7 +7809,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="136" t="s">
         <v>399</v>
       </c>
@@ -7806,7 +7818,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>400</v>
       </c>
@@ -7815,7 +7827,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="52" t="s">
         <v>401</v>
       </c>
@@ -7824,7 +7836,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="52" t="s">
         <v>403</v>
       </c>
@@ -7835,7 +7847,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="52" t="s">
         <v>405</v>
       </c>
@@ -7846,7 +7858,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="52" t="s">
         <v>407</v>
       </c>
@@ -7857,14 +7869,14 @@
         <v>101</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="52" t="s">
         <v>409</v>
       </c>
       <c r="B9" s="52"/>
       <c r="C9" s="50"/>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="52" t="s">
         <v>410</v>
       </c>
@@ -7875,7 +7887,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="52" t="s">
         <v>413</v>
       </c>
@@ -7886,7 +7898,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="52" t="s">
         <v>416</v>
       </c>
@@ -7897,7 +7909,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="52" t="s">
         <v>418</v>
       </c>
@@ -7908,7 +7920,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="52" t="s">
         <v>420</v>
       </c>
@@ -7919,7 +7931,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="52" t="s">
         <v>422</v>
       </c>
@@ -7930,7 +7942,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="137" t="s">
         <v>321</v>
       </c>
@@ -7941,7 +7953,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="137" t="s">
         <v>346</v>
       </c>
@@ -7952,7 +7964,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="52" t="s">
         <v>427</v>
       </c>
@@ -7963,7 +7975,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="53" t="s">
         <v>428</v>
       </c>
@@ -7974,7 +7986,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>430</v>
       </c>
@@ -7995,13 +8007,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AD19DE5-C22F-4D41-B540-76D70438E18B}">
   <dimension ref="A1:I16"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.85546875" customWidth="1"/>
     <col min="6" max="6" width="14.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" thickBot="1">
+    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="135" t="s">
         <v>3</v>
       </c>
@@ -8012,7 +8024,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="169">
         <v>46051</v>
       </c>
@@ -8027,7 +8039,7 @@
       <c r="H2" s="29"/>
       <c r="I2" s="55"/>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="171">
         <f>A2+7</f>
         <v>46058</v>
@@ -8037,14 +8049,14 @@
         <v>2</v>
       </c>
       <c r="C3" s="170" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F3" s="75"/>
       <c r="G3" s="2"/>
       <c r="H3" s="26"/>
       <c r="I3" s="27"/>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="171">
         <f t="shared" ref="A4:A12" si="0">A3+7</f>
         <v>46065</v>
@@ -8061,7 +8073,7 @@
       <c r="H4" s="26"/>
       <c r="I4" s="27"/>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="171">
         <f t="shared" si="0"/>
         <v>46072</v>
@@ -8071,14 +8083,14 @@
         <v>4</v>
       </c>
       <c r="C5" s="170" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F5" s="75"/>
       <c r="G5" s="2"/>
       <c r="H5" s="26"/>
       <c r="I5" s="27"/>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="133">
         <f t="shared" si="0"/>
         <v>46079</v>
@@ -8095,7 +8107,7 @@
       <c r="H6" s="26"/>
       <c r="I6" s="27"/>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="133">
         <f t="shared" si="0"/>
         <v>46086</v>
@@ -8105,14 +8117,14 @@
         <v>6</v>
       </c>
       <c r="C7" s="134" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F7" s="75"/>
       <c r="G7" s="2"/>
       <c r="H7" s="26"/>
       <c r="I7" s="27"/>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="133">
         <f t="shared" si="0"/>
         <v>46093</v>
@@ -8129,7 +8141,7 @@
       <c r="H8" s="26"/>
       <c r="I8" s="27"/>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="133">
         <f t="shared" si="0"/>
         <v>46100</v>
@@ -8146,7 +8158,7 @@
       <c r="H9" s="26"/>
       <c r="I9" s="27"/>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="133">
         <f t="shared" si="0"/>
         <v>46107</v>
@@ -8163,7 +8175,7 @@
       <c r="H10" s="26"/>
       <c r="I10" s="27"/>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="133">
         <f t="shared" si="0"/>
         <v>46114</v>
@@ -8176,7 +8188,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="133">
         <f t="shared" si="0"/>
         <v>46121</v>
@@ -8189,7 +8201,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="133">
         <f t="shared" ref="A13:A14" si="3">A12+7</f>
         <v>46128</v>
@@ -8202,7 +8214,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="133">
         <f t="shared" si="3"/>
         <v>46135</v>
@@ -8215,12 +8227,12 @@
         <v>434</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="133"/>
       <c r="B15" s="134"/>
       <c r="C15" s="134"/>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="G16" s="26"/>
     </row>
   </sheetData>
@@ -8247,7 +8259,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2BB5C5F-5790-4A91-A6E8-8841719DA1FC}">
   <dimension ref="A2:I20"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.42578125" customWidth="1"/>
     <col min="2" max="2" width="9.140625" customWidth="1"/>
@@ -8259,17 +8271,17 @@
     <col min="9" max="9" width="64.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" ht="23.25">
+    <row r="2" spans="1:9" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A2" s="91" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="18.75">
+    <row r="3" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A3" s="79" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="37.5">
+    <row r="5" spans="1:9" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A5" s="80" t="s">
         <v>3</v>
       </c>
@@ -8298,7 +8310,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="18.75">
+    <row r="6" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A6" s="92">
         <v>45694</v>
       </c>
@@ -8322,10 +8334,10 @@
       </c>
       <c r="H6" s="85"/>
       <c r="I6" s="84" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="18.75">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A7" s="83">
         <v>45708</v>
       </c>
@@ -8354,7 +8366,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="18.75">
+    <row r="8" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A8" s="83">
         <v>45722</v>
       </c>
@@ -8381,7 +8393,7 @@
       </c>
       <c r="I8" s="86"/>
     </row>
-    <row r="9" spans="1:9" ht="18.75">
+    <row r="9" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A9" s="83">
         <v>45735</v>
       </c>
@@ -8407,10 +8419,10 @@
         <v>206</v>
       </c>
       <c r="I9" s="86" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="18.75">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A10" s="83">
         <v>45744</v>
       </c>
@@ -8437,7 +8449,7 @@
       </c>
       <c r="I10" s="86"/>
     </row>
-    <row r="11" spans="1:9" ht="18.75">
+    <row r="11" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A11" s="83">
         <v>45750</v>
       </c>
@@ -8461,10 +8473,10 @@
       </c>
       <c r="H11" s="87"/>
       <c r="I11" s="86" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="18.75">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A12" s="83">
         <v>45758</v>
       </c>
@@ -8490,10 +8502,10 @@
         <v>31</v>
       </c>
       <c r="I12" s="86" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="18.75">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A13" s="83">
         <v>45764</v>
       </c>
@@ -8516,7 +8528,7 @@
       <c r="H13" s="87"/>
       <c r="I13" s="86"/>
     </row>
-    <row r="14" spans="1:9" ht="18.75">
+    <row r="14" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A14" s="88">
         <v>45771</v>
       </c>
@@ -8545,7 +8557,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="20" spans="8:8" ht="18.75">
+    <row r="20" spans="8:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="H20" s="79"/>
     </row>
   </sheetData>
